--- a/referencia/formularios/exemplos/exemplo-loteamento-vale-do-sol-avancado.xlsx
+++ b/referencia/formularios/exemplos/exemplo-loteamento-vale-do-sol-avancado.xlsx
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F883"/>
+  <dimension ref="A1:F917"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -600,7 +600,7 @@
     <row r="2" ht="92" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Como preencher: só as células AMARELAS da coluna B. Cinza-claro com valor em negrito = fixo do tipo de estudo (não editar); cinza com itálico = calculado pelo Excel, só para conferir (não editar). * = obrigatório. PERCENTUAL: digite como porcentagem (4% ou 4 numa célula já formatada em %; nunca 0,04 num campo sem formato). Números sem separador de milhar e com ponto decimal quando digitados fora do Excel. CAMPO COM VÁRIAS UNIDADES: há uma linha por unidade — preencha UMA só e deixe as outras em branco; o Excel não converte uma na outra. Listas (produtos, custos…) têm vagas numeradas; vaga totalmente em branco = sem item. Meses: 0 = mês da data de início do projeto.</t>
+          <t>Como preencher: só as células AMARELAS da coluna B. Cinza-claro com valor em negrito = fixo do tipo de estudo (não editar); cinza com itálico = calculado pelo Excel, só para conferir (não editar). * = obrigatório. PERCENTUAL: digite como porcentagem (4% ou 4 numa célula já formatada em %). O Excel guarda 0,04; a API do app espera pontos (4) e o importador converte pelo FORMATO da célula — por isso não troque o formato das células. Números sem separador de milhar e com ponto decimal quando digitados fora do Excel. CAMPO COM VÁRIAS UNIDADES: há uma linha por unidade — preencha UMA só e deixe as outras em branco; o Excel não converte uma na outra. Listas (produtos, custos…) têm vagas numeradas; vaga totalmente em branco = sem item. Meses: 0 = mês da data de início do projeto.</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[1].nome (tipo = cronograma)</t>
+          <t>fases[1].nome</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[1].inicio_mes</t>
+          <t>fases[1].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[1].duracao_meses</t>
+          <t>fases[1].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[2].nome (tipo = cronograma)</t>
+          <t>fases[2].nome</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[2].inicio_mes</t>
+          <t>fases[2].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[2].duracao_meses</t>
+          <t>fases[2].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[3].nome (tipo = cronograma)</t>
+          <t>fases[3].nome</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[3].inicio_mes</t>
+          <t>fases[3].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[3].duracao_meses</t>
+          <t>fases[3].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[4].nome (tipo = cronograma)</t>
+          <t>fases[4].nome</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[4].inicio_mes</t>
+          <t>fases[4].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[4].duracao_meses</t>
+          <t>fases[4].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[5].nome (tipo = cronograma)</t>
+          <t>fases[5].nome</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[5].inicio_mes</t>
+          <t>fases[5].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[5].duracao_meses</t>
+          <t>fases[5].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[1].nome</t>
+          <t>tipologias[1].nome</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[1].area_privativa_m2</t>
+          <t>tipologias[1].area_privativa_m2</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[1].area_privativa_aberta_m2</t>
+          <t>tipologias[1].area_privativa_aberta_m2</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[1].quantidade</t>
+          <t>tipologias[1].quantidade</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[1].preco_m2</t>
+          <t>tipologias[1].preco_m2</t>
         </is>
       </c>
     </row>
@@ -1693,7 +1693,7 @@
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[2].nome</t>
+          <t>tipologias[2].nome</t>
         </is>
       </c>
     </row>
@@ -1713,7 +1713,7 @@
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[2].area_privativa_m2</t>
+          <t>tipologias[2].area_privativa_m2</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[2].area_privativa_aberta_m2</t>
+          <t>tipologias[2].area_privativa_aberta_m2</t>
         </is>
       </c>
     </row>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[2].quantidade</t>
+          <t>tipologias[2].quantidade</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[2].preco_m2</t>
+          <t>tipologias[2].preco_m2</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[3].nome</t>
+          <t>tipologias[3].nome</t>
         </is>
       </c>
     </row>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[3].area_privativa_m2</t>
+          <t>tipologias[3].area_privativa_m2</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[3].area_privativa_aberta_m2</t>
+          <t>tipologias[3].area_privativa_aberta_m2</t>
         </is>
       </c>
     </row>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[3].quantidade</t>
+          <t>tipologias[3].quantidade</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[3].preco_m2</t>
+          <t>tipologias[3].preco_m2</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[4].nome</t>
+          <t>tipologias[4].nome</t>
         </is>
       </c>
     </row>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[4].area_privativa_m2</t>
+          <t>tipologias[4].area_privativa_m2</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[4].area_privativa_aberta_m2</t>
+          <t>tipologias[4].area_privativa_aberta_m2</t>
         </is>
       </c>
     </row>
@@ -1971,7 +1971,7 @@
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[4].quantidade</t>
+          <t>tipologias[4].quantidade</t>
         </is>
       </c>
     </row>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[4].preco_m2</t>
+          <t>tipologias[4].preco_m2</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[5].nome</t>
+          <t>tipologias[5].nome</t>
         </is>
       </c>
     </row>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[5].area_privativa_m2</t>
+          <t>tipologias[5].area_privativa_m2</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[5].area_privativa_aberta_m2</t>
+          <t>tipologias[5].area_privativa_aberta_m2</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2070,7 @@
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[5].quantidade</t>
+          <t>tipologias[5].quantidade</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[5].preco_m2</t>
+          <t>tipologias[5].preco_m2</t>
         </is>
       </c>
     </row>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="D88" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[6].nome</t>
+          <t>tipologias[6].nome</t>
         </is>
       </c>
     </row>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[6].area_privativa_m2</t>
+          <t>tipologias[6].area_privativa_m2</t>
         </is>
       </c>
     </row>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="D90" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[6].area_privativa_aberta_m2</t>
+          <t>tipologias[6].area_privativa_aberta_m2</t>
         </is>
       </c>
     </row>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[6].quantidade</t>
+          <t>tipologias[6].quantidade</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[6].preco_m2</t>
+          <t>tipologias[6].preco_m2</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[7].nome</t>
+          <t>tipologias[7].nome</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[7].area_privativa_m2</t>
+          <t>tipologias[7].area_privativa_m2</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[7].area_privativa_aberta_m2</t>
+          <t>tipologias[7].area_privativa_aberta_m2</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[7].quantidade</t>
+          <t>tipologias[7].quantidade</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[7].preco_m2</t>
+          <t>tipologias[7].preco_m2</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[8].nome</t>
+          <t>tipologias[8].nome</t>
         </is>
       </c>
     </row>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[8].area_privativa_m2</t>
+          <t>tipologias[8].area_privativa_m2</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[8].area_privativa_aberta_m2</t>
+          <t>tipologias[8].area_privativa_aberta_m2</t>
         </is>
       </c>
     </row>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[8].quantidade</t>
+          <t>tipologias[8].quantidade</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
       </c>
       <c r="D104" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[8].preco_m2</t>
+          <t>tipologias[8].preco_m2</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="D106" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[9].nome</t>
+          <t>tipologias[9].nome</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="D107" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[9].area_privativa_m2</t>
+          <t>tipologias[9].area_privativa_m2</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="D108" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[9].area_privativa_aberta_m2</t>
+          <t>tipologias[9].area_privativa_aberta_m2</t>
         </is>
       </c>
     </row>
@@ -2458,7 +2458,7 @@
       </c>
       <c r="D109" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[9].quantidade</t>
+          <t>tipologias[9].quantidade</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="D110" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[9].preco_m2</t>
+          <t>tipologias[9].preco_m2</t>
         </is>
       </c>
     </row>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="D112" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[10].nome</t>
+          <t>tipologias[10].nome</t>
         </is>
       </c>
     </row>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="D113" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[10].area_privativa_m2</t>
+          <t>tipologias[10].area_privativa_m2</t>
         </is>
       </c>
     </row>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="D114" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[10].area_privativa_aberta_m2</t>
+          <t>tipologias[10].area_privativa_aberta_m2</t>
         </is>
       </c>
     </row>
@@ -2555,7 +2555,7 @@
       </c>
       <c r="D115" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[10].quantidade</t>
+          <t>tipologias[10].quantidade</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="D116" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[10].preco_m2</t>
+          <t>tipologias[10].preco_m2</t>
         </is>
       </c>
     </row>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="D120" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[1].nome (tipo = receita)</t>
+          <t>grupos[1].nome</t>
         </is>
       </c>
     </row>
@@ -2634,7 +2634,7 @@
       </c>
       <c r="D121" s="8" t="inlineStr">
         <is>
-          <t>absorcao.blocos[pre_lancamento].pct</t>
+          <t>grupos[1].pre_lancamento_pct</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="D122" s="8" t="inlineStr">
         <is>
-          <t>absorcao.blocos[lancamento].pct</t>
+          <t>grupos[1].lancamento_pct</t>
         </is>
       </c>
     </row>
@@ -2674,7 +2674,7 @@
       </c>
       <c r="D123" s="8" t="inlineStr">
         <is>
-          <t>absorcao.blocos[obra].pct</t>
+          <t>grupos[1].obra_pct</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="D124" s="8" t="inlineStr">
         <is>
-          <t>absorcao.pos_chaves_meses</t>
+          <t>grupos[1].pos_chaves_meses</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="D125" s="8" t="inlineStr">
         <is>
-          <t>absorcao.correcao_estoque</t>
+          <t>grupos[1].correcao_estoque</t>
         </is>
       </c>
     </row>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="D126" s="8" t="inlineStr">
         <is>
-          <t>fluxo_pagamento.residuoAteMarco</t>
+          <t>grupos[1].residuo_sem_prazo</t>
         </is>
       </c>
     </row>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="D128" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[2].nome (tipo = receita)</t>
+          <t>grupos[2].nome</t>
         </is>
       </c>
     </row>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="D129" s="8" t="inlineStr">
         <is>
-          <t>absorcao.blocos[pre_lancamento].pct</t>
+          <t>grupos[2].pre_lancamento_pct</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
-          <t>absorcao.blocos[lancamento].pct</t>
+          <t>grupos[2].lancamento_pct</t>
         </is>
       </c>
     </row>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="D131" s="8" t="inlineStr">
         <is>
-          <t>absorcao.blocos[obra].pct</t>
+          <t>grupos[2].obra_pct</t>
         </is>
       </c>
     </row>
@@ -2845,7 +2845,7 @@
       </c>
       <c r="D132" s="8" t="inlineStr">
         <is>
-          <t>absorcao.pos_chaves_meses</t>
+          <t>grupos[2].pos_chaves_meses</t>
         </is>
       </c>
     </row>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="D133" s="8" t="inlineStr">
         <is>
-          <t>absorcao.correcao_estoque</t>
+          <t>grupos[2].correcao_estoque</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="D134" s="8" t="inlineStr">
         <is>
-          <t>fluxo_pagamento.residuoAteMarco</t>
+          <t>grupos[2].residuo_sem_prazo</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="D136" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[3].nome (tipo = receita)</t>
+          <t>grupos[3].nome</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="D137" s="8" t="inlineStr">
         <is>
-          <t>absorcao.blocos[pre_lancamento].pct</t>
+          <t>grupos[3].pre_lancamento_pct</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="D138" s="8" t="inlineStr">
         <is>
-          <t>absorcao.blocos[lancamento].pct</t>
+          <t>grupos[3].lancamento_pct</t>
         </is>
       </c>
     </row>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="D139" s="8" t="inlineStr">
         <is>
-          <t>absorcao.blocos[obra].pct</t>
+          <t>grupos[3].obra_pct</t>
         </is>
       </c>
     </row>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="D140" s="8" t="inlineStr">
         <is>
-          <t>absorcao.pos_chaves_meses</t>
+          <t>grupos[3].pos_chaves_meses</t>
         </is>
       </c>
     </row>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="D141" s="8" t="inlineStr">
         <is>
-          <t>absorcao.correcao_estoque</t>
+          <t>grupos[3].correcao_estoque</t>
         </is>
       </c>
     </row>
@@ -3022,7 +3022,7 @@
       </c>
       <c r="D142" s="8" t="inlineStr">
         <is>
-          <t>fluxo_pagamento.residuoAteMarco</t>
+          <t>grupos[3].residuo_sem_prazo</t>
         </is>
       </c>
     </row>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="D144" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[4].nome (tipo = receita)</t>
+          <t>grupos[4].nome</t>
         </is>
       </c>
     </row>
@@ -3065,7 +3065,7 @@
       </c>
       <c r="D145" s="8" t="inlineStr">
         <is>
-          <t>absorcao.blocos[pre_lancamento].pct</t>
+          <t>grupos[4].pre_lancamento_pct</t>
         </is>
       </c>
     </row>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="D146" s="8" t="inlineStr">
         <is>
-          <t>absorcao.blocos[lancamento].pct</t>
+          <t>grupos[4].lancamento_pct</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="D147" s="8" t="inlineStr">
         <is>
-          <t>absorcao.blocos[obra].pct</t>
+          <t>grupos[4].obra_pct</t>
         </is>
       </c>
     </row>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="D148" s="8" t="inlineStr">
         <is>
-          <t>absorcao.pos_chaves_meses</t>
+          <t>grupos[4].pos_chaves_meses</t>
         </is>
       </c>
     </row>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="D149" s="8" t="inlineStr">
         <is>
-          <t>absorcao.correcao_estoque</t>
+          <t>grupos[4].correcao_estoque</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="D150" s="8" t="inlineStr">
         <is>
-          <t>fluxo_pagamento.residuoAteMarco</t>
+          <t>grupos[4].residuo_sem_prazo</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="D152" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[5].nome (tipo = receita)</t>
+          <t>grupos[5].nome</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="D153" s="8" t="inlineStr">
         <is>
-          <t>absorcao.blocos[pre_lancamento].pct</t>
+          <t>grupos[5].pre_lancamento_pct</t>
         </is>
       </c>
     </row>
@@ -3216,7 +3216,7 @@
       </c>
       <c r="D154" s="8" t="inlineStr">
         <is>
-          <t>absorcao.blocos[lancamento].pct</t>
+          <t>grupos[5].lancamento_pct</t>
         </is>
       </c>
     </row>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="D155" s="8" t="inlineStr">
         <is>
-          <t>absorcao.blocos[obra].pct</t>
+          <t>grupos[5].obra_pct</t>
         </is>
       </c>
     </row>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="D156" s="8" t="inlineStr">
         <is>
-          <t>absorcao.pos_chaves_meses</t>
+          <t>grupos[5].pos_chaves_meses</t>
         </is>
       </c>
     </row>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="D157" s="8" t="inlineStr">
         <is>
-          <t>absorcao.correcao_estoque</t>
+          <t>grupos[5].correcao_estoque</t>
         </is>
       </c>
     </row>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="D158" s="8" t="inlineStr">
         <is>
-          <t>fluxo_pagamento.residuoAteMarco</t>
+          <t>grupos[5].residuo_sem_prazo</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="D162" s="8" t="inlineStr">
         <is>
-          <t>fluxo_pagamento[1].grupo</t>
+          <t>pagamento[1].grupo</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="D163" s="8" t="inlineStr">
         <is>
-          <t>entrada[i] / parcelas[i] #1</t>
+          <t>pagamento[1].linha</t>
         </is>
       </c>
     </row>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="D164" s="8" t="inlineStr">
         <is>
-          <t>pct #1</t>
+          <t>pagamento[1].pct</t>
         </is>
       </c>
     </row>
@@ -3393,7 +3393,7 @@
       </c>
       <c r="D165" s="8" t="inlineStr">
         <is>
-          <t>parcelas #1</t>
+          <t>pagamento[1].parcelas</t>
         </is>
       </c>
     </row>
@@ -3413,7 +3413,7 @@
       </c>
       <c r="D166" s="8" t="inlineStr">
         <is>
-          <t>entrada[i].descontoPct #1</t>
+          <t>pagamento[1].desconto_pct</t>
         </is>
       </c>
     </row>
@@ -3431,7 +3431,7 @@
       </c>
       <c r="D167" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].sinalPct #1</t>
+          <t>pagamento[1].sinal_pct</t>
         </is>
       </c>
     </row>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="D168" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].ao_longo_obra #1</t>
+          <t>pagamento[1].ao_longo_obra</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="D170" s="8" t="inlineStr">
         <is>
-          <t>fluxo_pagamento[2].grupo</t>
+          <t>pagamento[2].grupo</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3500,7 @@
       </c>
       <c r="D171" s="8" t="inlineStr">
         <is>
-          <t>entrada[i] / parcelas[i] #2</t>
+          <t>pagamento[2].linha</t>
         </is>
       </c>
     </row>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="D172" s="8" t="inlineStr">
         <is>
-          <t>pct #2</t>
+          <t>pagamento[2].pct</t>
         </is>
       </c>
     </row>
@@ -3540,7 +3540,7 @@
       </c>
       <c r="D173" s="8" t="inlineStr">
         <is>
-          <t>parcelas #2</t>
+          <t>pagamento[2].parcelas</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="D174" s="8" t="inlineStr">
         <is>
-          <t>entrada[i].descontoPct #2</t>
+          <t>pagamento[2].desconto_pct</t>
         </is>
       </c>
     </row>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="D175" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].sinalPct #2</t>
+          <t>pagamento[2].sinal_pct</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="D176" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].ao_longo_obra #2</t>
+          <t>pagamento[2].ao_longo_obra</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="D178" s="8" t="inlineStr">
         <is>
-          <t>fluxo_pagamento[3].grupo</t>
+          <t>pagamento[3].grupo</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="D179" s="8" t="inlineStr">
         <is>
-          <t>entrada[i] / parcelas[i] #3</t>
+          <t>pagamento[3].linha</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="D180" s="8" t="inlineStr">
         <is>
-          <t>pct #3</t>
+          <t>pagamento[3].pct</t>
         </is>
       </c>
     </row>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="D181" s="8" t="inlineStr">
         <is>
-          <t>parcelas #3</t>
+          <t>pagamento[3].parcelas</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="D182" s="8" t="inlineStr">
         <is>
-          <t>entrada[i].descontoPct #3</t>
+          <t>pagamento[3].desconto_pct</t>
         </is>
       </c>
     </row>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="D183" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].sinalPct #3</t>
+          <t>pagamento[3].sinal_pct</t>
         </is>
       </c>
     </row>
@@ -3747,7 +3747,7 @@
       </c>
       <c r="D184" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].ao_longo_obra #3</t>
+          <t>pagamento[3].ao_longo_obra</t>
         </is>
       </c>
     </row>
@@ -3776,7 +3776,7 @@
       </c>
       <c r="D186" s="8" t="inlineStr">
         <is>
-          <t>fluxo_pagamento[4].grupo</t>
+          <t>pagamento[4].grupo</t>
         </is>
       </c>
     </row>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="D187" s="8" t="inlineStr">
         <is>
-          <t>entrada[i] / parcelas[i] #4</t>
+          <t>pagamento[4].linha</t>
         </is>
       </c>
     </row>
@@ -3818,7 +3818,7 @@
       </c>
       <c r="D188" s="8" t="inlineStr">
         <is>
-          <t>pct #4</t>
+          <t>pagamento[4].pct</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="D189" s="8" t="inlineStr">
         <is>
-          <t>parcelas #4</t>
+          <t>pagamento[4].parcelas</t>
         </is>
       </c>
     </row>
@@ -3856,7 +3856,7 @@
       </c>
       <c r="D190" s="8" t="inlineStr">
         <is>
-          <t>entrada[i].descontoPct #4</t>
+          <t>pagamento[4].desconto_pct</t>
         </is>
       </c>
     </row>
@@ -3876,7 +3876,7 @@
       </c>
       <c r="D191" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].sinalPct #4</t>
+          <t>pagamento[4].sinal_pct</t>
         </is>
       </c>
     </row>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="D192" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].ao_longo_obra #4</t>
+          <t>pagamento[4].ao_longo_obra</t>
         </is>
       </c>
     </row>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="D194" s="8" t="inlineStr">
         <is>
-          <t>fluxo_pagamento[5].grupo</t>
+          <t>pagamento[5].grupo</t>
         </is>
       </c>
     </row>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="D195" s="8" t="inlineStr">
         <is>
-          <t>entrada[i] / parcelas[i] #5</t>
+          <t>pagamento[5].linha</t>
         </is>
       </c>
     </row>
@@ -3959,7 +3959,7 @@
       </c>
       <c r="D196" s="8" t="inlineStr">
         <is>
-          <t>pct #5</t>
+          <t>pagamento[5].pct</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="D197" s="8" t="inlineStr">
         <is>
-          <t>parcelas #5</t>
+          <t>pagamento[5].parcelas</t>
         </is>
       </c>
     </row>
@@ -3995,7 +3995,7 @@
       </c>
       <c r="D198" s="8" t="inlineStr">
         <is>
-          <t>entrada[i].descontoPct #5</t>
+          <t>pagamento[5].desconto_pct</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="D199" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].sinalPct #5</t>
+          <t>pagamento[5].sinal_pct</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="D200" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].ao_longo_obra #5</t>
+          <t>pagamento[5].ao_longo_obra</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="D202" s="8" t="inlineStr">
         <is>
-          <t>fluxo_pagamento[6].grupo</t>
+          <t>pagamento[6].grupo</t>
         </is>
       </c>
     </row>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="D203" s="8" t="inlineStr">
         <is>
-          <t>entrada[i] / parcelas[i] #6</t>
+          <t>pagamento[6].linha</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="D204" s="8" t="inlineStr">
         <is>
-          <t>pct #6</t>
+          <t>pagamento[6].pct</t>
         </is>
       </c>
     </row>
@@ -4110,7 +4110,7 @@
       </c>
       <c r="D205" s="8" t="inlineStr">
         <is>
-          <t>parcelas #6</t>
+          <t>pagamento[6].parcelas</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="D206" s="8" t="inlineStr">
         <is>
-          <t>entrada[i].descontoPct #6</t>
+          <t>pagamento[6].desconto_pct</t>
         </is>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="D207" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].sinalPct #6</t>
+          <t>pagamento[6].sinal_pct</t>
         </is>
       </c>
     </row>
@@ -4164,7 +4164,7 @@
       </c>
       <c r="D208" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].ao_longo_obra #6</t>
+          <t>pagamento[6].ao_longo_obra</t>
         </is>
       </c>
     </row>
@@ -4189,7 +4189,7 @@
       </c>
       <c r="D210" s="8" t="inlineStr">
         <is>
-          <t>fluxo_pagamento[7].grupo</t>
+          <t>pagamento[7].grupo</t>
         </is>
       </c>
     </row>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="D211" s="8" t="inlineStr">
         <is>
-          <t>entrada[i] / parcelas[i] #7</t>
+          <t>pagamento[7].linha</t>
         </is>
       </c>
     </row>
@@ -4225,7 +4225,7 @@
       </c>
       <c r="D212" s="8" t="inlineStr">
         <is>
-          <t>pct #7</t>
+          <t>pagamento[7].pct</t>
         </is>
       </c>
     </row>
@@ -4243,7 +4243,7 @@
       </c>
       <c r="D213" s="8" t="inlineStr">
         <is>
-          <t>parcelas #7</t>
+          <t>pagamento[7].parcelas</t>
         </is>
       </c>
     </row>
@@ -4261,7 +4261,7 @@
       </c>
       <c r="D214" s="8" t="inlineStr">
         <is>
-          <t>entrada[i].descontoPct #7</t>
+          <t>pagamento[7].desconto_pct</t>
         </is>
       </c>
     </row>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="D215" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].sinalPct #7</t>
+          <t>pagamento[7].sinal_pct</t>
         </is>
       </c>
     </row>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="D216" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].ao_longo_obra #7</t>
+          <t>pagamento[7].ao_longo_obra</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="D218" s="8" t="inlineStr">
         <is>
-          <t>fluxo_pagamento[8].grupo</t>
+          <t>pagamento[8].grupo</t>
         </is>
       </c>
     </row>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="D219" s="8" t="inlineStr">
         <is>
-          <t>entrada[i] / parcelas[i] #8</t>
+          <t>pagamento[8].linha</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="D220" s="8" t="inlineStr">
         <is>
-          <t>pct #8</t>
+          <t>pagamento[8].pct</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="D221" s="8" t="inlineStr">
         <is>
-          <t>parcelas #8</t>
+          <t>pagamento[8].parcelas</t>
         </is>
       </c>
     </row>
@@ -4394,7 +4394,7 @@
       </c>
       <c r="D222" s="8" t="inlineStr">
         <is>
-          <t>entrada[i].descontoPct #8</t>
+          <t>pagamento[8].desconto_pct</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="D223" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].sinalPct #8</t>
+          <t>pagamento[8].sinal_pct</t>
         </is>
       </c>
     </row>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="D224" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].ao_longo_obra #8</t>
+          <t>pagamento[8].ao_longo_obra</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="D226" s="8" t="inlineStr">
         <is>
-          <t>fluxo_pagamento[9].grupo</t>
+          <t>pagamento[9].grupo</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="D227" s="8" t="inlineStr">
         <is>
-          <t>entrada[i] / parcelas[i] #9</t>
+          <t>pagamento[9].linha</t>
         </is>
       </c>
     </row>
@@ -4491,7 +4491,7 @@
       </c>
       <c r="D228" s="8" t="inlineStr">
         <is>
-          <t>pct #9</t>
+          <t>pagamento[9].pct</t>
         </is>
       </c>
     </row>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="D229" s="8" t="inlineStr">
         <is>
-          <t>parcelas #9</t>
+          <t>pagamento[9].parcelas</t>
         </is>
       </c>
     </row>
@@ -4527,7 +4527,7 @@
       </c>
       <c r="D230" s="8" t="inlineStr">
         <is>
-          <t>entrada[i].descontoPct #9</t>
+          <t>pagamento[9].desconto_pct</t>
         </is>
       </c>
     </row>
@@ -4545,7 +4545,7 @@
       </c>
       <c r="D231" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].sinalPct #9</t>
+          <t>pagamento[9].sinal_pct</t>
         </is>
       </c>
     </row>
@@ -4563,7 +4563,7 @@
       </c>
       <c r="D232" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].ao_longo_obra #9</t>
+          <t>pagamento[9].ao_longo_obra</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="D234" s="8" t="inlineStr">
         <is>
-          <t>fluxo_pagamento[10].grupo</t>
+          <t>pagamento[10].grupo</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="D235" s="8" t="inlineStr">
         <is>
-          <t>entrada[i] / parcelas[i] #10</t>
+          <t>pagamento[10].linha</t>
         </is>
       </c>
     </row>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="D236" s="8" t="inlineStr">
         <is>
-          <t>pct #10</t>
+          <t>pagamento[10].pct</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="D237" s="8" t="inlineStr">
         <is>
-          <t>parcelas #10</t>
+          <t>pagamento[10].parcelas</t>
         </is>
       </c>
     </row>
@@ -4660,7 +4660,7 @@
       </c>
       <c r="D238" s="8" t="inlineStr">
         <is>
-          <t>entrada[i].descontoPct #10</t>
+          <t>pagamento[10].desconto_pct</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="D239" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].sinalPct #10</t>
+          <t>pagamento[10].sinal_pct</t>
         </is>
       </c>
     </row>
@@ -4696,7 +4696,7 @@
       </c>
       <c r="D240" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].ao_longo_obra #10</t>
+          <t>pagamento[10].ao_longo_obra</t>
         </is>
       </c>
     </row>
@@ -4732,7 +4732,7 @@
       </c>
       <c r="D243" s="8" t="inlineStr">
         <is>
-          <t>alocacao[1].fase_id</t>
+          <t>alocacoes[1].grupo</t>
         </is>
       </c>
     </row>
@@ -4754,7 +4754,7 @@
       </c>
       <c r="D244" s="8" t="inlineStr">
         <is>
-          <t>alocacao[1].tipologia_id</t>
+          <t>alocacoes[1].tipologia</t>
         </is>
       </c>
     </row>
@@ -4774,7 +4774,7 @@
       </c>
       <c r="D245" s="8" t="inlineStr">
         <is>
-          <t>alocacao[1].unidades</t>
+          <t>alocacoes[1].unidades</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="D246" s="8" t="inlineStr">
         <is>
-          <t>alocacao[1].preco_m2</t>
+          <t>alocacoes[1].preco_m2</t>
         </is>
       </c>
     </row>
@@ -4823,7 +4823,7 @@
       </c>
       <c r="D248" s="8" t="inlineStr">
         <is>
-          <t>alocacao[2].fase_id</t>
+          <t>alocacoes[2].grupo</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="D249" s="8" t="inlineStr">
         <is>
-          <t>alocacao[2].tipologia_id</t>
+          <t>alocacoes[2].tipologia</t>
         </is>
       </c>
     </row>
@@ -4865,7 +4865,7 @@
       </c>
       <c r="D250" s="8" t="inlineStr">
         <is>
-          <t>alocacao[2].unidades</t>
+          <t>alocacoes[2].unidades</t>
         </is>
       </c>
     </row>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="D251" s="8" t="inlineStr">
         <is>
-          <t>alocacao[2].preco_m2</t>
+          <t>alocacoes[2].preco_m2</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="D253" s="8" t="inlineStr">
         <is>
-          <t>alocacao[3].fase_id</t>
+          <t>alocacoes[3].grupo</t>
         </is>
       </c>
     </row>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="D254" s="8" t="inlineStr">
         <is>
-          <t>alocacao[3].tipologia_id</t>
+          <t>alocacoes[3].tipologia</t>
         </is>
       </c>
     </row>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="D255" s="8" t="inlineStr">
         <is>
-          <t>alocacao[3].unidades</t>
+          <t>alocacoes[3].unidades</t>
         </is>
       </c>
     </row>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="D256" s="8" t="inlineStr">
         <is>
-          <t>alocacao[3].preco_m2</t>
+          <t>alocacoes[3].preco_m2</t>
         </is>
       </c>
     </row>
@@ -5005,7 +5005,7 @@
       </c>
       <c r="D258" s="8" t="inlineStr">
         <is>
-          <t>alocacao[4].fase_id</t>
+          <t>alocacoes[4].grupo</t>
         </is>
       </c>
     </row>
@@ -5027,7 +5027,7 @@
       </c>
       <c r="D259" s="8" t="inlineStr">
         <is>
-          <t>alocacao[4].tipologia_id</t>
+          <t>alocacoes[4].tipologia</t>
         </is>
       </c>
     </row>
@@ -5047,7 +5047,7 @@
       </c>
       <c r="D260" s="8" t="inlineStr">
         <is>
-          <t>alocacao[4].unidades</t>
+          <t>alocacoes[4].unidades</t>
         </is>
       </c>
     </row>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="D261" s="8" t="inlineStr">
         <is>
-          <t>alocacao[4].preco_m2</t>
+          <t>alocacoes[4].preco_m2</t>
         </is>
       </c>
     </row>
@@ -5096,7 +5096,7 @@
       </c>
       <c r="D263" s="8" t="inlineStr">
         <is>
-          <t>alocacao[5].fase_id</t>
+          <t>alocacoes[5].grupo</t>
         </is>
       </c>
     </row>
@@ -5118,7 +5118,7 @@
       </c>
       <c r="D264" s="8" t="inlineStr">
         <is>
-          <t>alocacao[5].tipologia_id</t>
+          <t>alocacoes[5].tipologia</t>
         </is>
       </c>
     </row>
@@ -5138,7 +5138,7 @@
       </c>
       <c r="D265" s="8" t="inlineStr">
         <is>
-          <t>alocacao[5].unidades</t>
+          <t>alocacoes[5].unidades</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="D266" s="8" t="inlineStr">
         <is>
-          <t>alocacao[5].preco_m2</t>
+          <t>alocacoes[5].preco_m2</t>
         </is>
       </c>
     </row>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="D268" s="8" t="inlineStr">
         <is>
-          <t>alocacao[6].fase_id</t>
+          <t>alocacoes[6].grupo</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="D269" s="8" t="inlineStr">
         <is>
-          <t>alocacao[6].tipologia_id</t>
+          <t>alocacoes[6].tipologia</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="D270" s="8" t="inlineStr">
         <is>
-          <t>alocacao[6].unidades</t>
+          <t>alocacoes[6].unidades</t>
         </is>
       </c>
     </row>
@@ -5237,7 +5237,7 @@
       </c>
       <c r="D271" s="8" t="inlineStr">
         <is>
-          <t>alocacao[6].preco_m2</t>
+          <t>alocacoes[6].preco_m2</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="D273" s="8" t="inlineStr">
         <is>
-          <t>alocacao[7].fase_id</t>
+          <t>alocacoes[7].grupo</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="D274" s="8" t="inlineStr">
         <is>
-          <t>alocacao[7].tipologia_id</t>
+          <t>alocacoes[7].tipologia</t>
         </is>
       </c>
     </row>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="D275" s="8" t="inlineStr">
         <is>
-          <t>alocacao[7].unidades</t>
+          <t>alocacoes[7].unidades</t>
         </is>
       </c>
     </row>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="D276" s="8" t="inlineStr">
         <is>
-          <t>alocacao[7].preco_m2</t>
+          <t>alocacoes[7].preco_m2</t>
         </is>
       </c>
     </row>
@@ -5341,7 +5341,7 @@
       </c>
       <c r="D278" s="8" t="inlineStr">
         <is>
-          <t>alocacao[8].fase_id</t>
+          <t>alocacoes[8].grupo</t>
         </is>
       </c>
     </row>
@@ -5359,7 +5359,7 @@
       </c>
       <c r="D279" s="8" t="inlineStr">
         <is>
-          <t>alocacao[8].tipologia_id</t>
+          <t>alocacoes[8].tipologia</t>
         </is>
       </c>
     </row>
@@ -5377,7 +5377,7 @@
       </c>
       <c r="D280" s="8" t="inlineStr">
         <is>
-          <t>alocacao[8].unidades</t>
+          <t>alocacoes[8].unidades</t>
         </is>
       </c>
     </row>
@@ -5395,7 +5395,7 @@
       </c>
       <c r="D281" s="8" t="inlineStr">
         <is>
-          <t>alocacao[8].preco_m2</t>
+          <t>alocacoes[8].preco_m2</t>
         </is>
       </c>
     </row>
@@ -5420,7 +5420,7 @@
       </c>
       <c r="D283" s="8" t="inlineStr">
         <is>
-          <t>alocacao[9].fase_id</t>
+          <t>alocacoes[9].grupo</t>
         </is>
       </c>
     </row>
@@ -5438,7 +5438,7 @@
       </c>
       <c r="D284" s="8" t="inlineStr">
         <is>
-          <t>alocacao[9].tipologia_id</t>
+          <t>alocacoes[9].tipologia</t>
         </is>
       </c>
     </row>
@@ -5456,7 +5456,7 @@
       </c>
       <c r="D285" s="8" t="inlineStr">
         <is>
-          <t>alocacao[9].unidades</t>
+          <t>alocacoes[9].unidades</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="D286" s="8" t="inlineStr">
         <is>
-          <t>alocacao[9].preco_m2</t>
+          <t>alocacoes[9].preco_m2</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="D288" s="8" t="inlineStr">
         <is>
-          <t>alocacao[10].fase_id</t>
+          <t>alocacoes[10].grupo</t>
         </is>
       </c>
     </row>
@@ -5517,7 +5517,7 @@
       </c>
       <c r="D289" s="8" t="inlineStr">
         <is>
-          <t>alocacao[10].tipologia_id</t>
+          <t>alocacoes[10].tipologia</t>
         </is>
       </c>
     </row>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="D290" s="8" t="inlineStr">
         <is>
-          <t>alocacao[10].unidades</t>
+          <t>alocacoes[10].unidades</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="D291" s="8" t="inlineStr">
         <is>
-          <t>alocacao[10].preco_m2</t>
+          <t>alocacoes[10].preco_m2</t>
         </is>
       </c>
     </row>
@@ -5603,7 +5603,7 @@
       </c>
       <c r="D296" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[1].grupo</t>
+          <t>custos[1].grupo</t>
         </is>
       </c>
     </row>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="D297" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[1].categoria</t>
+          <t>custos[1].categoria</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="D298" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[1].subcategoria</t>
+          <t>custos[1].subcategoria</t>
         </is>
       </c>
     </row>
@@ -5669,7 +5669,7 @@
       </c>
       <c r="D299" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[1].orcamento_unidade</t>
+          <t>custos[1].unidade</t>
         </is>
       </c>
     </row>
@@ -5688,7 +5688,7 @@
       </c>
       <c r="D300" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[1].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[1].valor_rs</t>
         </is>
       </c>
     </row>
@@ -5705,7 +5705,7 @@
       </c>
       <c r="D301" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[1].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[1].valor_pct</t>
         </is>
       </c>
     </row>
@@ -5722,12 +5722,12 @@
       </c>
       <c r="C302" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D302" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[1].curva_id / distribuicao_modo</t>
+          <t>custos[1].distribuicao</t>
         </is>
       </c>
     </row>
@@ -5749,7 +5749,7 @@
       </c>
       <c r="D303" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[1].cronograma_evento / fase_ancora_id</t>
+          <t>custos[1].cronograma</t>
         </is>
       </c>
     </row>
@@ -5769,7 +5769,7 @@
       </c>
       <c r="D304" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[1].inicio_mes</t>
+          <t>custos[1].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -5789,7 +5789,7 @@
       </c>
       <c r="D305" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[1].duracao_meses</t>
+          <t>custos[1].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -5818,7 +5818,7 @@
       </c>
       <c r="D307" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[2].grupo</t>
+          <t>custos[2].grupo</t>
         </is>
       </c>
     </row>
@@ -5840,7 +5840,7 @@
       </c>
       <c r="D308" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[2].categoria</t>
+          <t>custos[2].categoria</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D309" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[2].subcategoria</t>
+          <t>custos[2].subcategoria</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D310" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[2].orcamento_unidade</t>
+          <t>custos[2].unidade</t>
         </is>
       </c>
     </row>
@@ -5899,7 +5899,7 @@
       </c>
       <c r="D311" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[2].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[2].valor_rs</t>
         </is>
       </c>
     </row>
@@ -5916,7 +5916,7 @@
       </c>
       <c r="D312" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[2].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[2].valor_pct</t>
         </is>
       </c>
     </row>
@@ -5933,12 +5933,12 @@
       </c>
       <c r="C313" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D313" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[2].curva_id / distribuicao_modo</t>
+          <t>custos[2].distribuicao</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="D314" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[2].cronograma_evento / fase_ancora_id</t>
+          <t>custos[2].cronograma</t>
         </is>
       </c>
     </row>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="D315" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[2].inicio_mes</t>
+          <t>custos[2].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="D316" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[2].duracao_meses</t>
+          <t>custos[2].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -6025,7 +6025,7 @@
       </c>
       <c r="D318" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[3].grupo</t>
+          <t>custos[3].grupo</t>
         </is>
       </c>
     </row>
@@ -6047,7 +6047,7 @@
       </c>
       <c r="D319" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[3].categoria</t>
+          <t>custos[3].categoria</t>
         </is>
       </c>
     </row>
@@ -6065,7 +6065,7 @@
       </c>
       <c r="D320" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[3].subcategoria</t>
+          <t>custos[3].subcategoria</t>
         </is>
       </c>
     </row>
@@ -6087,7 +6087,7 @@
       </c>
       <c r="D321" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[3].orcamento_unidade</t>
+          <t>custos[3].unidade</t>
         </is>
       </c>
     </row>
@@ -6104,7 +6104,7 @@
       </c>
       <c r="D322" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[3].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[3].valor_rs</t>
         </is>
       </c>
     </row>
@@ -6123,7 +6123,7 @@
       </c>
       <c r="D323" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[3].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[3].valor_pct</t>
         </is>
       </c>
     </row>
@@ -6136,12 +6136,12 @@
       <c r="B324" s="6" t="n"/>
       <c r="C324" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D324" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[3].curva_id / distribuicao_modo</t>
+          <t>custos[3].distribuicao</t>
         </is>
       </c>
     </row>
@@ -6159,7 +6159,7 @@
       </c>
       <c r="D325" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[3].cronograma_evento / fase_ancora_id</t>
+          <t>custos[3].cronograma</t>
         </is>
       </c>
     </row>
@@ -6177,7 +6177,7 @@
       </c>
       <c r="D326" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[3].inicio_mes</t>
+          <t>custos[3].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -6195,7 +6195,7 @@
       </c>
       <c r="D327" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[3].duracao_meses</t>
+          <t>custos[3].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="D329" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[4].grupo</t>
+          <t>custos[4].grupo</t>
         </is>
       </c>
     </row>
@@ -6246,7 +6246,7 @@
       </c>
       <c r="D330" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[4].categoria</t>
+          <t>custos[4].categoria</t>
         </is>
       </c>
     </row>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="D331" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[4].subcategoria</t>
+          <t>custos[4].subcategoria</t>
         </is>
       </c>
     </row>
@@ -6286,7 +6286,7 @@
       </c>
       <c r="D332" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[4].orcamento_unidade</t>
+          <t>custos[4].unidade</t>
         </is>
       </c>
     </row>
@@ -6303,7 +6303,7 @@
       </c>
       <c r="D333" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[4].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[4].valor_rs</t>
         </is>
       </c>
     </row>
@@ -6322,7 +6322,7 @@
       </c>
       <c r="D334" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[4].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[4].valor_pct</t>
         </is>
       </c>
     </row>
@@ -6339,12 +6339,12 @@
       </c>
       <c r="C335" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D335" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[4].curva_id / distribuicao_modo</t>
+          <t>custos[4].distribuicao</t>
         </is>
       </c>
     </row>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="D336" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[4].cronograma_evento / fase_ancora_id</t>
+          <t>custos[4].cronograma</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6386,7 @@
       </c>
       <c r="D337" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[4].inicio_mes</t>
+          <t>custos[4].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -6406,7 +6406,7 @@
       </c>
       <c r="D338" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[4].duracao_meses</t>
+          <t>custos[4].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -6435,7 +6435,7 @@
       </c>
       <c r="D340" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[5].grupo</t>
+          <t>custos[5].grupo</t>
         </is>
       </c>
     </row>
@@ -6457,7 +6457,7 @@
       </c>
       <c r="D341" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[5].categoria</t>
+          <t>custos[5].categoria</t>
         </is>
       </c>
     </row>
@@ -6475,7 +6475,7 @@
       </c>
       <c r="D342" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[5].subcategoria</t>
+          <t>custos[5].subcategoria</t>
         </is>
       </c>
     </row>
@@ -6497,7 +6497,7 @@
       </c>
       <c r="D343" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[5].orcamento_unidade</t>
+          <t>custos[5].unidade</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="D344" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[5].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[5].valor_rs</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="D345" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[5].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[5].valor_pct</t>
         </is>
       </c>
     </row>
@@ -6550,12 +6550,12 @@
       </c>
       <c r="C346" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D346" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[5].curva_id / distribuicao_modo</t>
+          <t>custos[5].distribuicao</t>
         </is>
       </c>
     </row>
@@ -6577,7 +6577,7 @@
       </c>
       <c r="D347" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[5].cronograma_evento / fase_ancora_id</t>
+          <t>custos[5].cronograma</t>
         </is>
       </c>
     </row>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="D348" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[5].inicio_mes</t>
+          <t>custos[5].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -6613,7 +6613,7 @@
       </c>
       <c r="D349" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[5].duracao_meses</t>
+          <t>custos[5].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="D351" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[6].grupo</t>
+          <t>custos[6].grupo</t>
         </is>
       </c>
     </row>
@@ -6664,7 +6664,7 @@
       </c>
       <c r="D352" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[6].categoria</t>
+          <t>custos[6].categoria</t>
         </is>
       </c>
     </row>
@@ -6682,7 +6682,7 @@
       </c>
       <c r="D353" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[6].subcategoria</t>
+          <t>custos[6].subcategoria</t>
         </is>
       </c>
     </row>
@@ -6704,7 +6704,7 @@
       </c>
       <c r="D354" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[6].orcamento_unidade</t>
+          <t>custos[6].unidade</t>
         </is>
       </c>
     </row>
@@ -6723,7 +6723,7 @@
       </c>
       <c r="D355" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[6].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[6].valor_rs</t>
         </is>
       </c>
     </row>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="D356" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[6].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[6].valor_pct</t>
         </is>
       </c>
     </row>
@@ -6757,12 +6757,12 @@
       </c>
       <c r="C357" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D357" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[6].curva_id / distribuicao_modo</t>
+          <t>custos[6].distribuicao</t>
         </is>
       </c>
     </row>
@@ -6784,7 +6784,7 @@
       </c>
       <c r="D358" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[6].cronograma_evento / fase_ancora_id</t>
+          <t>custos[6].cronograma</t>
         </is>
       </c>
     </row>
@@ -6802,7 +6802,7 @@
       </c>
       <c r="D359" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[6].inicio_mes</t>
+          <t>custos[6].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -6820,7 +6820,7 @@
       </c>
       <c r="D360" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[6].duracao_meses</t>
+          <t>custos[6].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -6849,7 +6849,7 @@
       </c>
       <c r="D362" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[7].grupo</t>
+          <t>custos[7].grupo</t>
         </is>
       </c>
     </row>
@@ -6871,7 +6871,7 @@
       </c>
       <c r="D363" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[7].categoria</t>
+          <t>custos[7].categoria</t>
         </is>
       </c>
     </row>
@@ -6889,7 +6889,7 @@
       </c>
       <c r="D364" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[7].subcategoria</t>
+          <t>custos[7].subcategoria</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
       </c>
       <c r="D365" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[7].orcamento_unidade</t>
+          <t>custos[7].unidade</t>
         </is>
       </c>
     </row>
@@ -6928,7 +6928,7 @@
       </c>
       <c r="D366" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[7].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[7].valor_rs</t>
         </is>
       </c>
     </row>
@@ -6947,7 +6947,7 @@
       </c>
       <c r="D367" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[7].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[7].valor_pct</t>
         </is>
       </c>
     </row>
@@ -6964,12 +6964,12 @@
       </c>
       <c r="C368" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D368" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[7].curva_id / distribuicao_modo</t>
+          <t>custos[7].distribuicao</t>
         </is>
       </c>
     </row>
@@ -6991,7 +6991,7 @@
       </c>
       <c r="D369" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[7].cronograma_evento / fase_ancora_id</t>
+          <t>custos[7].cronograma</t>
         </is>
       </c>
     </row>
@@ -7011,7 +7011,7 @@
       </c>
       <c r="D370" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[7].inicio_mes</t>
+          <t>custos[7].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -7031,7 +7031,7 @@
       </c>
       <c r="D371" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[7].duracao_meses</t>
+          <t>custos[7].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -7060,7 +7060,7 @@
       </c>
       <c r="D373" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[8].grupo</t>
+          <t>custos[8].grupo</t>
         </is>
       </c>
     </row>
@@ -7082,7 +7082,7 @@
       </c>
       <c r="D374" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[8].categoria</t>
+          <t>custos[8].categoria</t>
         </is>
       </c>
     </row>
@@ -7100,7 +7100,7 @@
       </c>
       <c r="D375" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[8].subcategoria</t>
+          <t>custos[8].subcategoria</t>
         </is>
       </c>
     </row>
@@ -7122,7 +7122,7 @@
       </c>
       <c r="D376" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[8].orcamento_unidade</t>
+          <t>custos[8].unidade</t>
         </is>
       </c>
     </row>
@@ -7139,7 +7139,7 @@
       </c>
       <c r="D377" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[8].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[8].valor_rs</t>
         </is>
       </c>
     </row>
@@ -7158,7 +7158,7 @@
       </c>
       <c r="D378" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[8].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[8].valor_pct</t>
         </is>
       </c>
     </row>
@@ -7175,12 +7175,12 @@
       </c>
       <c r="C379" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D379" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[8].curva_id / distribuicao_modo</t>
+          <t>custos[8].distribuicao</t>
         </is>
       </c>
     </row>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="D380" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[8].cronograma_evento / fase_ancora_id</t>
+          <t>custos[8].cronograma</t>
         </is>
       </c>
     </row>
@@ -7220,7 +7220,7 @@
       </c>
       <c r="D381" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[8].inicio_mes</t>
+          <t>custos[8].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="D382" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[8].duracao_meses</t>
+          <t>custos[8].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -7267,7 +7267,7 @@
       </c>
       <c r="D384" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[9].grupo</t>
+          <t>custos[9].grupo</t>
         </is>
       </c>
     </row>
@@ -7289,7 +7289,7 @@
       </c>
       <c r="D385" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[9].categoria</t>
+          <t>custos[9].categoria</t>
         </is>
       </c>
     </row>
@@ -7307,7 +7307,7 @@
       </c>
       <c r="D386" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[9].subcategoria</t>
+          <t>custos[9].subcategoria</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="D387" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[9].orcamento_unidade</t>
+          <t>custos[9].unidade</t>
         </is>
       </c>
     </row>
@@ -7346,7 +7346,7 @@
       </c>
       <c r="D388" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[9].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[9].valor_rs</t>
         </is>
       </c>
     </row>
@@ -7365,7 +7365,7 @@
       </c>
       <c r="D389" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[9].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[9].valor_pct</t>
         </is>
       </c>
     </row>
@@ -7382,12 +7382,12 @@
       </c>
       <c r="C390" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D390" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[9].curva_id / distribuicao_modo</t>
+          <t>custos[9].distribuicao</t>
         </is>
       </c>
     </row>
@@ -7409,7 +7409,7 @@
       </c>
       <c r="D391" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[9].cronograma_evento / fase_ancora_id</t>
+          <t>custos[9].cronograma</t>
         </is>
       </c>
     </row>
@@ -7427,7 +7427,7 @@
       </c>
       <c r="D392" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[9].inicio_mes</t>
+          <t>custos[9].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -7445,7 +7445,7 @@
       </c>
       <c r="D393" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[9].duracao_meses</t>
+          <t>custos[9].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="D395" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[10].grupo</t>
+          <t>custos[10].grupo</t>
         </is>
       </c>
     </row>
@@ -7488,7 +7488,7 @@
       </c>
       <c r="D396" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[10].categoria</t>
+          <t>custos[10].categoria</t>
         </is>
       </c>
     </row>
@@ -7506,7 +7506,7 @@
       </c>
       <c r="D397" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[10].subcategoria</t>
+          <t>custos[10].subcategoria</t>
         </is>
       </c>
     </row>
@@ -7524,7 +7524,7 @@
       </c>
       <c r="D398" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[10].orcamento_unidade</t>
+          <t>custos[10].unidade</t>
         </is>
       </c>
     </row>
@@ -7541,7 +7541,7 @@
       </c>
       <c r="D399" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[10].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[10].valor_rs</t>
         </is>
       </c>
     </row>
@@ -7558,7 +7558,7 @@
       </c>
       <c r="D400" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[10].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[10].valor_pct</t>
         </is>
       </c>
     </row>
@@ -7571,12 +7571,12 @@
       <c r="B401" s="6" t="n"/>
       <c r="C401" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D401" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[10].curva_id / distribuicao_modo</t>
+          <t>custos[10].distribuicao</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="D402" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[10].cronograma_evento / fase_ancora_id</t>
+          <t>custos[10].cronograma</t>
         </is>
       </c>
     </row>
@@ -7612,7 +7612,7 @@
       </c>
       <c r="D403" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[10].inicio_mes</t>
+          <t>custos[10].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -7630,7 +7630,7 @@
       </c>
       <c r="D404" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[10].duracao_meses</t>
+          <t>custos[10].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -7655,7 +7655,7 @@
       </c>
       <c r="D406" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[11].grupo</t>
+          <t>custos[11].grupo</t>
         </is>
       </c>
     </row>
@@ -7673,7 +7673,7 @@
       </c>
       <c r="D407" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[11].categoria</t>
+          <t>custos[11].categoria</t>
         </is>
       </c>
     </row>
@@ -7691,7 +7691,7 @@
       </c>
       <c r="D408" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[11].subcategoria</t>
+          <t>custos[11].subcategoria</t>
         </is>
       </c>
     </row>
@@ -7709,7 +7709,7 @@
       </c>
       <c r="D409" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[11].orcamento_unidade</t>
+          <t>custos[11].unidade</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7726,7 @@
       </c>
       <c r="D410" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[11].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[11].valor_rs</t>
         </is>
       </c>
     </row>
@@ -7743,7 +7743,7 @@
       </c>
       <c r="D411" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[11].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[11].valor_pct</t>
         </is>
       </c>
     </row>
@@ -7756,12 +7756,12 @@
       <c r="B412" s="6" t="n"/>
       <c r="C412" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D412" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[11].curva_id / distribuicao_modo</t>
+          <t>custos[11].distribuicao</t>
         </is>
       </c>
     </row>
@@ -7779,7 +7779,7 @@
       </c>
       <c r="D413" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[11].cronograma_evento / fase_ancora_id</t>
+          <t>custos[11].cronograma</t>
         </is>
       </c>
     </row>
@@ -7797,7 +7797,7 @@
       </c>
       <c r="D414" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[11].inicio_mes</t>
+          <t>custos[11].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -7815,7 +7815,7 @@
       </c>
       <c r="D415" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[11].duracao_meses</t>
+          <t>custos[11].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -7840,7 +7840,7 @@
       </c>
       <c r="D417" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[12].grupo</t>
+          <t>custos[12].grupo</t>
         </is>
       </c>
     </row>
@@ -7858,7 +7858,7 @@
       </c>
       <c r="D418" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[12].categoria</t>
+          <t>custos[12].categoria</t>
         </is>
       </c>
     </row>
@@ -7876,7 +7876,7 @@
       </c>
       <c r="D419" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[12].subcategoria</t>
+          <t>custos[12].subcategoria</t>
         </is>
       </c>
     </row>
@@ -7894,7 +7894,7 @@
       </c>
       <c r="D420" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[12].orcamento_unidade</t>
+          <t>custos[12].unidade</t>
         </is>
       </c>
     </row>
@@ -7911,7 +7911,7 @@
       </c>
       <c r="D421" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[12].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[12].valor_rs</t>
         </is>
       </c>
     </row>
@@ -7928,7 +7928,7 @@
       </c>
       <c r="D422" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[12].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[12].valor_pct</t>
         </is>
       </c>
     </row>
@@ -7941,12 +7941,12 @@
       <c r="B423" s="6" t="n"/>
       <c r="C423" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D423" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[12].curva_id / distribuicao_modo</t>
+          <t>custos[12].distribuicao</t>
         </is>
       </c>
     </row>
@@ -7964,7 +7964,7 @@
       </c>
       <c r="D424" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[12].cronograma_evento / fase_ancora_id</t>
+          <t>custos[12].cronograma</t>
         </is>
       </c>
     </row>
@@ -7982,7 +7982,7 @@
       </c>
       <c r="D425" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[12].inicio_mes</t>
+          <t>custos[12].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="D426" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[12].duracao_meses</t>
+          <t>custos[12].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -8025,7 +8025,7 @@
       </c>
       <c r="D428" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[13].grupo</t>
+          <t>custos[13].grupo</t>
         </is>
       </c>
     </row>
@@ -8043,7 +8043,7 @@
       </c>
       <c r="D429" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[13].categoria</t>
+          <t>custos[13].categoria</t>
         </is>
       </c>
     </row>
@@ -8061,7 +8061,7 @@
       </c>
       <c r="D430" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[13].subcategoria</t>
+          <t>custos[13].subcategoria</t>
         </is>
       </c>
     </row>
@@ -8079,7 +8079,7 @@
       </c>
       <c r="D431" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[13].orcamento_unidade</t>
+          <t>custos[13].unidade</t>
         </is>
       </c>
     </row>
@@ -8096,7 +8096,7 @@
       </c>
       <c r="D432" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[13].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[13].valor_rs</t>
         </is>
       </c>
     </row>
@@ -8113,7 +8113,7 @@
       </c>
       <c r="D433" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[13].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[13].valor_pct</t>
         </is>
       </c>
     </row>
@@ -8126,12 +8126,12 @@
       <c r="B434" s="6" t="n"/>
       <c r="C434" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D434" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[13].curva_id / distribuicao_modo</t>
+          <t>custos[13].distribuicao</t>
         </is>
       </c>
     </row>
@@ -8149,7 +8149,7 @@
       </c>
       <c r="D435" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[13].cronograma_evento / fase_ancora_id</t>
+          <t>custos[13].cronograma</t>
         </is>
       </c>
     </row>
@@ -8167,7 +8167,7 @@
       </c>
       <c r="D436" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[13].inicio_mes</t>
+          <t>custos[13].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -8185,7 +8185,7 @@
       </c>
       <c r="D437" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[13].duracao_meses</t>
+          <t>custos[13].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -8210,7 +8210,7 @@
       </c>
       <c r="D439" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[14].grupo</t>
+          <t>custos[14].grupo</t>
         </is>
       </c>
     </row>
@@ -8228,7 +8228,7 @@
       </c>
       <c r="D440" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[14].categoria</t>
+          <t>custos[14].categoria</t>
         </is>
       </c>
     </row>
@@ -8246,7 +8246,7 @@
       </c>
       <c r="D441" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[14].subcategoria</t>
+          <t>custos[14].subcategoria</t>
         </is>
       </c>
     </row>
@@ -8264,7 +8264,7 @@
       </c>
       <c r="D442" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[14].orcamento_unidade</t>
+          <t>custos[14].unidade</t>
         </is>
       </c>
     </row>
@@ -8281,7 +8281,7 @@
       </c>
       <c r="D443" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[14].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[14].valor_rs</t>
         </is>
       </c>
     </row>
@@ -8298,7 +8298,7 @@
       </c>
       <c r="D444" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[14].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[14].valor_pct</t>
         </is>
       </c>
     </row>
@@ -8311,12 +8311,12 @@
       <c r="B445" s="6" t="n"/>
       <c r="C445" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D445" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[14].curva_id / distribuicao_modo</t>
+          <t>custos[14].distribuicao</t>
         </is>
       </c>
     </row>
@@ -8334,7 +8334,7 @@
       </c>
       <c r="D446" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[14].cronograma_evento / fase_ancora_id</t>
+          <t>custos[14].cronograma</t>
         </is>
       </c>
     </row>
@@ -8352,7 +8352,7 @@
       </c>
       <c r="D447" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[14].inicio_mes</t>
+          <t>custos[14].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -8370,7 +8370,7 @@
       </c>
       <c r="D448" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[14].duracao_meses</t>
+          <t>custos[14].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -8395,7 +8395,7 @@
       </c>
       <c r="D450" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[15].grupo</t>
+          <t>custos[15].grupo</t>
         </is>
       </c>
     </row>
@@ -8413,7 +8413,7 @@
       </c>
       <c r="D451" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[15].categoria</t>
+          <t>custos[15].categoria</t>
         </is>
       </c>
     </row>
@@ -8431,7 +8431,7 @@
       </c>
       <c r="D452" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[15].subcategoria</t>
+          <t>custos[15].subcategoria</t>
         </is>
       </c>
     </row>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="D453" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[15].orcamento_unidade</t>
+          <t>custos[15].unidade</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="D454" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[15].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[15].valor_rs</t>
         </is>
       </c>
     </row>
@@ -8483,7 +8483,7 @@
       </c>
       <c r="D455" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[15].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[15].valor_pct</t>
         </is>
       </c>
     </row>
@@ -8496,12 +8496,12 @@
       <c r="B456" s="6" t="n"/>
       <c r="C456" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D456" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[15].curva_id / distribuicao_modo</t>
+          <t>custos[15].distribuicao</t>
         </is>
       </c>
     </row>
@@ -8519,7 +8519,7 @@
       </c>
       <c r="D457" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[15].cronograma_evento / fase_ancora_id</t>
+          <t>custos[15].cronograma</t>
         </is>
       </c>
     </row>
@@ -8537,7 +8537,7 @@
       </c>
       <c r="D458" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[15].inicio_mes</t>
+          <t>custos[15].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -8555,7 +8555,7 @@
       </c>
       <c r="D459" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[15].duracao_meses</t>
+          <t>custos[15].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -8580,7 +8580,7 @@
       </c>
       <c r="D461" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[16].grupo</t>
+          <t>custos[16].grupo</t>
         </is>
       </c>
     </row>
@@ -8598,7 +8598,7 @@
       </c>
       <c r="D462" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[16].categoria</t>
+          <t>custos[16].categoria</t>
         </is>
       </c>
     </row>
@@ -8616,7 +8616,7 @@
       </c>
       <c r="D463" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[16].subcategoria</t>
+          <t>custos[16].subcategoria</t>
         </is>
       </c>
     </row>
@@ -8634,7 +8634,7 @@
       </c>
       <c r="D464" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[16].orcamento_unidade</t>
+          <t>custos[16].unidade</t>
         </is>
       </c>
     </row>
@@ -8651,7 +8651,7 @@
       </c>
       <c r="D465" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[16].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[16].valor_rs</t>
         </is>
       </c>
     </row>
@@ -8668,7 +8668,7 @@
       </c>
       <c r="D466" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[16].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[16].valor_pct</t>
         </is>
       </c>
     </row>
@@ -8681,12 +8681,12 @@
       <c r="B467" s="6" t="n"/>
       <c r="C467" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D467" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[16].curva_id / distribuicao_modo</t>
+          <t>custos[16].distribuicao</t>
         </is>
       </c>
     </row>
@@ -8704,7 +8704,7 @@
       </c>
       <c r="D468" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[16].cronograma_evento / fase_ancora_id</t>
+          <t>custos[16].cronograma</t>
         </is>
       </c>
     </row>
@@ -8722,7 +8722,7 @@
       </c>
       <c r="D469" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[16].inicio_mes</t>
+          <t>custos[16].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -8740,7 +8740,7 @@
       </c>
       <c r="D470" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[16].duracao_meses</t>
+          <t>custos[16].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -8765,7 +8765,7 @@
       </c>
       <c r="D472" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[17].grupo</t>
+          <t>custos[17].grupo</t>
         </is>
       </c>
     </row>
@@ -8783,7 +8783,7 @@
       </c>
       <c r="D473" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[17].categoria</t>
+          <t>custos[17].categoria</t>
         </is>
       </c>
     </row>
@@ -8801,7 +8801,7 @@
       </c>
       <c r="D474" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[17].subcategoria</t>
+          <t>custos[17].subcategoria</t>
         </is>
       </c>
     </row>
@@ -8819,7 +8819,7 @@
       </c>
       <c r="D475" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[17].orcamento_unidade</t>
+          <t>custos[17].unidade</t>
         </is>
       </c>
     </row>
@@ -8836,7 +8836,7 @@
       </c>
       <c r="D476" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[17].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[17].valor_rs</t>
         </is>
       </c>
     </row>
@@ -8853,7 +8853,7 @@
       </c>
       <c r="D477" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[17].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[17].valor_pct</t>
         </is>
       </c>
     </row>
@@ -8866,12 +8866,12 @@
       <c r="B478" s="6" t="n"/>
       <c r="C478" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D478" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[17].curva_id / distribuicao_modo</t>
+          <t>custos[17].distribuicao</t>
         </is>
       </c>
     </row>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="D479" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[17].cronograma_evento / fase_ancora_id</t>
+          <t>custos[17].cronograma</t>
         </is>
       </c>
     </row>
@@ -8907,7 +8907,7 @@
       </c>
       <c r="D480" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[17].inicio_mes</t>
+          <t>custos[17].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -8925,7 +8925,7 @@
       </c>
       <c r="D481" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[17].duracao_meses</t>
+          <t>custos[17].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -8950,7 +8950,7 @@
       </c>
       <c r="D483" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[18].grupo</t>
+          <t>custos[18].grupo</t>
         </is>
       </c>
     </row>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="D484" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[18].categoria</t>
+          <t>custos[18].categoria</t>
         </is>
       </c>
     </row>
@@ -8986,7 +8986,7 @@
       </c>
       <c r="D485" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[18].subcategoria</t>
+          <t>custos[18].subcategoria</t>
         </is>
       </c>
     </row>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="D486" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[18].orcamento_unidade</t>
+          <t>custos[18].unidade</t>
         </is>
       </c>
     </row>
@@ -9021,7 +9021,7 @@
       </c>
       <c r="D487" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[18].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[18].valor_rs</t>
         </is>
       </c>
     </row>
@@ -9038,7 +9038,7 @@
       </c>
       <c r="D488" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[18].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[18].valor_pct</t>
         </is>
       </c>
     </row>
@@ -9051,12 +9051,12 @@
       <c r="B489" s="6" t="n"/>
       <c r="C489" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D489" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[18].curva_id / distribuicao_modo</t>
+          <t>custos[18].distribuicao</t>
         </is>
       </c>
     </row>
@@ -9074,7 +9074,7 @@
       </c>
       <c r="D490" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[18].cronograma_evento / fase_ancora_id</t>
+          <t>custos[18].cronograma</t>
         </is>
       </c>
     </row>
@@ -9092,7 +9092,7 @@
       </c>
       <c r="D491" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[18].inicio_mes</t>
+          <t>custos[18].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="D492" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[18].duracao_meses</t>
+          <t>custos[18].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -9135,7 +9135,7 @@
       </c>
       <c r="D494" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[19].grupo</t>
+          <t>custos[19].grupo</t>
         </is>
       </c>
     </row>
@@ -9153,7 +9153,7 @@
       </c>
       <c r="D495" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[19].categoria</t>
+          <t>custos[19].categoria</t>
         </is>
       </c>
     </row>
@@ -9171,7 +9171,7 @@
       </c>
       <c r="D496" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[19].subcategoria</t>
+          <t>custos[19].subcategoria</t>
         </is>
       </c>
     </row>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="D497" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[19].orcamento_unidade</t>
+          <t>custos[19].unidade</t>
         </is>
       </c>
     </row>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="D498" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[19].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[19].valor_rs</t>
         </is>
       </c>
     </row>
@@ -9223,7 +9223,7 @@
       </c>
       <c r="D499" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[19].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[19].valor_pct</t>
         </is>
       </c>
     </row>
@@ -9236,12 +9236,12 @@
       <c r="B500" s="6" t="n"/>
       <c r="C500" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D500" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[19].curva_id / distribuicao_modo</t>
+          <t>custos[19].distribuicao</t>
         </is>
       </c>
     </row>
@@ -9259,7 +9259,7 @@
       </c>
       <c r="D501" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[19].cronograma_evento / fase_ancora_id</t>
+          <t>custos[19].cronograma</t>
         </is>
       </c>
     </row>
@@ -9277,7 +9277,7 @@
       </c>
       <c r="D502" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[19].inicio_mes</t>
+          <t>custos[19].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -9295,7 +9295,7 @@
       </c>
       <c r="D503" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[19].duracao_meses</t>
+          <t>custos[19].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -9320,7 +9320,7 @@
       </c>
       <c r="D505" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[20].grupo</t>
+          <t>custos[20].grupo</t>
         </is>
       </c>
     </row>
@@ -9338,7 +9338,7 @@
       </c>
       <c r="D506" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[20].categoria</t>
+          <t>custos[20].categoria</t>
         </is>
       </c>
     </row>
@@ -9356,7 +9356,7 @@
       </c>
       <c r="D507" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[20].subcategoria</t>
+          <t>custos[20].subcategoria</t>
         </is>
       </c>
     </row>
@@ -9374,7 +9374,7 @@
       </c>
       <c r="D508" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[20].orcamento_unidade</t>
+          <t>custos[20].unidade</t>
         </is>
       </c>
     </row>
@@ -9391,7 +9391,7 @@
       </c>
       <c r="D509" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[20].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[20].valor_rs</t>
         </is>
       </c>
     </row>
@@ -9408,7 +9408,7 @@
       </c>
       <c r="D510" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[20].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[20].valor_pct</t>
         </is>
       </c>
     </row>
@@ -9421,12 +9421,12 @@
       <c r="B511" s="6" t="n"/>
       <c r="C511" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D511" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[20].curva_id / distribuicao_modo</t>
+          <t>custos[20].distribuicao</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="D512" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[20].cronograma_evento / fase_ancora_id</t>
+          <t>custos[20].cronograma</t>
         </is>
       </c>
     </row>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="D513" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[20].inicio_mes</t>
+          <t>custos[20].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -9480,7 +9480,7 @@
       </c>
       <c r="D514" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[20].duracao_meses</t>
+          <t>custos[20].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -9505,7 +9505,7 @@
       </c>
       <c r="D516" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[21].grupo</t>
+          <t>custos[21].grupo</t>
         </is>
       </c>
     </row>
@@ -9523,7 +9523,7 @@
       </c>
       <c r="D517" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[21].categoria</t>
+          <t>custos[21].categoria</t>
         </is>
       </c>
     </row>
@@ -9541,7 +9541,7 @@
       </c>
       <c r="D518" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[21].subcategoria</t>
+          <t>custos[21].subcategoria</t>
         </is>
       </c>
     </row>
@@ -9559,7 +9559,7 @@
       </c>
       <c r="D519" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[21].orcamento_unidade</t>
+          <t>custos[21].unidade</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="D520" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[21].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[21].valor_rs</t>
         </is>
       </c>
     </row>
@@ -9593,7 +9593,7 @@
       </c>
       <c r="D521" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[21].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[21].valor_pct</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       <c r="B522" s="6" t="n"/>
       <c r="C522" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D522" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[21].curva_id / distribuicao_modo</t>
+          <t>custos[21].distribuicao</t>
         </is>
       </c>
     </row>
@@ -9629,7 +9629,7 @@
       </c>
       <c r="D523" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[21].cronograma_evento / fase_ancora_id</t>
+          <t>custos[21].cronograma</t>
         </is>
       </c>
     </row>
@@ -9647,7 +9647,7 @@
       </c>
       <c r="D524" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[21].inicio_mes</t>
+          <t>custos[21].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -9665,7 +9665,7 @@
       </c>
       <c r="D525" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[21].duracao_meses</t>
+          <t>custos[21].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -9690,7 +9690,7 @@
       </c>
       <c r="D527" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[22].grupo</t>
+          <t>custos[22].grupo</t>
         </is>
       </c>
     </row>
@@ -9708,7 +9708,7 @@
       </c>
       <c r="D528" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[22].categoria</t>
+          <t>custos[22].categoria</t>
         </is>
       </c>
     </row>
@@ -9726,7 +9726,7 @@
       </c>
       <c r="D529" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[22].subcategoria</t>
+          <t>custos[22].subcategoria</t>
         </is>
       </c>
     </row>
@@ -9744,7 +9744,7 @@
       </c>
       <c r="D530" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[22].orcamento_unidade</t>
+          <t>custos[22].unidade</t>
         </is>
       </c>
     </row>
@@ -9761,7 +9761,7 @@
       </c>
       <c r="D531" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[22].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[22].valor_rs</t>
         </is>
       </c>
     </row>
@@ -9778,7 +9778,7 @@
       </c>
       <c r="D532" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[22].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[22].valor_pct</t>
         </is>
       </c>
     </row>
@@ -9791,12 +9791,12 @@
       <c r="B533" s="6" t="n"/>
       <c r="C533" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D533" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[22].curva_id / distribuicao_modo</t>
+          <t>custos[22].distribuicao</t>
         </is>
       </c>
     </row>
@@ -9814,7 +9814,7 @@
       </c>
       <c r="D534" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[22].cronograma_evento / fase_ancora_id</t>
+          <t>custos[22].cronograma</t>
         </is>
       </c>
     </row>
@@ -9832,7 +9832,7 @@
       </c>
       <c r="D535" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[22].inicio_mes</t>
+          <t>custos[22].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -9850,7 +9850,7 @@
       </c>
       <c r="D536" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[22].duracao_meses</t>
+          <t>custos[22].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -9875,7 +9875,7 @@
       </c>
       <c r="D538" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[23].grupo</t>
+          <t>custos[23].grupo</t>
         </is>
       </c>
     </row>
@@ -9893,7 +9893,7 @@
       </c>
       <c r="D539" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[23].categoria</t>
+          <t>custos[23].categoria</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="D540" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[23].subcategoria</t>
+          <t>custos[23].subcategoria</t>
         </is>
       </c>
     </row>
@@ -9929,7 +9929,7 @@
       </c>
       <c r="D541" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[23].orcamento_unidade</t>
+          <t>custos[23].unidade</t>
         </is>
       </c>
     </row>
@@ -9946,7 +9946,7 @@
       </c>
       <c r="D542" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[23].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[23].valor_rs</t>
         </is>
       </c>
     </row>
@@ -9963,7 +9963,7 @@
       </c>
       <c r="D543" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[23].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[23].valor_pct</t>
         </is>
       </c>
     </row>
@@ -9976,12 +9976,12 @@
       <c r="B544" s="6" t="n"/>
       <c r="C544" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D544" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[23].curva_id / distribuicao_modo</t>
+          <t>custos[23].distribuicao</t>
         </is>
       </c>
     </row>
@@ -9999,7 +9999,7 @@
       </c>
       <c r="D545" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[23].cronograma_evento / fase_ancora_id</t>
+          <t>custos[23].cronograma</t>
         </is>
       </c>
     </row>
@@ -10017,7 +10017,7 @@
       </c>
       <c r="D546" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[23].inicio_mes</t>
+          <t>custos[23].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -10035,7 +10035,7 @@
       </c>
       <c r="D547" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[23].duracao_meses</t>
+          <t>custos[23].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -10060,7 +10060,7 @@
       </c>
       <c r="D549" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[24].grupo</t>
+          <t>custos[24].grupo</t>
         </is>
       </c>
     </row>
@@ -10078,7 +10078,7 @@
       </c>
       <c r="D550" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[24].categoria</t>
+          <t>custos[24].categoria</t>
         </is>
       </c>
     </row>
@@ -10096,7 +10096,7 @@
       </c>
       <c r="D551" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[24].subcategoria</t>
+          <t>custos[24].subcategoria</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="D552" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[24].orcamento_unidade</t>
+          <t>custos[24].unidade</t>
         </is>
       </c>
     </row>
@@ -10131,7 +10131,7 @@
       </c>
       <c r="D553" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[24].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[24].valor_rs</t>
         </is>
       </c>
     </row>
@@ -10148,7 +10148,7 @@
       </c>
       <c r="D554" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[24].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[24].valor_pct</t>
         </is>
       </c>
     </row>
@@ -10161,12 +10161,12 @@
       <c r="B555" s="6" t="n"/>
       <c r="C555" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D555" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[24].curva_id / distribuicao_modo</t>
+          <t>custos[24].distribuicao</t>
         </is>
       </c>
     </row>
@@ -10184,7 +10184,7 @@
       </c>
       <c r="D556" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[24].cronograma_evento / fase_ancora_id</t>
+          <t>custos[24].cronograma</t>
         </is>
       </c>
     </row>
@@ -10202,7 +10202,7 @@
       </c>
       <c r="D557" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[24].inicio_mes</t>
+          <t>custos[24].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -10220,7 +10220,7 @@
       </c>
       <c r="D558" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[24].duracao_meses</t>
+          <t>custos[24].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -10245,7 +10245,7 @@
       </c>
       <c r="D560" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[25].grupo</t>
+          <t>custos[25].grupo</t>
         </is>
       </c>
     </row>
@@ -10263,7 +10263,7 @@
       </c>
       <c r="D561" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[25].categoria</t>
+          <t>custos[25].categoria</t>
         </is>
       </c>
     </row>
@@ -10281,7 +10281,7 @@
       </c>
       <c r="D562" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[25].subcategoria</t>
+          <t>custos[25].subcategoria</t>
         </is>
       </c>
     </row>
@@ -10299,7 +10299,7 @@
       </c>
       <c r="D563" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[25].orcamento_unidade</t>
+          <t>custos[25].unidade</t>
         </is>
       </c>
     </row>
@@ -10316,7 +10316,7 @@
       </c>
       <c r="D564" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[25].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[25].valor_rs</t>
         </is>
       </c>
     </row>
@@ -10333,7 +10333,7 @@
       </c>
       <c r="D565" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[25].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[25].valor_pct</t>
         </is>
       </c>
     </row>
@@ -10346,12 +10346,12 @@
       <c r="B566" s="6" t="n"/>
       <c r="C566" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D566" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[25].curva_id / distribuicao_modo</t>
+          <t>custos[25].distribuicao</t>
         </is>
       </c>
     </row>
@@ -10369,7 +10369,7 @@
       </c>
       <c r="D567" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[25].cronograma_evento / fase_ancora_id</t>
+          <t>custos[25].cronograma</t>
         </is>
       </c>
     </row>
@@ -10387,7 +10387,7 @@
       </c>
       <c r="D568" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[25].inicio_mes</t>
+          <t>custos[25].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -10405,7 +10405,7 @@
       </c>
       <c r="D569" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[25].duracao_meses</t>
+          <t>custos[25].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -10430,7 +10430,7 @@
       </c>
       <c r="D571" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[26].grupo</t>
+          <t>custos[26].grupo</t>
         </is>
       </c>
     </row>
@@ -10448,7 +10448,7 @@
       </c>
       <c r="D572" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[26].categoria</t>
+          <t>custos[26].categoria</t>
         </is>
       </c>
     </row>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="D573" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[26].subcategoria</t>
+          <t>custos[26].subcategoria</t>
         </is>
       </c>
     </row>
@@ -10484,7 +10484,7 @@
       </c>
       <c r="D574" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[26].orcamento_unidade</t>
+          <t>custos[26].unidade</t>
         </is>
       </c>
     </row>
@@ -10501,7 +10501,7 @@
       </c>
       <c r="D575" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[26].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[26].valor_rs</t>
         </is>
       </c>
     </row>
@@ -10518,7 +10518,7 @@
       </c>
       <c r="D576" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[26].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[26].valor_pct</t>
         </is>
       </c>
     </row>
@@ -10531,12 +10531,12 @@
       <c r="B577" s="6" t="n"/>
       <c r="C577" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D577" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[26].curva_id / distribuicao_modo</t>
+          <t>custos[26].distribuicao</t>
         </is>
       </c>
     </row>
@@ -10554,7 +10554,7 @@
       </c>
       <c r="D578" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[26].cronograma_evento / fase_ancora_id</t>
+          <t>custos[26].cronograma</t>
         </is>
       </c>
     </row>
@@ -10572,7 +10572,7 @@
       </c>
       <c r="D579" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[26].inicio_mes</t>
+          <t>custos[26].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -10590,7 +10590,7 @@
       </c>
       <c r="D580" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[26].duracao_meses</t>
+          <t>custos[26].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -10615,7 +10615,7 @@
       </c>
       <c r="D582" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[27].grupo</t>
+          <t>custos[27].grupo</t>
         </is>
       </c>
     </row>
@@ -10633,7 +10633,7 @@
       </c>
       <c r="D583" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[27].categoria</t>
+          <t>custos[27].categoria</t>
         </is>
       </c>
     </row>
@@ -10651,7 +10651,7 @@
       </c>
       <c r="D584" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[27].subcategoria</t>
+          <t>custos[27].subcategoria</t>
         </is>
       </c>
     </row>
@@ -10669,7 +10669,7 @@
       </c>
       <c r="D585" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[27].orcamento_unidade</t>
+          <t>custos[27].unidade</t>
         </is>
       </c>
     </row>
@@ -10686,7 +10686,7 @@
       </c>
       <c r="D586" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[27].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[27].valor_rs</t>
         </is>
       </c>
     </row>
@@ -10703,7 +10703,7 @@
       </c>
       <c r="D587" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[27].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[27].valor_pct</t>
         </is>
       </c>
     </row>
@@ -10716,12 +10716,12 @@
       <c r="B588" s="6" t="n"/>
       <c r="C588" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D588" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[27].curva_id / distribuicao_modo</t>
+          <t>custos[27].distribuicao</t>
         </is>
       </c>
     </row>
@@ -10739,7 +10739,7 @@
       </c>
       <c r="D589" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[27].cronograma_evento / fase_ancora_id</t>
+          <t>custos[27].cronograma</t>
         </is>
       </c>
     </row>
@@ -10757,7 +10757,7 @@
       </c>
       <c r="D590" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[27].inicio_mes</t>
+          <t>custos[27].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -10775,7 +10775,7 @@
       </c>
       <c r="D591" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[27].duracao_meses</t>
+          <t>custos[27].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="D593" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[28].grupo</t>
+          <t>custos[28].grupo</t>
         </is>
       </c>
     </row>
@@ -10818,7 +10818,7 @@
       </c>
       <c r="D594" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[28].categoria</t>
+          <t>custos[28].categoria</t>
         </is>
       </c>
     </row>
@@ -10836,7 +10836,7 @@
       </c>
       <c r="D595" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[28].subcategoria</t>
+          <t>custos[28].subcategoria</t>
         </is>
       </c>
     </row>
@@ -10854,7 +10854,7 @@
       </c>
       <c r="D596" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[28].orcamento_unidade</t>
+          <t>custos[28].unidade</t>
         </is>
       </c>
     </row>
@@ -10871,7 +10871,7 @@
       </c>
       <c r="D597" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[28].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[28].valor_rs</t>
         </is>
       </c>
     </row>
@@ -10888,7 +10888,7 @@
       </c>
       <c r="D598" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[28].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[28].valor_pct</t>
         </is>
       </c>
     </row>
@@ -10901,12 +10901,12 @@
       <c r="B599" s="6" t="n"/>
       <c r="C599" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D599" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[28].curva_id / distribuicao_modo</t>
+          <t>custos[28].distribuicao</t>
         </is>
       </c>
     </row>
@@ -10924,7 +10924,7 @@
       </c>
       <c r="D600" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[28].cronograma_evento / fase_ancora_id</t>
+          <t>custos[28].cronograma</t>
         </is>
       </c>
     </row>
@@ -10942,7 +10942,7 @@
       </c>
       <c r="D601" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[28].inicio_mes</t>
+          <t>custos[28].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -10960,7 +10960,7 @@
       </c>
       <c r="D602" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[28].duracao_meses</t>
+          <t>custos[28].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="D604" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[permuta_fisica#1].permuta_tipologia_id</t>
+          <t>permuta_fisica[1].tipologia</t>
         </is>
       </c>
     </row>
@@ -11009,7 +11009,7 @@
       </c>
       <c r="D605" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[permuta_fisica#1].permuta_quantidade</t>
+          <t>permuta_fisica[1].unidades</t>
         </is>
       </c>
     </row>
@@ -11027,7 +11027,7 @@
       </c>
       <c r="D606" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[permuta_fisica#2].permuta_tipologia_id</t>
+          <t>permuta_fisica[2].tipologia</t>
         </is>
       </c>
     </row>
@@ -11045,7 +11045,7 @@
       </c>
       <c r="D607" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[permuta_fisica#2].permuta_quantidade</t>
+          <t>permuta_fisica[2].unidades</t>
         </is>
       </c>
     </row>
@@ -11074,7 +11074,7 @@
       </c>
       <c r="D609" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[permuta_financeira#1].orcamento_unidade</t>
+          <t>permuta_financeira[1].unidade</t>
         </is>
       </c>
     </row>
@@ -11092,7 +11092,7 @@
       </c>
       <c r="D610" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[permuta_financeira#1].orcamento_valor</t>
+          <t>permuta_financeira[1].valor_rs</t>
         </is>
       </c>
     </row>
@@ -11112,7 +11112,7 @@
       </c>
       <c r="D611" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[permuta_financeira#1].orcamento_valor</t>
+          <t>permuta_financeira[1].valor_pct</t>
         </is>
       </c>
     </row>
@@ -11134,7 +11134,7 @@
       </c>
       <c r="D612" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[permuta_financeira#1].permuta_financeira_deduzir_imposto</t>
+          <t>permuta_financeira[1].deduzir_imposto</t>
         </is>
       </c>
     </row>
@@ -11156,7 +11156,7 @@
       </c>
       <c r="D613" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[permuta_financeira#1].permuta_financeira_deduzir_corretagem</t>
+          <t>permuta_financeira[1].deduzir_corretagem</t>
         </is>
       </c>
     </row>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="D614" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[permuta_financeira#2].orcamento_unidade</t>
+          <t>permuta_financeira[2].unidade</t>
         </is>
       </c>
     </row>
@@ -11192,7 +11192,7 @@
       </c>
       <c r="D615" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[permuta_financeira#2].orcamento_valor</t>
+          <t>permuta_financeira[2].valor_rs</t>
         </is>
       </c>
     </row>
@@ -11210,7 +11210,7 @@
       </c>
       <c r="D616" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[permuta_financeira#2].orcamento_valor</t>
+          <t>permuta_financeira[2].valor_pct</t>
         </is>
       </c>
     </row>
@@ -11228,7 +11228,7 @@
       </c>
       <c r="D617" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[permuta_financeira#2].permuta_financeira_deduzir_imposto</t>
+          <t>permuta_financeira[2].deduzir_imposto</t>
         </is>
       </c>
     </row>
@@ -11246,7 +11246,7 @@
       </c>
       <c r="D618" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[permuta_financeira#2].permuta_financeira_deduzir_corretagem</t>
+          <t>permuta_financeira[2].deduzir_corretagem</t>
         </is>
       </c>
     </row>
@@ -11282,7 +11282,7 @@
       </c>
       <c r="D621" s="8" t="inlineStr">
         <is>
-          <t>funding[financiamento_producao].nome</t>
+          <t>funding.financiamento_producao.nome</t>
         </is>
       </c>
     </row>
@@ -11304,7 +11304,7 @@
       </c>
       <c r="D622" s="8" t="inlineStr">
         <is>
-          <t>funding[financiamento_producao].ativo</t>
+          <t>funding.financiamento_producao.ativo</t>
         </is>
       </c>
     </row>
@@ -11324,7 +11324,7 @@
       </c>
       <c r="D623" s="8" t="inlineStr">
         <is>
-          <t>funding[financiamento_producao].valor</t>
+          <t>funding.financiamento_producao.valor</t>
         </is>
       </c>
     </row>
@@ -11344,7 +11344,7 @@
       </c>
       <c r="D624" s="8" t="inlineStr">
         <is>
-          <t>funding[financiamento_producao].taxa_anual</t>
+          <t>funding.financiamento_producao.taxa_anual</t>
         </is>
       </c>
     </row>
@@ -11364,7 +11364,7 @@
       </c>
       <c r="D625" s="8" t="inlineStr">
         <is>
-          <t>funding[financiamento_producao].exposicao_minima</t>
+          <t>funding.financiamento_producao.exposicao_minima</t>
         </is>
       </c>
     </row>
@@ -11384,7 +11384,7 @@
       </c>
       <c r="D626" s="8" t="inlineStr">
         <is>
-          <t>funding[financiamento_producao].percentual_financiavel</t>
+          <t>funding.financiamento_producao.percentual_financiavel</t>
         </is>
       </c>
     </row>
@@ -11406,7 +11406,7 @@
       </c>
       <c r="D627" s="8" t="inlineStr">
         <is>
-          <t>funding[financiamento_producao].amortizar_com_caixa_disponivel</t>
+          <t>funding.financiamento_producao.amortizar_com_caixa_disponivel</t>
         </is>
       </c>
     </row>
@@ -11419,12 +11419,12 @@
       <c r="B628" s="6" t="n"/>
       <c r="C628" s="7" t="inlineStr">
         <is>
-          <t>linhas de custo (texto); vazio = padrão</t>
+          <t>linhas de custo separadas por ";" — Categoria ou Categoria / Subcategoria; vazio = padrão</t>
         </is>
       </c>
       <c r="D628" s="8" t="inlineStr">
         <is>
-          <t>funding[financiamento_producao].custo_linha_ids</t>
+          <t>funding.financiamento_producao.base_financiavel</t>
         </is>
       </c>
     </row>
@@ -11453,7 +11453,7 @@
       </c>
       <c r="D630" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#1].nome</t>
+          <t>funding.divida[1].nome</t>
         </is>
       </c>
     </row>
@@ -11473,7 +11473,7 @@
       </c>
       <c r="D631" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#1].valor</t>
+          <t>funding.divida[1].valor</t>
         </is>
       </c>
     </row>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="D632" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#1].cronograma_evento / fase_ancora_id</t>
+          <t>funding.divida[1].aporte</t>
         </is>
       </c>
     </row>
@@ -11513,7 +11513,7 @@
       </c>
       <c r="D633" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#1].inicio_mes</t>
+          <t>funding.divida[1].mes</t>
         </is>
       </c>
     </row>
@@ -11535,7 +11535,7 @@
       </c>
       <c r="D634" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#1].distribuir_aporte</t>
+          <t>funding.divida[1].distribuir_aporte</t>
         </is>
       </c>
     </row>
@@ -11555,7 +11555,7 @@
       </c>
       <c r="D635" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#1].aporte_meses</t>
+          <t>funding.divida[1].aporte_meses</t>
         </is>
       </c>
     </row>
@@ -11575,7 +11575,7 @@
       </c>
       <c r="D636" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#1].taxa_anual</t>
+          <t>funding.divida[1].taxa_anual</t>
         </is>
       </c>
     </row>
@@ -11595,7 +11595,7 @@
       </c>
       <c r="D637" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#1].periodo_amortizacao_meses</t>
+          <t>funding.divida[1].amortizacao_meses</t>
         </is>
       </c>
     </row>
@@ -11615,7 +11615,7 @@
       </c>
       <c r="D638" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#1].periodo_carencia_meses</t>
+          <t>funding.divida[1].carencia_meses</t>
         </is>
       </c>
     </row>
@@ -11635,7 +11635,7 @@
       </c>
       <c r="D639" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#1].taxa_estruturacao_pct</t>
+          <t>funding.divida[1].estruturacao_pct</t>
         </is>
       </c>
     </row>
@@ -11655,7 +11655,7 @@
       </c>
       <c r="D640" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#1].taxa_administracao_mensal</t>
+          <t>funding.divida[1].administracao_mensal</t>
         </is>
       </c>
     </row>
@@ -11675,7 +11675,7 @@
       </c>
       <c r="D641" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#1].outros_encargos_iniciais</t>
+          <t>funding.divida[1].outros_encargos</t>
         </is>
       </c>
     </row>
@@ -11700,7 +11700,7 @@
       </c>
       <c r="D643" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#2].nome</t>
+          <t>funding.divida[2].nome</t>
         </is>
       </c>
     </row>
@@ -11718,7 +11718,7 @@
       </c>
       <c r="D644" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#2].valor</t>
+          <t>funding.divida[2].valor</t>
         </is>
       </c>
     </row>
@@ -11736,7 +11736,7 @@
       </c>
       <c r="D645" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#2].cronograma_evento / fase_ancora_id</t>
+          <t>funding.divida[2].aporte</t>
         </is>
       </c>
     </row>
@@ -11754,7 +11754,7 @@
       </c>
       <c r="D646" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#2].inicio_mes</t>
+          <t>funding.divida[2].mes</t>
         </is>
       </c>
     </row>
@@ -11772,7 +11772,7 @@
       </c>
       <c r="D647" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#2].distribuir_aporte</t>
+          <t>funding.divida[2].distribuir_aporte</t>
         </is>
       </c>
     </row>
@@ -11790,7 +11790,7 @@
       </c>
       <c r="D648" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#2].aporte_meses</t>
+          <t>funding.divida[2].aporte_meses</t>
         </is>
       </c>
     </row>
@@ -11808,7 +11808,7 @@
       </c>
       <c r="D649" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#2].taxa_anual</t>
+          <t>funding.divida[2].taxa_anual</t>
         </is>
       </c>
     </row>
@@ -11826,7 +11826,7 @@
       </c>
       <c r="D650" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#2].periodo_amortizacao_meses</t>
+          <t>funding.divida[2].amortizacao_meses</t>
         </is>
       </c>
     </row>
@@ -11844,7 +11844,7 @@
       </c>
       <c r="D651" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#2].periodo_carencia_meses</t>
+          <t>funding.divida[2].carencia_meses</t>
         </is>
       </c>
     </row>
@@ -11862,7 +11862,7 @@
       </c>
       <c r="D652" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#2].taxa_estruturacao_pct</t>
+          <t>funding.divida[2].estruturacao_pct</t>
         </is>
       </c>
     </row>
@@ -11880,7 +11880,7 @@
       </c>
       <c r="D653" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#2].taxa_administracao_mensal</t>
+          <t>funding.divida[2].administracao_mensal</t>
         </is>
       </c>
     </row>
@@ -11898,7 +11898,7 @@
       </c>
       <c r="D654" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#2].outros_encargos_iniciais</t>
+          <t>funding.divida[2].outros_encargos</t>
         </is>
       </c>
     </row>
@@ -11923,7 +11923,7 @@
       </c>
       <c r="D656" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#3].nome</t>
+          <t>funding.divida[3].nome</t>
         </is>
       </c>
     </row>
@@ -11941,7 +11941,7 @@
       </c>
       <c r="D657" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#3].valor</t>
+          <t>funding.divida[3].valor</t>
         </is>
       </c>
     </row>
@@ -11959,7 +11959,7 @@
       </c>
       <c r="D658" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#3].cronograma_evento / fase_ancora_id</t>
+          <t>funding.divida[3].aporte</t>
         </is>
       </c>
     </row>
@@ -11977,7 +11977,7 @@
       </c>
       <c r="D659" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#3].inicio_mes</t>
+          <t>funding.divida[3].mes</t>
         </is>
       </c>
     </row>
@@ -11995,7 +11995,7 @@
       </c>
       <c r="D660" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#3].distribuir_aporte</t>
+          <t>funding.divida[3].distribuir_aporte</t>
         </is>
       </c>
     </row>
@@ -12013,7 +12013,7 @@
       </c>
       <c r="D661" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#3].aporte_meses</t>
+          <t>funding.divida[3].aporte_meses</t>
         </is>
       </c>
     </row>
@@ -12031,7 +12031,7 @@
       </c>
       <c r="D662" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#3].taxa_anual</t>
+          <t>funding.divida[3].taxa_anual</t>
         </is>
       </c>
     </row>
@@ -12049,7 +12049,7 @@
       </c>
       <c r="D663" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#3].periodo_amortizacao_meses</t>
+          <t>funding.divida[3].amortizacao_meses</t>
         </is>
       </c>
     </row>
@@ -12067,7 +12067,7 @@
       </c>
       <c r="D664" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#3].periodo_carencia_meses</t>
+          <t>funding.divida[3].carencia_meses</t>
         </is>
       </c>
     </row>
@@ -12085,7 +12085,7 @@
       </c>
       <c r="D665" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#3].taxa_estruturacao_pct</t>
+          <t>funding.divida[3].estruturacao_pct</t>
         </is>
       </c>
     </row>
@@ -12103,7 +12103,7 @@
       </c>
       <c r="D666" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#3].taxa_administracao_mensal</t>
+          <t>funding.divida[3].administracao_mensal</t>
         </is>
       </c>
     </row>
@@ -12121,7 +12121,7 @@
       </c>
       <c r="D667" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#3].outros_encargos_iniciais</t>
+          <t>funding.divida[3].outros_encargos</t>
         </is>
       </c>
     </row>
@@ -12150,7 +12150,7 @@
       </c>
       <c r="D669" s="8" t="inlineStr">
         <is>
-          <t>funding[equity#1].nome</t>
+          <t>funding.equity[1].nome</t>
         </is>
       </c>
     </row>
@@ -12170,7 +12170,7 @@
       </c>
       <c r="D670" s="8" t="inlineStr">
         <is>
-          <t>funding[equity#1].valor</t>
+          <t>funding.equity[1].valor</t>
         </is>
       </c>
     </row>
@@ -12192,7 +12192,7 @@
       </c>
       <c r="D671" s="8" t="inlineStr">
         <is>
-          <t>funding[equity#1].cronograma_evento / fase_ancora_id</t>
+          <t>funding.equity[1].aporte</t>
         </is>
       </c>
     </row>
@@ -12210,7 +12210,7 @@
       </c>
       <c r="D672" s="8" t="inlineStr">
         <is>
-          <t>funding[equity#1].inicio_mes</t>
+          <t>funding.equity[1].mes</t>
         </is>
       </c>
     </row>
@@ -12232,7 +12232,7 @@
       </c>
       <c r="D673" s="8" t="inlineStr">
         <is>
-          <t>funding[equity#1].modo_retorno</t>
+          <t>funding.equity[1].modo_retorno</t>
         </is>
       </c>
     </row>
@@ -12252,7 +12252,7 @@
       </c>
       <c r="D674" s="8" t="inlineStr">
         <is>
-          <t>funding[equity#1].pct_retorno</t>
+          <t>funding.equity[1].pct_retorno</t>
         </is>
       </c>
     </row>
@@ -12277,7 +12277,7 @@
       </c>
       <c r="D676" s="8" t="inlineStr">
         <is>
-          <t>funding[equity#2].nome</t>
+          <t>funding.equity[2].nome</t>
         </is>
       </c>
     </row>
@@ -12295,7 +12295,7 @@
       </c>
       <c r="D677" s="8" t="inlineStr">
         <is>
-          <t>funding[equity#2].valor</t>
+          <t>funding.equity[2].valor</t>
         </is>
       </c>
     </row>
@@ -12313,7 +12313,7 @@
       </c>
       <c r="D678" s="8" t="inlineStr">
         <is>
-          <t>funding[equity#2].cronograma_evento / fase_ancora_id</t>
+          <t>funding.equity[2].aporte</t>
         </is>
       </c>
     </row>
@@ -12331,7 +12331,7 @@
       </c>
       <c r="D679" s="8" t="inlineStr">
         <is>
-          <t>funding[equity#2].inicio_mes</t>
+          <t>funding.equity[2].mes</t>
         </is>
       </c>
     </row>
@@ -12349,7 +12349,7 @@
       </c>
       <c r="D680" s="8" t="inlineStr">
         <is>
-          <t>funding[equity#2].modo_retorno</t>
+          <t>funding.equity[2].modo_retorno</t>
         </is>
       </c>
     </row>
@@ -12367,7 +12367,7 @@
       </c>
       <c r="D681" s="8" t="inlineStr">
         <is>
-          <t>funding[equity#2].pct_retorno</t>
+          <t>funding.equity[2].pct_retorno</t>
         </is>
       </c>
     </row>
@@ -12392,7 +12392,7 @@
       </c>
       <c r="D683" s="8" t="inlineStr">
         <is>
-          <t>funding[equity#3].nome</t>
+          <t>funding.equity[3].nome</t>
         </is>
       </c>
     </row>
@@ -12410,7 +12410,7 @@
       </c>
       <c r="D684" s="8" t="inlineStr">
         <is>
-          <t>funding[equity#3].valor</t>
+          <t>funding.equity[3].valor</t>
         </is>
       </c>
     </row>
@@ -12428,7 +12428,7 @@
       </c>
       <c r="D685" s="8" t="inlineStr">
         <is>
-          <t>funding[equity#3].cronograma_evento / fase_ancora_id</t>
+          <t>funding.equity[3].aporte</t>
         </is>
       </c>
     </row>
@@ -12446,7 +12446,7 @@
       </c>
       <c r="D686" s="8" t="inlineStr">
         <is>
-          <t>funding[equity#3].inicio_mes</t>
+          <t>funding.equity[3].mes</t>
         </is>
       </c>
     </row>
@@ -12464,7 +12464,7 @@
       </c>
       <c r="D687" s="8" t="inlineStr">
         <is>
-          <t>funding[equity#3].modo_retorno</t>
+          <t>funding.equity[3].modo_retorno</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12482,7 @@
       </c>
       <c r="D688" s="8" t="inlineStr">
         <is>
-          <t>funding[equity#3].pct_retorno</t>
+          <t>funding.equity[3].pct_retorno</t>
         </is>
       </c>
     </row>
@@ -12511,7 +12511,7 @@
       </c>
       <c r="D690" s="8" t="inlineStr">
         <is>
-          <t>avancado_cenarios[1].nome</t>
+          <t>cenarios[1].nome</t>
         </is>
       </c>
     </row>
@@ -12531,7 +12531,7 @@
       </c>
       <c r="D691" s="8" t="inlineStr">
         <is>
-          <t>avancado_cenarios[1].preco_venda_pct</t>
+          <t>cenarios[1].preco_venda_pct</t>
         </is>
       </c>
     </row>
@@ -12551,7 +12551,7 @@
       </c>
       <c r="D692" s="8" t="inlineStr">
         <is>
-          <t>avancado_cenarios[1].custo_obra_pct</t>
+          <t>cenarios[1].custo_obra_pct</t>
         </is>
       </c>
     </row>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="D693" s="8" t="inlineStr">
         <is>
-          <t>avancado_cenarios[2].nome</t>
+          <t>cenarios[2].nome</t>
         </is>
       </c>
     </row>
@@ -12593,7 +12593,7 @@
       </c>
       <c r="D694" s="8" t="inlineStr">
         <is>
-          <t>avancado_cenarios[2].preco_venda_pct</t>
+          <t>cenarios[2].preco_venda_pct</t>
         </is>
       </c>
     </row>
@@ -12613,7 +12613,7 @@
       </c>
       <c r="D695" s="8" t="inlineStr">
         <is>
-          <t>avancado_cenarios[2].custo_obra_pct</t>
+          <t>cenarios[2].custo_obra_pct</t>
         </is>
       </c>
     </row>
@@ -12631,7 +12631,7 @@
       </c>
       <c r="D696" s="8" t="inlineStr">
         <is>
-          <t>avancado_cenarios[3].nome</t>
+          <t>cenarios[3].nome</t>
         </is>
       </c>
     </row>
@@ -12649,7 +12649,7 @@
       </c>
       <c r="D697" s="8" t="inlineStr">
         <is>
-          <t>avancado_cenarios[3].preco_venda_pct</t>
+          <t>cenarios[3].preco_venda_pct</t>
         </is>
       </c>
     </row>
@@ -12667,7 +12667,7 @@
       </c>
       <c r="D698" s="8" t="inlineStr">
         <is>
-          <t>avancado_cenarios[3].custo_obra_pct</t>
+          <t>cenarios[3].custo_obra_pct</t>
         </is>
       </c>
     </row>
@@ -12685,7 +12685,7 @@
       </c>
       <c r="D699" s="8" t="inlineStr">
         <is>
-          <t>avancado_cenarios[4].nome</t>
+          <t>cenarios[4].nome</t>
         </is>
       </c>
     </row>
@@ -12703,7 +12703,7 @@
       </c>
       <c r="D700" s="8" t="inlineStr">
         <is>
-          <t>avancado_cenarios[4].preco_venda_pct</t>
+          <t>cenarios[4].preco_venda_pct</t>
         </is>
       </c>
     </row>
@@ -12721,7 +12721,7 @@
       </c>
       <c r="D701" s="8" t="inlineStr">
         <is>
-          <t>avancado_cenarios[4].custo_obra_pct</t>
+          <t>cenarios[4].custo_obra_pct</t>
         </is>
       </c>
     </row>
@@ -12739,7 +12739,7 @@
       </c>
       <c r="D702" s="8" t="inlineStr">
         <is>
-          <t>avancado_cenarios[5].nome</t>
+          <t>cenarios[5].nome</t>
         </is>
       </c>
     </row>
@@ -12757,7 +12757,7 @@
       </c>
       <c r="D703" s="8" t="inlineStr">
         <is>
-          <t>avancado_cenarios[5].preco_venda_pct</t>
+          <t>cenarios[5].preco_venda_pct</t>
         </is>
       </c>
     </row>
@@ -12775,7 +12775,7 @@
       </c>
       <c r="D704" s="8" t="inlineStr">
         <is>
-          <t>avancado_cenarios[5].custo_obra_pct</t>
+          <t>cenarios[5].custo_obra_pct</t>
         </is>
       </c>
     </row>
@@ -15603,16 +15603,16 @@
     <row r="844">
       <c r="A844" s="18" t="inlineStr">
         <is>
-          <t>Σ custos conversíveis — terreno</t>
-        </is>
-      </c>
-      <c r="B844" s="24">
-        <f>IF($B$296="terreno",N($B$816),0)+IF($B$307="terreno",N($B$817),0)+IF($B$318="terreno",N($B$818),0)+IF($B$329="terreno",N($B$819),0)+IF($B$340="terreno",N($B$820),0)+IF($B$351="terreno",N($B$821),0)+IF($B$362="terreno",N($B$822),0)+IF($B$373="terreno",N($B$823),0)+IF($B$384="terreno",N($B$824),0)+IF($B$395="terreno",N($B$825),0)+IF($B$406="terreno",N($B$826),0)+IF($B$417="terreno",N($B$827),0)+IF($B$428="terreno",N($B$828),0)+IF($B$439="terreno",N($B$829),0)+IF($B$450="terreno",N($B$830),0)+IF($B$461="terreno",N($B$831),0)+IF($B$472="terreno",N($B$832),0)+IF($B$483="terreno",N($B$833),0)+IF($B$494="terreno",N($B$834),0)+IF($B$505="terreno",N($B$835),0)+IF($B$516="terreno",N($B$836),0)+IF($B$527="terreno",N($B$837),0)+IF($B$538="terreno",N($B$838),0)+IF($B$549="terreno",N($B$839),0)+IF($B$560="terreno",N($B$840),0)+IF($B$571="terreno",N($B$841),0)+IF($B$582="terreno",N($B$842),0)+IF($B$593="terreno",N($B$843),0)</f>
+          <t>Custo 1 — conferência</t>
+        </is>
+      </c>
+      <c r="B844" s="23">
+        <f>IF(AND($B$296="",$B$297=""),"",IF(OR($B$296="",$B$297="",$B$299=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$296="terreno",$B$297="Preço",OR($B$299="rs",$B$299="rs_m2_terreno")),AND($B$296="terreno",$B$297="Registro",OR($B$299="rs",$B$299="rs_m2_priv")),AND($B$296="terreno",$B$297="Outro",OR($B$299="rs",$B$299="pct_vgv")),AND($B$296="obra",$B$297="Construção",OR($B$299="rs",$B$299="rs_m2_priv")),AND($B$296="obra",$B$297="Outorga",OR($B$299="rs",$B$299="pct_vgv")),AND($B$296="obra",$B$297="Decoração",OR($B$299="rs",$B$299="rs_m2_priv")),AND($B$296="obra",$B$297="Gestão da obra",OR($B$299="rs",$B$299="pct_obra")),AND($B$296="obra",$B$297="Contingência",OR($B$299="rs",$B$299="pct_vgv")),AND($B$296="obra",$B$297="Outro",OR($B$299="rs",$B$299="pct_vgv")),AND($B$296="diretos",$B$297="Marketing &amp; Publicidade",OR($B$299="rs",$B$299="pct_vgv",$B$299="pct_recebido")),AND($B$296="diretos",$B$297="Corretagem de vendas",OR($B$299="pct_vgv")),AND($B$296="diretos",$B$297="Projetos",OR($B$299="rs",$B$299="rs_m2_priv",$B$299="pct_constr")),AND($B$296="diretos",$B$297="Licenças e Aprovações",OR($B$299="rs",$B$299="rs_m2_priv")),AND($B$296="diretos",$B$297="Manutenção pós-obra",OR($B$299="rs",$B$299="pct_vgv",$B$299="pct_recebido")),AND($B$296="diretos",$B$297="Outro",OR($B$299="rs",$B$299="pct_vgv",$B$299="pct_recebido")),AND($B$296="indireto",$B$297="Marketing global",OR($B$299="rs",$B$299="pct_vgv",$B$299="pct_recebido")),AND($B$296="indireto",$B$297="Stand de vendas",OR($B$299="rs",$B$299="pct_vgv")),AND($B$296="indireto",$B$297="Gestão",OR($B$299="rs",$B$299="pct_vgv",$B$299="pct_recebido")),AND($B$296="indireto",$B$297="Outro",OR($B$299="rs",$B$299="pct_vgv",$B$299="pct_recebido")),AND($B$296="financeiro",$B$297="Juros de financiamento",OR($B$299="rs",$B$299="pct_vgv")),AND($B$296="financeiro",$B$297="Taxas bancárias",OR($B$299="rs",$B$299="pct_vgv")),AND($B$296="financeiro",$B$297="Estruturação de dívida",OR($B$299="rs",$B$299="pct_vgv")),AND($B$296="financeiro",$B$297="Investidores",OR($B$299="rs",$B$299="pct_vgv")),AND($B$296="financeiro",$B$297="Outro",OR($B$299="rs",$B$299="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$300&lt;&gt;"",$B$301&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$299,3)="pct",$B$301="",$B$300=""),"⚠ falta o valor na linha certa","OK")))))</f>
         <v/>
       </c>
       <c r="C844" s="20" t="inlineStr">
         <is>
-          <t>R$</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="D844" s="21" t="inlineStr">
@@ -15624,16 +15624,16 @@
     <row r="845">
       <c r="A845" s="18" t="inlineStr">
         <is>
-          <t>Σ custos conversíveis — obra</t>
-        </is>
-      </c>
-      <c r="B845" s="24">
-        <f>IF($B$296="obra",N($B$816),0)+IF($B$307="obra",N($B$817),0)+IF($B$318="obra",N($B$818),0)+IF($B$329="obra",N($B$819),0)+IF($B$340="obra",N($B$820),0)+IF($B$351="obra",N($B$821),0)+IF($B$362="obra",N($B$822),0)+IF($B$373="obra",N($B$823),0)+IF($B$384="obra",N($B$824),0)+IF($B$395="obra",N($B$825),0)+IF($B$406="obra",N($B$826),0)+IF($B$417="obra",N($B$827),0)+IF($B$428="obra",N($B$828),0)+IF($B$439="obra",N($B$829),0)+IF($B$450="obra",N($B$830),0)+IF($B$461="obra",N($B$831),0)+IF($B$472="obra",N($B$832),0)+IF($B$483="obra",N($B$833),0)+IF($B$494="obra",N($B$834),0)+IF($B$505="obra",N($B$835),0)+IF($B$516="obra",N($B$836),0)+IF($B$527="obra",N($B$837),0)+IF($B$538="obra",N($B$838),0)+IF($B$549="obra",N($B$839),0)+IF($B$560="obra",N($B$840),0)+IF($B$571="obra",N($B$841),0)+IF($B$582="obra",N($B$842),0)+IF($B$593="obra",N($B$843),0)</f>
+          <t>Custo 2 — conferência</t>
+        </is>
+      </c>
+      <c r="B845" s="23">
+        <f>IF(AND($B$307="",$B$308=""),"",IF(OR($B$307="",$B$308="",$B$310=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$307="terreno",$B$308="Preço",OR($B$310="rs",$B$310="rs_m2_terreno")),AND($B$307="terreno",$B$308="Registro",OR($B$310="rs",$B$310="rs_m2_priv")),AND($B$307="terreno",$B$308="Outro",OR($B$310="rs",$B$310="pct_vgv")),AND($B$307="obra",$B$308="Construção",OR($B$310="rs",$B$310="rs_m2_priv")),AND($B$307="obra",$B$308="Outorga",OR($B$310="rs",$B$310="pct_vgv")),AND($B$307="obra",$B$308="Decoração",OR($B$310="rs",$B$310="rs_m2_priv")),AND($B$307="obra",$B$308="Gestão da obra",OR($B$310="rs",$B$310="pct_obra")),AND($B$307="obra",$B$308="Contingência",OR($B$310="rs",$B$310="pct_vgv")),AND($B$307="obra",$B$308="Outro",OR($B$310="rs",$B$310="pct_vgv")),AND($B$307="diretos",$B$308="Marketing &amp; Publicidade",OR($B$310="rs",$B$310="pct_vgv",$B$310="pct_recebido")),AND($B$307="diretos",$B$308="Corretagem de vendas",OR($B$310="pct_vgv")),AND($B$307="diretos",$B$308="Projetos",OR($B$310="rs",$B$310="rs_m2_priv",$B$310="pct_constr")),AND($B$307="diretos",$B$308="Licenças e Aprovações",OR($B$310="rs",$B$310="rs_m2_priv")),AND($B$307="diretos",$B$308="Manutenção pós-obra",OR($B$310="rs",$B$310="pct_vgv",$B$310="pct_recebido")),AND($B$307="diretos",$B$308="Outro",OR($B$310="rs",$B$310="pct_vgv",$B$310="pct_recebido")),AND($B$307="indireto",$B$308="Marketing global",OR($B$310="rs",$B$310="pct_vgv",$B$310="pct_recebido")),AND($B$307="indireto",$B$308="Stand de vendas",OR($B$310="rs",$B$310="pct_vgv")),AND($B$307="indireto",$B$308="Gestão",OR($B$310="rs",$B$310="pct_vgv",$B$310="pct_recebido")),AND($B$307="indireto",$B$308="Outro",OR($B$310="rs",$B$310="pct_vgv",$B$310="pct_recebido")),AND($B$307="financeiro",$B$308="Juros de financiamento",OR($B$310="rs",$B$310="pct_vgv")),AND($B$307="financeiro",$B$308="Taxas bancárias",OR($B$310="rs",$B$310="pct_vgv")),AND($B$307="financeiro",$B$308="Estruturação de dívida",OR($B$310="rs",$B$310="pct_vgv")),AND($B$307="financeiro",$B$308="Investidores",OR($B$310="rs",$B$310="pct_vgv")),AND($B$307="financeiro",$B$308="Outro",OR($B$310="rs",$B$310="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$311&lt;&gt;"",$B$312&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$310,3)="pct",$B$312="",$B$311=""),"⚠ falta o valor na linha certa","OK")))))</f>
         <v/>
       </c>
       <c r="C845" s="20" t="inlineStr">
         <is>
-          <t>R$</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="D845" s="21" t="inlineStr">
@@ -15645,16 +15645,16 @@
     <row r="846">
       <c r="A846" s="18" t="inlineStr">
         <is>
-          <t>Σ custos conversíveis — diretos</t>
-        </is>
-      </c>
-      <c r="B846" s="24">
-        <f>IF($B$296="diretos",N($B$816),0)+IF($B$307="diretos",N($B$817),0)+IF($B$318="diretos",N($B$818),0)+IF($B$329="diretos",N($B$819),0)+IF($B$340="diretos",N($B$820),0)+IF($B$351="diretos",N($B$821),0)+IF($B$362="diretos",N($B$822),0)+IF($B$373="diretos",N($B$823),0)+IF($B$384="diretos",N($B$824),0)+IF($B$395="diretos",N($B$825),0)+IF($B$406="diretos",N($B$826),0)+IF($B$417="diretos",N($B$827),0)+IF($B$428="diretos",N($B$828),0)+IF($B$439="diretos",N($B$829),0)+IF($B$450="diretos",N($B$830),0)+IF($B$461="diretos",N($B$831),0)+IF($B$472="diretos",N($B$832),0)+IF($B$483="diretos",N($B$833),0)+IF($B$494="diretos",N($B$834),0)+IF($B$505="diretos",N($B$835),0)+IF($B$516="diretos",N($B$836),0)+IF($B$527="diretos",N($B$837),0)+IF($B$538="diretos",N($B$838),0)+IF($B$549="diretos",N($B$839),0)+IF($B$560="diretos",N($B$840),0)+IF($B$571="diretos",N($B$841),0)+IF($B$582="diretos",N($B$842),0)+IF($B$593="diretos",N($B$843),0)</f>
+          <t>Custo 3 — conferência</t>
+        </is>
+      </c>
+      <c r="B846" s="23">
+        <f>IF(AND($B$318="",$B$319=""),"",IF(OR($B$318="",$B$319="",$B$321=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$318="terreno",$B$319="Preço",OR($B$321="rs",$B$321="rs_m2_terreno")),AND($B$318="terreno",$B$319="Registro",OR($B$321="rs",$B$321="rs_m2_priv")),AND($B$318="terreno",$B$319="Outro",OR($B$321="rs",$B$321="pct_vgv")),AND($B$318="obra",$B$319="Construção",OR($B$321="rs",$B$321="rs_m2_priv")),AND($B$318="obra",$B$319="Outorga",OR($B$321="rs",$B$321="pct_vgv")),AND($B$318="obra",$B$319="Decoração",OR($B$321="rs",$B$321="rs_m2_priv")),AND($B$318="obra",$B$319="Gestão da obra",OR($B$321="rs",$B$321="pct_obra")),AND($B$318="obra",$B$319="Contingência",OR($B$321="rs",$B$321="pct_vgv")),AND($B$318="obra",$B$319="Outro",OR($B$321="rs",$B$321="pct_vgv")),AND($B$318="diretos",$B$319="Marketing &amp; Publicidade",OR($B$321="rs",$B$321="pct_vgv",$B$321="pct_recebido")),AND($B$318="diretos",$B$319="Corretagem de vendas",OR($B$321="pct_vgv")),AND($B$318="diretos",$B$319="Projetos",OR($B$321="rs",$B$321="rs_m2_priv",$B$321="pct_constr")),AND($B$318="diretos",$B$319="Licenças e Aprovações",OR($B$321="rs",$B$321="rs_m2_priv")),AND($B$318="diretos",$B$319="Manutenção pós-obra",OR($B$321="rs",$B$321="pct_vgv",$B$321="pct_recebido")),AND($B$318="diretos",$B$319="Outro",OR($B$321="rs",$B$321="pct_vgv",$B$321="pct_recebido")),AND($B$318="indireto",$B$319="Marketing global",OR($B$321="rs",$B$321="pct_vgv",$B$321="pct_recebido")),AND($B$318="indireto",$B$319="Stand de vendas",OR($B$321="rs",$B$321="pct_vgv")),AND($B$318="indireto",$B$319="Gestão",OR($B$321="rs",$B$321="pct_vgv",$B$321="pct_recebido")),AND($B$318="indireto",$B$319="Outro",OR($B$321="rs",$B$321="pct_vgv",$B$321="pct_recebido")),AND($B$318="financeiro",$B$319="Juros de financiamento",OR($B$321="rs",$B$321="pct_vgv")),AND($B$318="financeiro",$B$319="Taxas bancárias",OR($B$321="rs",$B$321="pct_vgv")),AND($B$318="financeiro",$B$319="Estruturação de dívida",OR($B$321="rs",$B$321="pct_vgv")),AND($B$318="financeiro",$B$319="Investidores",OR($B$321="rs",$B$321="pct_vgv")),AND($B$318="financeiro",$B$319="Outro",OR($B$321="rs",$B$321="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$322&lt;&gt;"",$B$323&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$321,3)="pct",$B$323="",$B$322=""),"⚠ falta o valor na linha certa","OK")))))</f>
         <v/>
       </c>
       <c r="C846" s="20" t="inlineStr">
         <is>
-          <t>R$</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="D846" s="21" t="inlineStr">
@@ -15666,16 +15666,16 @@
     <row r="847">
       <c r="A847" s="18" t="inlineStr">
         <is>
-          <t>Σ custos conversíveis — indireto</t>
-        </is>
-      </c>
-      <c r="B847" s="24">
-        <f>IF($B$296="indireto",N($B$816),0)+IF($B$307="indireto",N($B$817),0)+IF($B$318="indireto",N($B$818),0)+IF($B$329="indireto",N($B$819),0)+IF($B$340="indireto",N($B$820),0)+IF($B$351="indireto",N($B$821),0)+IF($B$362="indireto",N($B$822),0)+IF($B$373="indireto",N($B$823),0)+IF($B$384="indireto",N($B$824),0)+IF($B$395="indireto",N($B$825),0)+IF($B$406="indireto",N($B$826),0)+IF($B$417="indireto",N($B$827),0)+IF($B$428="indireto",N($B$828),0)+IF($B$439="indireto",N($B$829),0)+IF($B$450="indireto",N($B$830),0)+IF($B$461="indireto",N($B$831),0)+IF($B$472="indireto",N($B$832),0)+IF($B$483="indireto",N($B$833),0)+IF($B$494="indireto",N($B$834),0)+IF($B$505="indireto",N($B$835),0)+IF($B$516="indireto",N($B$836),0)+IF($B$527="indireto",N($B$837),0)+IF($B$538="indireto",N($B$838),0)+IF($B$549="indireto",N($B$839),0)+IF($B$560="indireto",N($B$840),0)+IF($B$571="indireto",N($B$841),0)+IF($B$582="indireto",N($B$842),0)+IF($B$593="indireto",N($B$843),0)</f>
+          <t>Custo 4 — conferência</t>
+        </is>
+      </c>
+      <c r="B847" s="23">
+        <f>IF(AND($B$329="",$B$330=""),"",IF(OR($B$329="",$B$330="",$B$332=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$329="terreno",$B$330="Preço",OR($B$332="rs",$B$332="rs_m2_terreno")),AND($B$329="terreno",$B$330="Registro",OR($B$332="rs",$B$332="rs_m2_priv")),AND($B$329="terreno",$B$330="Outro",OR($B$332="rs",$B$332="pct_vgv")),AND($B$329="obra",$B$330="Construção",OR($B$332="rs",$B$332="rs_m2_priv")),AND($B$329="obra",$B$330="Outorga",OR($B$332="rs",$B$332="pct_vgv")),AND($B$329="obra",$B$330="Decoração",OR($B$332="rs",$B$332="rs_m2_priv")),AND($B$329="obra",$B$330="Gestão da obra",OR($B$332="rs",$B$332="pct_obra")),AND($B$329="obra",$B$330="Contingência",OR($B$332="rs",$B$332="pct_vgv")),AND($B$329="obra",$B$330="Outro",OR($B$332="rs",$B$332="pct_vgv")),AND($B$329="diretos",$B$330="Marketing &amp; Publicidade",OR($B$332="rs",$B$332="pct_vgv",$B$332="pct_recebido")),AND($B$329="diretos",$B$330="Corretagem de vendas",OR($B$332="pct_vgv")),AND($B$329="diretos",$B$330="Projetos",OR($B$332="rs",$B$332="rs_m2_priv",$B$332="pct_constr")),AND($B$329="diretos",$B$330="Licenças e Aprovações",OR($B$332="rs",$B$332="rs_m2_priv")),AND($B$329="diretos",$B$330="Manutenção pós-obra",OR($B$332="rs",$B$332="pct_vgv",$B$332="pct_recebido")),AND($B$329="diretos",$B$330="Outro",OR($B$332="rs",$B$332="pct_vgv",$B$332="pct_recebido")),AND($B$329="indireto",$B$330="Marketing global",OR($B$332="rs",$B$332="pct_vgv",$B$332="pct_recebido")),AND($B$329="indireto",$B$330="Stand de vendas",OR($B$332="rs",$B$332="pct_vgv")),AND($B$329="indireto",$B$330="Gestão",OR($B$332="rs",$B$332="pct_vgv",$B$332="pct_recebido")),AND($B$329="indireto",$B$330="Outro",OR($B$332="rs",$B$332="pct_vgv",$B$332="pct_recebido")),AND($B$329="financeiro",$B$330="Juros de financiamento",OR($B$332="rs",$B$332="pct_vgv")),AND($B$329="financeiro",$B$330="Taxas bancárias",OR($B$332="rs",$B$332="pct_vgv")),AND($B$329="financeiro",$B$330="Estruturação de dívida",OR($B$332="rs",$B$332="pct_vgv")),AND($B$329="financeiro",$B$330="Investidores",OR($B$332="rs",$B$332="pct_vgv")),AND($B$329="financeiro",$B$330="Outro",OR($B$332="rs",$B$332="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$333&lt;&gt;"",$B$334&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$332,3)="pct",$B$334="",$B$333=""),"⚠ falta o valor na linha certa","OK")))))</f>
         <v/>
       </c>
       <c r="C847" s="20" t="inlineStr">
         <is>
-          <t>R$</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="D847" s="21" t="inlineStr">
@@ -15687,16 +15687,16 @@
     <row r="848">
       <c r="A848" s="18" t="inlineStr">
         <is>
-          <t>Σ custos conversíveis — financeiro</t>
-        </is>
-      </c>
-      <c r="B848" s="24">
-        <f>IF($B$296="financeiro",N($B$816),0)+IF($B$307="financeiro",N($B$817),0)+IF($B$318="financeiro",N($B$818),0)+IF($B$329="financeiro",N($B$819),0)+IF($B$340="financeiro",N($B$820),0)+IF($B$351="financeiro",N($B$821),0)+IF($B$362="financeiro",N($B$822),0)+IF($B$373="financeiro",N($B$823),0)+IF($B$384="financeiro",N($B$824),0)+IF($B$395="financeiro",N($B$825),0)+IF($B$406="financeiro",N($B$826),0)+IF($B$417="financeiro",N($B$827),0)+IF($B$428="financeiro",N($B$828),0)+IF($B$439="financeiro",N($B$829),0)+IF($B$450="financeiro",N($B$830),0)+IF($B$461="financeiro",N($B$831),0)+IF($B$472="financeiro",N($B$832),0)+IF($B$483="financeiro",N($B$833),0)+IF($B$494="financeiro",N($B$834),0)+IF($B$505="financeiro",N($B$835),0)+IF($B$516="financeiro",N($B$836),0)+IF($B$527="financeiro",N($B$837),0)+IF($B$538="financeiro",N($B$838),0)+IF($B$549="financeiro",N($B$839),0)+IF($B$560="financeiro",N($B$840),0)+IF($B$571="financeiro",N($B$841),0)+IF($B$582="financeiro",N($B$842),0)+IF($B$593="financeiro",N($B$843),0)</f>
+          <t>Custo 5 — conferência</t>
+        </is>
+      </c>
+      <c r="B848" s="23">
+        <f>IF(AND($B$340="",$B$341=""),"",IF(OR($B$340="",$B$341="",$B$343=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$340="terreno",$B$341="Preço",OR($B$343="rs",$B$343="rs_m2_terreno")),AND($B$340="terreno",$B$341="Registro",OR($B$343="rs",$B$343="rs_m2_priv")),AND($B$340="terreno",$B$341="Outro",OR($B$343="rs",$B$343="pct_vgv")),AND($B$340="obra",$B$341="Construção",OR($B$343="rs",$B$343="rs_m2_priv")),AND($B$340="obra",$B$341="Outorga",OR($B$343="rs",$B$343="pct_vgv")),AND($B$340="obra",$B$341="Decoração",OR($B$343="rs",$B$343="rs_m2_priv")),AND($B$340="obra",$B$341="Gestão da obra",OR($B$343="rs",$B$343="pct_obra")),AND($B$340="obra",$B$341="Contingência",OR($B$343="rs",$B$343="pct_vgv")),AND($B$340="obra",$B$341="Outro",OR($B$343="rs",$B$343="pct_vgv")),AND($B$340="diretos",$B$341="Marketing &amp; Publicidade",OR($B$343="rs",$B$343="pct_vgv",$B$343="pct_recebido")),AND($B$340="diretos",$B$341="Corretagem de vendas",OR($B$343="pct_vgv")),AND($B$340="diretos",$B$341="Projetos",OR($B$343="rs",$B$343="rs_m2_priv",$B$343="pct_constr")),AND($B$340="diretos",$B$341="Licenças e Aprovações",OR($B$343="rs",$B$343="rs_m2_priv")),AND($B$340="diretos",$B$341="Manutenção pós-obra",OR($B$343="rs",$B$343="pct_vgv",$B$343="pct_recebido")),AND($B$340="diretos",$B$341="Outro",OR($B$343="rs",$B$343="pct_vgv",$B$343="pct_recebido")),AND($B$340="indireto",$B$341="Marketing global",OR($B$343="rs",$B$343="pct_vgv",$B$343="pct_recebido")),AND($B$340="indireto",$B$341="Stand de vendas",OR($B$343="rs",$B$343="pct_vgv")),AND($B$340="indireto",$B$341="Gestão",OR($B$343="rs",$B$343="pct_vgv",$B$343="pct_recebido")),AND($B$340="indireto",$B$341="Outro",OR($B$343="rs",$B$343="pct_vgv",$B$343="pct_recebido")),AND($B$340="financeiro",$B$341="Juros de financiamento",OR($B$343="rs",$B$343="pct_vgv")),AND($B$340="financeiro",$B$341="Taxas bancárias",OR($B$343="rs",$B$343="pct_vgv")),AND($B$340="financeiro",$B$341="Estruturação de dívida",OR($B$343="rs",$B$343="pct_vgv")),AND($B$340="financeiro",$B$341="Investidores",OR($B$343="rs",$B$343="pct_vgv")),AND($B$340="financeiro",$B$341="Outro",OR($B$343="rs",$B$343="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$344&lt;&gt;"",$B$345&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$343,3)="pct",$B$345="",$B$344=""),"⚠ falta o valor na linha certa","OK")))))</f>
         <v/>
       </c>
       <c r="C848" s="20" t="inlineStr">
         <is>
-          <t>R$</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="D848" s="21" t="inlineStr">
@@ -15708,16 +15708,16 @@
     <row r="849">
       <c r="A849" s="18" t="inlineStr">
         <is>
-          <t>Permuta física 1 — VGV entregue (unidades × área × preço sugerido)</t>
-        </is>
-      </c>
-      <c r="B849" s="24">
-        <f>IF($B$604="",0,N($B$605)*(($B$58=$B$604)*(N($B$59)+N($B$60))*N($B$62)+($B$64=$B$604)*(N($B$65)+N($B$66))*N($B$68)+($B$70=$B$604)*(N($B$71)+N($B$72))*N($B$74)+($B$76=$B$604)*(N($B$77)+N($B$78))*N($B$80)+($B$82=$B$604)*(N($B$83)+N($B$84))*N($B$86)+($B$88=$B$604)*(N($B$89)+N($B$90))*N($B$92)+($B$94=$B$604)*(N($B$95)+N($B$96))*N($B$98)+($B$100=$B$604)*(N($B$101)+N($B$102))*N($B$104)+($B$106=$B$604)*(N($B$107)+N($B$108))*N($B$110)+($B$112=$B$604)*(N($B$113)+N($B$114))*N($B$116)))</f>
+          <t>Custo 6 — conferência</t>
+        </is>
+      </c>
+      <c r="B849" s="23">
+        <f>IF(AND($B$351="",$B$352=""),"",IF(OR($B$351="",$B$352="",$B$354=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$351="terreno",$B$352="Preço",OR($B$354="rs",$B$354="rs_m2_terreno")),AND($B$351="terreno",$B$352="Registro",OR($B$354="rs",$B$354="rs_m2_priv")),AND($B$351="terreno",$B$352="Outro",OR($B$354="rs",$B$354="pct_vgv")),AND($B$351="obra",$B$352="Construção",OR($B$354="rs",$B$354="rs_m2_priv")),AND($B$351="obra",$B$352="Outorga",OR($B$354="rs",$B$354="pct_vgv")),AND($B$351="obra",$B$352="Decoração",OR($B$354="rs",$B$354="rs_m2_priv")),AND($B$351="obra",$B$352="Gestão da obra",OR($B$354="rs",$B$354="pct_obra")),AND($B$351="obra",$B$352="Contingência",OR($B$354="rs",$B$354="pct_vgv")),AND($B$351="obra",$B$352="Outro",OR($B$354="rs",$B$354="pct_vgv")),AND($B$351="diretos",$B$352="Marketing &amp; Publicidade",OR($B$354="rs",$B$354="pct_vgv",$B$354="pct_recebido")),AND($B$351="diretos",$B$352="Corretagem de vendas",OR($B$354="pct_vgv")),AND($B$351="diretos",$B$352="Projetos",OR($B$354="rs",$B$354="rs_m2_priv",$B$354="pct_constr")),AND($B$351="diretos",$B$352="Licenças e Aprovações",OR($B$354="rs",$B$354="rs_m2_priv")),AND($B$351="diretos",$B$352="Manutenção pós-obra",OR($B$354="rs",$B$354="pct_vgv",$B$354="pct_recebido")),AND($B$351="diretos",$B$352="Outro",OR($B$354="rs",$B$354="pct_vgv",$B$354="pct_recebido")),AND($B$351="indireto",$B$352="Marketing global",OR($B$354="rs",$B$354="pct_vgv",$B$354="pct_recebido")),AND($B$351="indireto",$B$352="Stand de vendas",OR($B$354="rs",$B$354="pct_vgv")),AND($B$351="indireto",$B$352="Gestão",OR($B$354="rs",$B$354="pct_vgv",$B$354="pct_recebido")),AND($B$351="indireto",$B$352="Outro",OR($B$354="rs",$B$354="pct_vgv",$B$354="pct_recebido")),AND($B$351="financeiro",$B$352="Juros de financiamento",OR($B$354="rs",$B$354="pct_vgv")),AND($B$351="financeiro",$B$352="Taxas bancárias",OR($B$354="rs",$B$354="pct_vgv")),AND($B$351="financeiro",$B$352="Estruturação de dívida",OR($B$354="rs",$B$354="pct_vgv")),AND($B$351="financeiro",$B$352="Investidores",OR($B$354="rs",$B$354="pct_vgv")),AND($B$351="financeiro",$B$352="Outro",OR($B$354="rs",$B$354="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$355&lt;&gt;"",$B$356&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$354,3)="pct",$B$356="",$B$355=""),"⚠ falta o valor na linha certa","OK")))))</f>
         <v/>
       </c>
       <c r="C849" s="20" t="inlineStr">
         <is>
-          <t>R$</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="D849" s="21" t="inlineStr">
@@ -15729,16 +15729,16 @@
     <row r="850">
       <c r="A850" s="18" t="inlineStr">
         <is>
-          <t>Permuta financeira 1 — equivalente em R$</t>
-        </is>
-      </c>
-      <c r="B850" s="24">
-        <f>IF($B$609="pct_vgv",N($B$611)*$B$757,IF($B$609="rs",N($B$610),0))</f>
+          <t>Custo 7 — conferência</t>
+        </is>
+      </c>
+      <c r="B850" s="23">
+        <f>IF(AND($B$362="",$B$363=""),"",IF(OR($B$362="",$B$363="",$B$365=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$362="terreno",$B$363="Preço",OR($B$365="rs",$B$365="rs_m2_terreno")),AND($B$362="terreno",$B$363="Registro",OR($B$365="rs",$B$365="rs_m2_priv")),AND($B$362="terreno",$B$363="Outro",OR($B$365="rs",$B$365="pct_vgv")),AND($B$362="obra",$B$363="Construção",OR($B$365="rs",$B$365="rs_m2_priv")),AND($B$362="obra",$B$363="Outorga",OR($B$365="rs",$B$365="pct_vgv")),AND($B$362="obra",$B$363="Decoração",OR($B$365="rs",$B$365="rs_m2_priv")),AND($B$362="obra",$B$363="Gestão da obra",OR($B$365="rs",$B$365="pct_obra")),AND($B$362="obra",$B$363="Contingência",OR($B$365="rs",$B$365="pct_vgv")),AND($B$362="obra",$B$363="Outro",OR($B$365="rs",$B$365="pct_vgv")),AND($B$362="diretos",$B$363="Marketing &amp; Publicidade",OR($B$365="rs",$B$365="pct_vgv",$B$365="pct_recebido")),AND($B$362="diretos",$B$363="Corretagem de vendas",OR($B$365="pct_vgv")),AND($B$362="diretos",$B$363="Projetos",OR($B$365="rs",$B$365="rs_m2_priv",$B$365="pct_constr")),AND($B$362="diretos",$B$363="Licenças e Aprovações",OR($B$365="rs",$B$365="rs_m2_priv")),AND($B$362="diretos",$B$363="Manutenção pós-obra",OR($B$365="rs",$B$365="pct_vgv",$B$365="pct_recebido")),AND($B$362="diretos",$B$363="Outro",OR($B$365="rs",$B$365="pct_vgv",$B$365="pct_recebido")),AND($B$362="indireto",$B$363="Marketing global",OR($B$365="rs",$B$365="pct_vgv",$B$365="pct_recebido")),AND($B$362="indireto",$B$363="Stand de vendas",OR($B$365="rs",$B$365="pct_vgv")),AND($B$362="indireto",$B$363="Gestão",OR($B$365="rs",$B$365="pct_vgv",$B$365="pct_recebido")),AND($B$362="indireto",$B$363="Outro",OR($B$365="rs",$B$365="pct_vgv",$B$365="pct_recebido")),AND($B$362="financeiro",$B$363="Juros de financiamento",OR($B$365="rs",$B$365="pct_vgv")),AND($B$362="financeiro",$B$363="Taxas bancárias",OR($B$365="rs",$B$365="pct_vgv")),AND($B$362="financeiro",$B$363="Estruturação de dívida",OR($B$365="rs",$B$365="pct_vgv")),AND($B$362="financeiro",$B$363="Investidores",OR($B$365="rs",$B$365="pct_vgv")),AND($B$362="financeiro",$B$363="Outro",OR($B$365="rs",$B$365="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$366&lt;&gt;"",$B$367&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$365,3)="pct",$B$367="",$B$366=""),"⚠ falta o valor na linha certa","OK")))))</f>
         <v/>
       </c>
       <c r="C850" s="20" t="inlineStr">
         <is>
-          <t>R$</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="D850" s="21" t="inlineStr">
@@ -15750,16 +15750,16 @@
     <row r="851">
       <c r="A851" s="18" t="inlineStr">
         <is>
-          <t>Permuta física 2 — VGV entregue (unidades × área × preço sugerido)</t>
-        </is>
-      </c>
-      <c r="B851" s="24">
-        <f>IF($B$606="",0,N($B$607)*(($B$58=$B$606)*(N($B$59)+N($B$60))*N($B$62)+($B$64=$B$606)*(N($B$65)+N($B$66))*N($B$68)+($B$70=$B$606)*(N($B$71)+N($B$72))*N($B$74)+($B$76=$B$606)*(N($B$77)+N($B$78))*N($B$80)+($B$82=$B$606)*(N($B$83)+N($B$84))*N($B$86)+($B$88=$B$606)*(N($B$89)+N($B$90))*N($B$92)+($B$94=$B$606)*(N($B$95)+N($B$96))*N($B$98)+($B$100=$B$606)*(N($B$101)+N($B$102))*N($B$104)+($B$106=$B$606)*(N($B$107)+N($B$108))*N($B$110)+($B$112=$B$606)*(N($B$113)+N($B$114))*N($B$116)))</f>
+          <t>Custo 8 — conferência</t>
+        </is>
+      </c>
+      <c r="B851" s="23">
+        <f>IF(AND($B$373="",$B$374=""),"",IF(OR($B$373="",$B$374="",$B$376=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$373="terreno",$B$374="Preço",OR($B$376="rs",$B$376="rs_m2_terreno")),AND($B$373="terreno",$B$374="Registro",OR($B$376="rs",$B$376="rs_m2_priv")),AND($B$373="terreno",$B$374="Outro",OR($B$376="rs",$B$376="pct_vgv")),AND($B$373="obra",$B$374="Construção",OR($B$376="rs",$B$376="rs_m2_priv")),AND($B$373="obra",$B$374="Outorga",OR($B$376="rs",$B$376="pct_vgv")),AND($B$373="obra",$B$374="Decoração",OR($B$376="rs",$B$376="rs_m2_priv")),AND($B$373="obra",$B$374="Gestão da obra",OR($B$376="rs",$B$376="pct_obra")),AND($B$373="obra",$B$374="Contingência",OR($B$376="rs",$B$376="pct_vgv")),AND($B$373="obra",$B$374="Outro",OR($B$376="rs",$B$376="pct_vgv")),AND($B$373="diretos",$B$374="Marketing &amp; Publicidade",OR($B$376="rs",$B$376="pct_vgv",$B$376="pct_recebido")),AND($B$373="diretos",$B$374="Corretagem de vendas",OR($B$376="pct_vgv")),AND($B$373="diretos",$B$374="Projetos",OR($B$376="rs",$B$376="rs_m2_priv",$B$376="pct_constr")),AND($B$373="diretos",$B$374="Licenças e Aprovações",OR($B$376="rs",$B$376="rs_m2_priv")),AND($B$373="diretos",$B$374="Manutenção pós-obra",OR($B$376="rs",$B$376="pct_vgv",$B$376="pct_recebido")),AND($B$373="diretos",$B$374="Outro",OR($B$376="rs",$B$376="pct_vgv",$B$376="pct_recebido")),AND($B$373="indireto",$B$374="Marketing global",OR($B$376="rs",$B$376="pct_vgv",$B$376="pct_recebido")),AND($B$373="indireto",$B$374="Stand de vendas",OR($B$376="rs",$B$376="pct_vgv")),AND($B$373="indireto",$B$374="Gestão",OR($B$376="rs",$B$376="pct_vgv",$B$376="pct_recebido")),AND($B$373="indireto",$B$374="Outro",OR($B$376="rs",$B$376="pct_vgv",$B$376="pct_recebido")),AND($B$373="financeiro",$B$374="Juros de financiamento",OR($B$376="rs",$B$376="pct_vgv")),AND($B$373="financeiro",$B$374="Taxas bancárias",OR($B$376="rs",$B$376="pct_vgv")),AND($B$373="financeiro",$B$374="Estruturação de dívida",OR($B$376="rs",$B$376="pct_vgv")),AND($B$373="financeiro",$B$374="Investidores",OR($B$376="rs",$B$376="pct_vgv")),AND($B$373="financeiro",$B$374="Outro",OR($B$376="rs",$B$376="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$377&lt;&gt;"",$B$378&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$376,3)="pct",$B$378="",$B$377=""),"⚠ falta o valor na linha certa","OK")))))</f>
         <v/>
       </c>
       <c r="C851" s="20" t="inlineStr">
         <is>
-          <t>R$</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="D851" s="21" t="inlineStr">
@@ -15771,16 +15771,16 @@
     <row r="852">
       <c r="A852" s="18" t="inlineStr">
         <is>
-          <t>Permuta financeira 2 — equivalente em R$</t>
-        </is>
-      </c>
-      <c r="B852" s="24">
-        <f>IF($B$614="pct_vgv",N($B$616)*$B$757,IF($B$614="rs",N($B$615),0))</f>
+          <t>Custo 9 — conferência</t>
+        </is>
+      </c>
+      <c r="B852" s="23">
+        <f>IF(AND($B$384="",$B$385=""),"",IF(OR($B$384="",$B$385="",$B$387=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$384="terreno",$B$385="Preço",OR($B$387="rs",$B$387="rs_m2_terreno")),AND($B$384="terreno",$B$385="Registro",OR($B$387="rs",$B$387="rs_m2_priv")),AND($B$384="terreno",$B$385="Outro",OR($B$387="rs",$B$387="pct_vgv")),AND($B$384="obra",$B$385="Construção",OR($B$387="rs",$B$387="rs_m2_priv")),AND($B$384="obra",$B$385="Outorga",OR($B$387="rs",$B$387="pct_vgv")),AND($B$384="obra",$B$385="Decoração",OR($B$387="rs",$B$387="rs_m2_priv")),AND($B$384="obra",$B$385="Gestão da obra",OR($B$387="rs",$B$387="pct_obra")),AND($B$384="obra",$B$385="Contingência",OR($B$387="rs",$B$387="pct_vgv")),AND($B$384="obra",$B$385="Outro",OR($B$387="rs",$B$387="pct_vgv")),AND($B$384="diretos",$B$385="Marketing &amp; Publicidade",OR($B$387="rs",$B$387="pct_vgv",$B$387="pct_recebido")),AND($B$384="diretos",$B$385="Corretagem de vendas",OR($B$387="pct_vgv")),AND($B$384="diretos",$B$385="Projetos",OR($B$387="rs",$B$387="rs_m2_priv",$B$387="pct_constr")),AND($B$384="diretos",$B$385="Licenças e Aprovações",OR($B$387="rs",$B$387="rs_m2_priv")),AND($B$384="diretos",$B$385="Manutenção pós-obra",OR($B$387="rs",$B$387="pct_vgv",$B$387="pct_recebido")),AND($B$384="diretos",$B$385="Outro",OR($B$387="rs",$B$387="pct_vgv",$B$387="pct_recebido")),AND($B$384="indireto",$B$385="Marketing global",OR($B$387="rs",$B$387="pct_vgv",$B$387="pct_recebido")),AND($B$384="indireto",$B$385="Stand de vendas",OR($B$387="rs",$B$387="pct_vgv")),AND($B$384="indireto",$B$385="Gestão",OR($B$387="rs",$B$387="pct_vgv",$B$387="pct_recebido")),AND($B$384="indireto",$B$385="Outro",OR($B$387="rs",$B$387="pct_vgv",$B$387="pct_recebido")),AND($B$384="financeiro",$B$385="Juros de financiamento",OR($B$387="rs",$B$387="pct_vgv")),AND($B$384="financeiro",$B$385="Taxas bancárias",OR($B$387="rs",$B$387="pct_vgv")),AND($B$384="financeiro",$B$385="Estruturação de dívida",OR($B$387="rs",$B$387="pct_vgv")),AND($B$384="financeiro",$B$385="Investidores",OR($B$387="rs",$B$387="pct_vgv")),AND($B$384="financeiro",$B$385="Outro",OR($B$387="rs",$B$387="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$388&lt;&gt;"",$B$389&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$387,3)="pct",$B$389="",$B$388=""),"⚠ falta o valor na linha certa","OK")))))</f>
         <v/>
       </c>
       <c r="C852" s="20" t="inlineStr">
         <is>
-          <t>R$</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="D852" s="21" t="inlineStr">
@@ -15792,16 +15792,16 @@
     <row r="853">
       <c r="A853" s="18" t="inlineStr">
         <is>
-          <t>Σ valor das dívidas</t>
-        </is>
-      </c>
-      <c r="B853" s="24">
-        <f>N($B$631)+N($B$644)+N($B$657)</f>
+          <t>Custo 10 — conferência</t>
+        </is>
+      </c>
+      <c r="B853" s="23">
+        <f>IF(AND($B$395="",$B$396=""),"",IF(OR($B$395="",$B$396="",$B$398=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$395="terreno",$B$396="Preço",OR($B$398="rs",$B$398="rs_m2_terreno")),AND($B$395="terreno",$B$396="Registro",OR($B$398="rs",$B$398="rs_m2_priv")),AND($B$395="terreno",$B$396="Outro",OR($B$398="rs",$B$398="pct_vgv")),AND($B$395="obra",$B$396="Construção",OR($B$398="rs",$B$398="rs_m2_priv")),AND($B$395="obra",$B$396="Outorga",OR($B$398="rs",$B$398="pct_vgv")),AND($B$395="obra",$B$396="Decoração",OR($B$398="rs",$B$398="rs_m2_priv")),AND($B$395="obra",$B$396="Gestão da obra",OR($B$398="rs",$B$398="pct_obra")),AND($B$395="obra",$B$396="Contingência",OR($B$398="rs",$B$398="pct_vgv")),AND($B$395="obra",$B$396="Outro",OR($B$398="rs",$B$398="pct_vgv")),AND($B$395="diretos",$B$396="Marketing &amp; Publicidade",OR($B$398="rs",$B$398="pct_vgv",$B$398="pct_recebido")),AND($B$395="diretos",$B$396="Corretagem de vendas",OR($B$398="pct_vgv")),AND($B$395="diretos",$B$396="Projetos",OR($B$398="rs",$B$398="rs_m2_priv",$B$398="pct_constr")),AND($B$395="diretos",$B$396="Licenças e Aprovações",OR($B$398="rs",$B$398="rs_m2_priv")),AND($B$395="diretos",$B$396="Manutenção pós-obra",OR($B$398="rs",$B$398="pct_vgv",$B$398="pct_recebido")),AND($B$395="diretos",$B$396="Outro",OR($B$398="rs",$B$398="pct_vgv",$B$398="pct_recebido")),AND($B$395="indireto",$B$396="Marketing global",OR($B$398="rs",$B$398="pct_vgv",$B$398="pct_recebido")),AND($B$395="indireto",$B$396="Stand de vendas",OR($B$398="rs",$B$398="pct_vgv")),AND($B$395="indireto",$B$396="Gestão",OR($B$398="rs",$B$398="pct_vgv",$B$398="pct_recebido")),AND($B$395="indireto",$B$396="Outro",OR($B$398="rs",$B$398="pct_vgv",$B$398="pct_recebido")),AND($B$395="financeiro",$B$396="Juros de financiamento",OR($B$398="rs",$B$398="pct_vgv")),AND($B$395="financeiro",$B$396="Taxas bancárias",OR($B$398="rs",$B$398="pct_vgv")),AND($B$395="financeiro",$B$396="Estruturação de dívida",OR($B$398="rs",$B$398="pct_vgv")),AND($B$395="financeiro",$B$396="Investidores",OR($B$398="rs",$B$398="pct_vgv")),AND($B$395="financeiro",$B$396="Outro",OR($B$398="rs",$B$398="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$399&lt;&gt;"",$B$400&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$398,3)="pct",$B$400="",$B$399=""),"⚠ falta o valor na linha certa","OK")))))</f>
         <v/>
       </c>
       <c r="C853" s="20" t="inlineStr">
         <is>
-          <t>R$</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="D853" s="21" t="inlineStr">
@@ -15813,203 +15813,840 @@
     <row r="854">
       <c r="A854" s="18" t="inlineStr">
         <is>
+          <t>Custo 11 — conferência</t>
+        </is>
+      </c>
+      <c r="B854" s="23">
+        <f>IF(AND($B$406="",$B$407=""),"",IF(OR($B$406="",$B$407="",$B$409=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$406="terreno",$B$407="Preço",OR($B$409="rs",$B$409="rs_m2_terreno")),AND($B$406="terreno",$B$407="Registro",OR($B$409="rs",$B$409="rs_m2_priv")),AND($B$406="terreno",$B$407="Outro",OR($B$409="rs",$B$409="pct_vgv")),AND($B$406="obra",$B$407="Construção",OR($B$409="rs",$B$409="rs_m2_priv")),AND($B$406="obra",$B$407="Outorga",OR($B$409="rs",$B$409="pct_vgv")),AND($B$406="obra",$B$407="Decoração",OR($B$409="rs",$B$409="rs_m2_priv")),AND($B$406="obra",$B$407="Gestão da obra",OR($B$409="rs",$B$409="pct_obra")),AND($B$406="obra",$B$407="Contingência",OR($B$409="rs",$B$409="pct_vgv")),AND($B$406="obra",$B$407="Outro",OR($B$409="rs",$B$409="pct_vgv")),AND($B$406="diretos",$B$407="Marketing &amp; Publicidade",OR($B$409="rs",$B$409="pct_vgv",$B$409="pct_recebido")),AND($B$406="diretos",$B$407="Corretagem de vendas",OR($B$409="pct_vgv")),AND($B$406="diretos",$B$407="Projetos",OR($B$409="rs",$B$409="rs_m2_priv",$B$409="pct_constr")),AND($B$406="diretos",$B$407="Licenças e Aprovações",OR($B$409="rs",$B$409="rs_m2_priv")),AND($B$406="diretos",$B$407="Manutenção pós-obra",OR($B$409="rs",$B$409="pct_vgv",$B$409="pct_recebido")),AND($B$406="diretos",$B$407="Outro",OR($B$409="rs",$B$409="pct_vgv",$B$409="pct_recebido")),AND($B$406="indireto",$B$407="Marketing global",OR($B$409="rs",$B$409="pct_vgv",$B$409="pct_recebido")),AND($B$406="indireto",$B$407="Stand de vendas",OR($B$409="rs",$B$409="pct_vgv")),AND($B$406="indireto",$B$407="Gestão",OR($B$409="rs",$B$409="pct_vgv",$B$409="pct_recebido")),AND($B$406="indireto",$B$407="Outro",OR($B$409="rs",$B$409="pct_vgv",$B$409="pct_recebido")),AND($B$406="financeiro",$B$407="Juros de financiamento",OR($B$409="rs",$B$409="pct_vgv")),AND($B$406="financeiro",$B$407="Taxas bancárias",OR($B$409="rs",$B$409="pct_vgv")),AND($B$406="financeiro",$B$407="Estruturação de dívida",OR($B$409="rs",$B$409="pct_vgv")),AND($B$406="financeiro",$B$407="Investidores",OR($B$409="rs",$B$409="pct_vgv")),AND($B$406="financeiro",$B$407="Outro",OR($B$409="rs",$B$409="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$410&lt;&gt;"",$B$411&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$409,3)="pct",$B$411="",$B$410=""),"⚠ falta o valor na linha certa","OK")))))</f>
+        <v/>
+      </c>
+      <c r="C854" s="20" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="D854" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" s="18" t="inlineStr">
+        <is>
+          <t>Custo 12 — conferência</t>
+        </is>
+      </c>
+      <c r="B855" s="23">
+        <f>IF(AND($B$417="",$B$418=""),"",IF(OR($B$417="",$B$418="",$B$420=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$417="terreno",$B$418="Preço",OR($B$420="rs",$B$420="rs_m2_terreno")),AND($B$417="terreno",$B$418="Registro",OR($B$420="rs",$B$420="rs_m2_priv")),AND($B$417="terreno",$B$418="Outro",OR($B$420="rs",$B$420="pct_vgv")),AND($B$417="obra",$B$418="Construção",OR($B$420="rs",$B$420="rs_m2_priv")),AND($B$417="obra",$B$418="Outorga",OR($B$420="rs",$B$420="pct_vgv")),AND($B$417="obra",$B$418="Decoração",OR($B$420="rs",$B$420="rs_m2_priv")),AND($B$417="obra",$B$418="Gestão da obra",OR($B$420="rs",$B$420="pct_obra")),AND($B$417="obra",$B$418="Contingência",OR($B$420="rs",$B$420="pct_vgv")),AND($B$417="obra",$B$418="Outro",OR($B$420="rs",$B$420="pct_vgv")),AND($B$417="diretos",$B$418="Marketing &amp; Publicidade",OR($B$420="rs",$B$420="pct_vgv",$B$420="pct_recebido")),AND($B$417="diretos",$B$418="Corretagem de vendas",OR($B$420="pct_vgv")),AND($B$417="diretos",$B$418="Projetos",OR($B$420="rs",$B$420="rs_m2_priv",$B$420="pct_constr")),AND($B$417="diretos",$B$418="Licenças e Aprovações",OR($B$420="rs",$B$420="rs_m2_priv")),AND($B$417="diretos",$B$418="Manutenção pós-obra",OR($B$420="rs",$B$420="pct_vgv",$B$420="pct_recebido")),AND($B$417="diretos",$B$418="Outro",OR($B$420="rs",$B$420="pct_vgv",$B$420="pct_recebido")),AND($B$417="indireto",$B$418="Marketing global",OR($B$420="rs",$B$420="pct_vgv",$B$420="pct_recebido")),AND($B$417="indireto",$B$418="Stand de vendas",OR($B$420="rs",$B$420="pct_vgv")),AND($B$417="indireto",$B$418="Gestão",OR($B$420="rs",$B$420="pct_vgv",$B$420="pct_recebido")),AND($B$417="indireto",$B$418="Outro",OR($B$420="rs",$B$420="pct_vgv",$B$420="pct_recebido")),AND($B$417="financeiro",$B$418="Juros de financiamento",OR($B$420="rs",$B$420="pct_vgv")),AND($B$417="financeiro",$B$418="Taxas bancárias",OR($B$420="rs",$B$420="pct_vgv")),AND($B$417="financeiro",$B$418="Estruturação de dívida",OR($B$420="rs",$B$420="pct_vgv")),AND($B$417="financeiro",$B$418="Investidores",OR($B$420="rs",$B$420="pct_vgv")),AND($B$417="financeiro",$B$418="Outro",OR($B$420="rs",$B$420="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$421&lt;&gt;"",$B$422&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$420,3)="pct",$B$422="",$B$421=""),"⚠ falta o valor na linha certa","OK")))))</f>
+        <v/>
+      </c>
+      <c r="C855" s="20" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="D855" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" s="18" t="inlineStr">
+        <is>
+          <t>Custo 13 — conferência</t>
+        </is>
+      </c>
+      <c r="B856" s="23">
+        <f>IF(AND($B$428="",$B$429=""),"",IF(OR($B$428="",$B$429="",$B$431=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$428="terreno",$B$429="Preço",OR($B$431="rs",$B$431="rs_m2_terreno")),AND($B$428="terreno",$B$429="Registro",OR($B$431="rs",$B$431="rs_m2_priv")),AND($B$428="terreno",$B$429="Outro",OR($B$431="rs",$B$431="pct_vgv")),AND($B$428="obra",$B$429="Construção",OR($B$431="rs",$B$431="rs_m2_priv")),AND($B$428="obra",$B$429="Outorga",OR($B$431="rs",$B$431="pct_vgv")),AND($B$428="obra",$B$429="Decoração",OR($B$431="rs",$B$431="rs_m2_priv")),AND($B$428="obra",$B$429="Gestão da obra",OR($B$431="rs",$B$431="pct_obra")),AND($B$428="obra",$B$429="Contingência",OR($B$431="rs",$B$431="pct_vgv")),AND($B$428="obra",$B$429="Outro",OR($B$431="rs",$B$431="pct_vgv")),AND($B$428="diretos",$B$429="Marketing &amp; Publicidade",OR($B$431="rs",$B$431="pct_vgv",$B$431="pct_recebido")),AND($B$428="diretos",$B$429="Corretagem de vendas",OR($B$431="pct_vgv")),AND($B$428="diretos",$B$429="Projetos",OR($B$431="rs",$B$431="rs_m2_priv",$B$431="pct_constr")),AND($B$428="diretos",$B$429="Licenças e Aprovações",OR($B$431="rs",$B$431="rs_m2_priv")),AND($B$428="diretos",$B$429="Manutenção pós-obra",OR($B$431="rs",$B$431="pct_vgv",$B$431="pct_recebido")),AND($B$428="diretos",$B$429="Outro",OR($B$431="rs",$B$431="pct_vgv",$B$431="pct_recebido")),AND($B$428="indireto",$B$429="Marketing global",OR($B$431="rs",$B$431="pct_vgv",$B$431="pct_recebido")),AND($B$428="indireto",$B$429="Stand de vendas",OR($B$431="rs",$B$431="pct_vgv")),AND($B$428="indireto",$B$429="Gestão",OR($B$431="rs",$B$431="pct_vgv",$B$431="pct_recebido")),AND($B$428="indireto",$B$429="Outro",OR($B$431="rs",$B$431="pct_vgv",$B$431="pct_recebido")),AND($B$428="financeiro",$B$429="Juros de financiamento",OR($B$431="rs",$B$431="pct_vgv")),AND($B$428="financeiro",$B$429="Taxas bancárias",OR($B$431="rs",$B$431="pct_vgv")),AND($B$428="financeiro",$B$429="Estruturação de dívida",OR($B$431="rs",$B$431="pct_vgv")),AND($B$428="financeiro",$B$429="Investidores",OR($B$431="rs",$B$431="pct_vgv")),AND($B$428="financeiro",$B$429="Outro",OR($B$431="rs",$B$431="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$432&lt;&gt;"",$B$433&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$431,3)="pct",$B$433="",$B$432=""),"⚠ falta o valor na linha certa","OK")))))</f>
+        <v/>
+      </c>
+      <c r="C856" s="20" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="D856" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" s="18" t="inlineStr">
+        <is>
+          <t>Custo 14 — conferência</t>
+        </is>
+      </c>
+      <c r="B857" s="23">
+        <f>IF(AND($B$439="",$B$440=""),"",IF(OR($B$439="",$B$440="",$B$442=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$439="terreno",$B$440="Preço",OR($B$442="rs",$B$442="rs_m2_terreno")),AND($B$439="terreno",$B$440="Registro",OR($B$442="rs",$B$442="rs_m2_priv")),AND($B$439="terreno",$B$440="Outro",OR($B$442="rs",$B$442="pct_vgv")),AND($B$439="obra",$B$440="Construção",OR($B$442="rs",$B$442="rs_m2_priv")),AND($B$439="obra",$B$440="Outorga",OR($B$442="rs",$B$442="pct_vgv")),AND($B$439="obra",$B$440="Decoração",OR($B$442="rs",$B$442="rs_m2_priv")),AND($B$439="obra",$B$440="Gestão da obra",OR($B$442="rs",$B$442="pct_obra")),AND($B$439="obra",$B$440="Contingência",OR($B$442="rs",$B$442="pct_vgv")),AND($B$439="obra",$B$440="Outro",OR($B$442="rs",$B$442="pct_vgv")),AND($B$439="diretos",$B$440="Marketing &amp; Publicidade",OR($B$442="rs",$B$442="pct_vgv",$B$442="pct_recebido")),AND($B$439="diretos",$B$440="Corretagem de vendas",OR($B$442="pct_vgv")),AND($B$439="diretos",$B$440="Projetos",OR($B$442="rs",$B$442="rs_m2_priv",$B$442="pct_constr")),AND($B$439="diretos",$B$440="Licenças e Aprovações",OR($B$442="rs",$B$442="rs_m2_priv")),AND($B$439="diretos",$B$440="Manutenção pós-obra",OR($B$442="rs",$B$442="pct_vgv",$B$442="pct_recebido")),AND($B$439="diretos",$B$440="Outro",OR($B$442="rs",$B$442="pct_vgv",$B$442="pct_recebido")),AND($B$439="indireto",$B$440="Marketing global",OR($B$442="rs",$B$442="pct_vgv",$B$442="pct_recebido")),AND($B$439="indireto",$B$440="Stand de vendas",OR($B$442="rs",$B$442="pct_vgv")),AND($B$439="indireto",$B$440="Gestão",OR($B$442="rs",$B$442="pct_vgv",$B$442="pct_recebido")),AND($B$439="indireto",$B$440="Outro",OR($B$442="rs",$B$442="pct_vgv",$B$442="pct_recebido")),AND($B$439="financeiro",$B$440="Juros de financiamento",OR($B$442="rs",$B$442="pct_vgv")),AND($B$439="financeiro",$B$440="Taxas bancárias",OR($B$442="rs",$B$442="pct_vgv")),AND($B$439="financeiro",$B$440="Estruturação de dívida",OR($B$442="rs",$B$442="pct_vgv")),AND($B$439="financeiro",$B$440="Investidores",OR($B$442="rs",$B$442="pct_vgv")),AND($B$439="financeiro",$B$440="Outro",OR($B$442="rs",$B$442="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$443&lt;&gt;"",$B$444&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$442,3)="pct",$B$444="",$B$443=""),"⚠ falta o valor na linha certa","OK")))))</f>
+        <v/>
+      </c>
+      <c r="C857" s="20" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="D857" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" s="18" t="inlineStr">
+        <is>
+          <t>Custo 15 — conferência</t>
+        </is>
+      </c>
+      <c r="B858" s="23">
+        <f>IF(AND($B$450="",$B$451=""),"",IF(OR($B$450="",$B$451="",$B$453=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$450="terreno",$B$451="Preço",OR($B$453="rs",$B$453="rs_m2_terreno")),AND($B$450="terreno",$B$451="Registro",OR($B$453="rs",$B$453="rs_m2_priv")),AND($B$450="terreno",$B$451="Outro",OR($B$453="rs",$B$453="pct_vgv")),AND($B$450="obra",$B$451="Construção",OR($B$453="rs",$B$453="rs_m2_priv")),AND($B$450="obra",$B$451="Outorga",OR($B$453="rs",$B$453="pct_vgv")),AND($B$450="obra",$B$451="Decoração",OR($B$453="rs",$B$453="rs_m2_priv")),AND($B$450="obra",$B$451="Gestão da obra",OR($B$453="rs",$B$453="pct_obra")),AND($B$450="obra",$B$451="Contingência",OR($B$453="rs",$B$453="pct_vgv")),AND($B$450="obra",$B$451="Outro",OR($B$453="rs",$B$453="pct_vgv")),AND($B$450="diretos",$B$451="Marketing &amp; Publicidade",OR($B$453="rs",$B$453="pct_vgv",$B$453="pct_recebido")),AND($B$450="diretos",$B$451="Corretagem de vendas",OR($B$453="pct_vgv")),AND($B$450="diretos",$B$451="Projetos",OR($B$453="rs",$B$453="rs_m2_priv",$B$453="pct_constr")),AND($B$450="diretos",$B$451="Licenças e Aprovações",OR($B$453="rs",$B$453="rs_m2_priv")),AND($B$450="diretos",$B$451="Manutenção pós-obra",OR($B$453="rs",$B$453="pct_vgv",$B$453="pct_recebido")),AND($B$450="diretos",$B$451="Outro",OR($B$453="rs",$B$453="pct_vgv",$B$453="pct_recebido")),AND($B$450="indireto",$B$451="Marketing global",OR($B$453="rs",$B$453="pct_vgv",$B$453="pct_recebido")),AND($B$450="indireto",$B$451="Stand de vendas",OR($B$453="rs",$B$453="pct_vgv")),AND($B$450="indireto",$B$451="Gestão",OR($B$453="rs",$B$453="pct_vgv",$B$453="pct_recebido")),AND($B$450="indireto",$B$451="Outro",OR($B$453="rs",$B$453="pct_vgv",$B$453="pct_recebido")),AND($B$450="financeiro",$B$451="Juros de financiamento",OR($B$453="rs",$B$453="pct_vgv")),AND($B$450="financeiro",$B$451="Taxas bancárias",OR($B$453="rs",$B$453="pct_vgv")),AND($B$450="financeiro",$B$451="Estruturação de dívida",OR($B$453="rs",$B$453="pct_vgv")),AND($B$450="financeiro",$B$451="Investidores",OR($B$453="rs",$B$453="pct_vgv")),AND($B$450="financeiro",$B$451="Outro",OR($B$453="rs",$B$453="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$454&lt;&gt;"",$B$455&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$453,3)="pct",$B$455="",$B$454=""),"⚠ falta o valor na linha certa","OK")))))</f>
+        <v/>
+      </c>
+      <c r="C858" s="20" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="D858" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" s="18" t="inlineStr">
+        <is>
+          <t>Custo 16 — conferência</t>
+        </is>
+      </c>
+      <c r="B859" s="23">
+        <f>IF(AND($B$461="",$B$462=""),"",IF(OR($B$461="",$B$462="",$B$464=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$461="terreno",$B$462="Preço",OR($B$464="rs",$B$464="rs_m2_terreno")),AND($B$461="terreno",$B$462="Registro",OR($B$464="rs",$B$464="rs_m2_priv")),AND($B$461="terreno",$B$462="Outro",OR($B$464="rs",$B$464="pct_vgv")),AND($B$461="obra",$B$462="Construção",OR($B$464="rs",$B$464="rs_m2_priv")),AND($B$461="obra",$B$462="Outorga",OR($B$464="rs",$B$464="pct_vgv")),AND($B$461="obra",$B$462="Decoração",OR($B$464="rs",$B$464="rs_m2_priv")),AND($B$461="obra",$B$462="Gestão da obra",OR($B$464="rs",$B$464="pct_obra")),AND($B$461="obra",$B$462="Contingência",OR($B$464="rs",$B$464="pct_vgv")),AND($B$461="obra",$B$462="Outro",OR($B$464="rs",$B$464="pct_vgv")),AND($B$461="diretos",$B$462="Marketing &amp; Publicidade",OR($B$464="rs",$B$464="pct_vgv",$B$464="pct_recebido")),AND($B$461="diretos",$B$462="Corretagem de vendas",OR($B$464="pct_vgv")),AND($B$461="diretos",$B$462="Projetos",OR($B$464="rs",$B$464="rs_m2_priv",$B$464="pct_constr")),AND($B$461="diretos",$B$462="Licenças e Aprovações",OR($B$464="rs",$B$464="rs_m2_priv")),AND($B$461="diretos",$B$462="Manutenção pós-obra",OR($B$464="rs",$B$464="pct_vgv",$B$464="pct_recebido")),AND($B$461="diretos",$B$462="Outro",OR($B$464="rs",$B$464="pct_vgv",$B$464="pct_recebido")),AND($B$461="indireto",$B$462="Marketing global",OR($B$464="rs",$B$464="pct_vgv",$B$464="pct_recebido")),AND($B$461="indireto",$B$462="Stand de vendas",OR($B$464="rs",$B$464="pct_vgv")),AND($B$461="indireto",$B$462="Gestão",OR($B$464="rs",$B$464="pct_vgv",$B$464="pct_recebido")),AND($B$461="indireto",$B$462="Outro",OR($B$464="rs",$B$464="pct_vgv",$B$464="pct_recebido")),AND($B$461="financeiro",$B$462="Juros de financiamento",OR($B$464="rs",$B$464="pct_vgv")),AND($B$461="financeiro",$B$462="Taxas bancárias",OR($B$464="rs",$B$464="pct_vgv")),AND($B$461="financeiro",$B$462="Estruturação de dívida",OR($B$464="rs",$B$464="pct_vgv")),AND($B$461="financeiro",$B$462="Investidores",OR($B$464="rs",$B$464="pct_vgv")),AND($B$461="financeiro",$B$462="Outro",OR($B$464="rs",$B$464="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$465&lt;&gt;"",$B$466&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$464,3)="pct",$B$466="",$B$465=""),"⚠ falta o valor na linha certa","OK")))))</f>
+        <v/>
+      </c>
+      <c r="C859" s="20" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="D859" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" s="18" t="inlineStr">
+        <is>
+          <t>Custo 17 — conferência</t>
+        </is>
+      </c>
+      <c r="B860" s="23">
+        <f>IF(AND($B$472="",$B$473=""),"",IF(OR($B$472="",$B$473="",$B$475=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$472="terreno",$B$473="Preço",OR($B$475="rs",$B$475="rs_m2_terreno")),AND($B$472="terreno",$B$473="Registro",OR($B$475="rs",$B$475="rs_m2_priv")),AND($B$472="terreno",$B$473="Outro",OR($B$475="rs",$B$475="pct_vgv")),AND($B$472="obra",$B$473="Construção",OR($B$475="rs",$B$475="rs_m2_priv")),AND($B$472="obra",$B$473="Outorga",OR($B$475="rs",$B$475="pct_vgv")),AND($B$472="obra",$B$473="Decoração",OR($B$475="rs",$B$475="rs_m2_priv")),AND($B$472="obra",$B$473="Gestão da obra",OR($B$475="rs",$B$475="pct_obra")),AND($B$472="obra",$B$473="Contingência",OR($B$475="rs",$B$475="pct_vgv")),AND($B$472="obra",$B$473="Outro",OR($B$475="rs",$B$475="pct_vgv")),AND($B$472="diretos",$B$473="Marketing &amp; Publicidade",OR($B$475="rs",$B$475="pct_vgv",$B$475="pct_recebido")),AND($B$472="diretos",$B$473="Corretagem de vendas",OR($B$475="pct_vgv")),AND($B$472="diretos",$B$473="Projetos",OR($B$475="rs",$B$475="rs_m2_priv",$B$475="pct_constr")),AND($B$472="diretos",$B$473="Licenças e Aprovações",OR($B$475="rs",$B$475="rs_m2_priv")),AND($B$472="diretos",$B$473="Manutenção pós-obra",OR($B$475="rs",$B$475="pct_vgv",$B$475="pct_recebido")),AND($B$472="diretos",$B$473="Outro",OR($B$475="rs",$B$475="pct_vgv",$B$475="pct_recebido")),AND($B$472="indireto",$B$473="Marketing global",OR($B$475="rs",$B$475="pct_vgv",$B$475="pct_recebido")),AND($B$472="indireto",$B$473="Stand de vendas",OR($B$475="rs",$B$475="pct_vgv")),AND($B$472="indireto",$B$473="Gestão",OR($B$475="rs",$B$475="pct_vgv",$B$475="pct_recebido")),AND($B$472="indireto",$B$473="Outro",OR($B$475="rs",$B$475="pct_vgv",$B$475="pct_recebido")),AND($B$472="financeiro",$B$473="Juros de financiamento",OR($B$475="rs",$B$475="pct_vgv")),AND($B$472="financeiro",$B$473="Taxas bancárias",OR($B$475="rs",$B$475="pct_vgv")),AND($B$472="financeiro",$B$473="Estruturação de dívida",OR($B$475="rs",$B$475="pct_vgv")),AND($B$472="financeiro",$B$473="Investidores",OR($B$475="rs",$B$475="pct_vgv")),AND($B$472="financeiro",$B$473="Outro",OR($B$475="rs",$B$475="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$476&lt;&gt;"",$B$477&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$475,3)="pct",$B$477="",$B$476=""),"⚠ falta o valor na linha certa","OK")))))</f>
+        <v/>
+      </c>
+      <c r="C860" s="20" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="D860" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" s="18" t="inlineStr">
+        <is>
+          <t>Custo 18 — conferência</t>
+        </is>
+      </c>
+      <c r="B861" s="23">
+        <f>IF(AND($B$483="",$B$484=""),"",IF(OR($B$483="",$B$484="",$B$486=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$483="terreno",$B$484="Preço",OR($B$486="rs",$B$486="rs_m2_terreno")),AND($B$483="terreno",$B$484="Registro",OR($B$486="rs",$B$486="rs_m2_priv")),AND($B$483="terreno",$B$484="Outro",OR($B$486="rs",$B$486="pct_vgv")),AND($B$483="obra",$B$484="Construção",OR($B$486="rs",$B$486="rs_m2_priv")),AND($B$483="obra",$B$484="Outorga",OR($B$486="rs",$B$486="pct_vgv")),AND($B$483="obra",$B$484="Decoração",OR($B$486="rs",$B$486="rs_m2_priv")),AND($B$483="obra",$B$484="Gestão da obra",OR($B$486="rs",$B$486="pct_obra")),AND($B$483="obra",$B$484="Contingência",OR($B$486="rs",$B$486="pct_vgv")),AND($B$483="obra",$B$484="Outro",OR($B$486="rs",$B$486="pct_vgv")),AND($B$483="diretos",$B$484="Marketing &amp; Publicidade",OR($B$486="rs",$B$486="pct_vgv",$B$486="pct_recebido")),AND($B$483="diretos",$B$484="Corretagem de vendas",OR($B$486="pct_vgv")),AND($B$483="diretos",$B$484="Projetos",OR($B$486="rs",$B$486="rs_m2_priv",$B$486="pct_constr")),AND($B$483="diretos",$B$484="Licenças e Aprovações",OR($B$486="rs",$B$486="rs_m2_priv")),AND($B$483="diretos",$B$484="Manutenção pós-obra",OR($B$486="rs",$B$486="pct_vgv",$B$486="pct_recebido")),AND($B$483="diretos",$B$484="Outro",OR($B$486="rs",$B$486="pct_vgv",$B$486="pct_recebido")),AND($B$483="indireto",$B$484="Marketing global",OR($B$486="rs",$B$486="pct_vgv",$B$486="pct_recebido")),AND($B$483="indireto",$B$484="Stand de vendas",OR($B$486="rs",$B$486="pct_vgv")),AND($B$483="indireto",$B$484="Gestão",OR($B$486="rs",$B$486="pct_vgv",$B$486="pct_recebido")),AND($B$483="indireto",$B$484="Outro",OR($B$486="rs",$B$486="pct_vgv",$B$486="pct_recebido")),AND($B$483="financeiro",$B$484="Juros de financiamento",OR($B$486="rs",$B$486="pct_vgv")),AND($B$483="financeiro",$B$484="Taxas bancárias",OR($B$486="rs",$B$486="pct_vgv")),AND($B$483="financeiro",$B$484="Estruturação de dívida",OR($B$486="rs",$B$486="pct_vgv")),AND($B$483="financeiro",$B$484="Investidores",OR($B$486="rs",$B$486="pct_vgv")),AND($B$483="financeiro",$B$484="Outro",OR($B$486="rs",$B$486="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$487&lt;&gt;"",$B$488&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$486,3)="pct",$B$488="",$B$487=""),"⚠ falta o valor na linha certa","OK")))))</f>
+        <v/>
+      </c>
+      <c r="C861" s="20" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="D861" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" s="18" t="inlineStr">
+        <is>
+          <t>Custo 19 — conferência</t>
+        </is>
+      </c>
+      <c r="B862" s="23">
+        <f>IF(AND($B$494="",$B$495=""),"",IF(OR($B$494="",$B$495="",$B$497=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$494="terreno",$B$495="Preço",OR($B$497="rs",$B$497="rs_m2_terreno")),AND($B$494="terreno",$B$495="Registro",OR($B$497="rs",$B$497="rs_m2_priv")),AND($B$494="terreno",$B$495="Outro",OR($B$497="rs",$B$497="pct_vgv")),AND($B$494="obra",$B$495="Construção",OR($B$497="rs",$B$497="rs_m2_priv")),AND($B$494="obra",$B$495="Outorga",OR($B$497="rs",$B$497="pct_vgv")),AND($B$494="obra",$B$495="Decoração",OR($B$497="rs",$B$497="rs_m2_priv")),AND($B$494="obra",$B$495="Gestão da obra",OR($B$497="rs",$B$497="pct_obra")),AND($B$494="obra",$B$495="Contingência",OR($B$497="rs",$B$497="pct_vgv")),AND($B$494="obra",$B$495="Outro",OR($B$497="rs",$B$497="pct_vgv")),AND($B$494="diretos",$B$495="Marketing &amp; Publicidade",OR($B$497="rs",$B$497="pct_vgv",$B$497="pct_recebido")),AND($B$494="diretos",$B$495="Corretagem de vendas",OR($B$497="pct_vgv")),AND($B$494="diretos",$B$495="Projetos",OR($B$497="rs",$B$497="rs_m2_priv",$B$497="pct_constr")),AND($B$494="diretos",$B$495="Licenças e Aprovações",OR($B$497="rs",$B$497="rs_m2_priv")),AND($B$494="diretos",$B$495="Manutenção pós-obra",OR($B$497="rs",$B$497="pct_vgv",$B$497="pct_recebido")),AND($B$494="diretos",$B$495="Outro",OR($B$497="rs",$B$497="pct_vgv",$B$497="pct_recebido")),AND($B$494="indireto",$B$495="Marketing global",OR($B$497="rs",$B$497="pct_vgv",$B$497="pct_recebido")),AND($B$494="indireto",$B$495="Stand de vendas",OR($B$497="rs",$B$497="pct_vgv")),AND($B$494="indireto",$B$495="Gestão",OR($B$497="rs",$B$497="pct_vgv",$B$497="pct_recebido")),AND($B$494="indireto",$B$495="Outro",OR($B$497="rs",$B$497="pct_vgv",$B$497="pct_recebido")),AND($B$494="financeiro",$B$495="Juros de financiamento",OR($B$497="rs",$B$497="pct_vgv")),AND($B$494="financeiro",$B$495="Taxas bancárias",OR($B$497="rs",$B$497="pct_vgv")),AND($B$494="financeiro",$B$495="Estruturação de dívida",OR($B$497="rs",$B$497="pct_vgv")),AND($B$494="financeiro",$B$495="Investidores",OR($B$497="rs",$B$497="pct_vgv")),AND($B$494="financeiro",$B$495="Outro",OR($B$497="rs",$B$497="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$498&lt;&gt;"",$B$499&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$497,3)="pct",$B$499="",$B$498=""),"⚠ falta o valor na linha certa","OK")))))</f>
+        <v/>
+      </c>
+      <c r="C862" s="20" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="D862" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" s="18" t="inlineStr">
+        <is>
+          <t>Custo 20 — conferência</t>
+        </is>
+      </c>
+      <c r="B863" s="23">
+        <f>IF(AND($B$505="",$B$506=""),"",IF(OR($B$505="",$B$506="",$B$508=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$505="terreno",$B$506="Preço",OR($B$508="rs",$B$508="rs_m2_terreno")),AND($B$505="terreno",$B$506="Registro",OR($B$508="rs",$B$508="rs_m2_priv")),AND($B$505="terreno",$B$506="Outro",OR($B$508="rs",$B$508="pct_vgv")),AND($B$505="obra",$B$506="Construção",OR($B$508="rs",$B$508="rs_m2_priv")),AND($B$505="obra",$B$506="Outorga",OR($B$508="rs",$B$508="pct_vgv")),AND($B$505="obra",$B$506="Decoração",OR($B$508="rs",$B$508="rs_m2_priv")),AND($B$505="obra",$B$506="Gestão da obra",OR($B$508="rs",$B$508="pct_obra")),AND($B$505="obra",$B$506="Contingência",OR($B$508="rs",$B$508="pct_vgv")),AND($B$505="obra",$B$506="Outro",OR($B$508="rs",$B$508="pct_vgv")),AND($B$505="diretos",$B$506="Marketing &amp; Publicidade",OR($B$508="rs",$B$508="pct_vgv",$B$508="pct_recebido")),AND($B$505="diretos",$B$506="Corretagem de vendas",OR($B$508="pct_vgv")),AND($B$505="diretos",$B$506="Projetos",OR($B$508="rs",$B$508="rs_m2_priv",$B$508="pct_constr")),AND($B$505="diretos",$B$506="Licenças e Aprovações",OR($B$508="rs",$B$508="rs_m2_priv")),AND($B$505="diretos",$B$506="Manutenção pós-obra",OR($B$508="rs",$B$508="pct_vgv",$B$508="pct_recebido")),AND($B$505="diretos",$B$506="Outro",OR($B$508="rs",$B$508="pct_vgv",$B$508="pct_recebido")),AND($B$505="indireto",$B$506="Marketing global",OR($B$508="rs",$B$508="pct_vgv",$B$508="pct_recebido")),AND($B$505="indireto",$B$506="Stand de vendas",OR($B$508="rs",$B$508="pct_vgv")),AND($B$505="indireto",$B$506="Gestão",OR($B$508="rs",$B$508="pct_vgv",$B$508="pct_recebido")),AND($B$505="indireto",$B$506="Outro",OR($B$508="rs",$B$508="pct_vgv",$B$508="pct_recebido")),AND($B$505="financeiro",$B$506="Juros de financiamento",OR($B$508="rs",$B$508="pct_vgv")),AND($B$505="financeiro",$B$506="Taxas bancárias",OR($B$508="rs",$B$508="pct_vgv")),AND($B$505="financeiro",$B$506="Estruturação de dívida",OR($B$508="rs",$B$508="pct_vgv")),AND($B$505="financeiro",$B$506="Investidores",OR($B$508="rs",$B$508="pct_vgv")),AND($B$505="financeiro",$B$506="Outro",OR($B$508="rs",$B$508="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$509&lt;&gt;"",$B$510&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$508,3)="pct",$B$510="",$B$509=""),"⚠ falta o valor na linha certa","OK")))))</f>
+        <v/>
+      </c>
+      <c r="C863" s="20" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="D863" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" s="18" t="inlineStr">
+        <is>
+          <t>Custo 21 — conferência</t>
+        </is>
+      </c>
+      <c r="B864" s="23">
+        <f>IF(AND($B$516="",$B$517=""),"",IF(OR($B$516="",$B$517="",$B$519=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$516="terreno",$B$517="Preço",OR($B$519="rs",$B$519="rs_m2_terreno")),AND($B$516="terreno",$B$517="Registro",OR($B$519="rs",$B$519="rs_m2_priv")),AND($B$516="terreno",$B$517="Outro",OR($B$519="rs",$B$519="pct_vgv")),AND($B$516="obra",$B$517="Construção",OR($B$519="rs",$B$519="rs_m2_priv")),AND($B$516="obra",$B$517="Outorga",OR($B$519="rs",$B$519="pct_vgv")),AND($B$516="obra",$B$517="Decoração",OR($B$519="rs",$B$519="rs_m2_priv")),AND($B$516="obra",$B$517="Gestão da obra",OR($B$519="rs",$B$519="pct_obra")),AND($B$516="obra",$B$517="Contingência",OR($B$519="rs",$B$519="pct_vgv")),AND($B$516="obra",$B$517="Outro",OR($B$519="rs",$B$519="pct_vgv")),AND($B$516="diretos",$B$517="Marketing &amp; Publicidade",OR($B$519="rs",$B$519="pct_vgv",$B$519="pct_recebido")),AND($B$516="diretos",$B$517="Corretagem de vendas",OR($B$519="pct_vgv")),AND($B$516="diretos",$B$517="Projetos",OR($B$519="rs",$B$519="rs_m2_priv",$B$519="pct_constr")),AND($B$516="diretos",$B$517="Licenças e Aprovações",OR($B$519="rs",$B$519="rs_m2_priv")),AND($B$516="diretos",$B$517="Manutenção pós-obra",OR($B$519="rs",$B$519="pct_vgv",$B$519="pct_recebido")),AND($B$516="diretos",$B$517="Outro",OR($B$519="rs",$B$519="pct_vgv",$B$519="pct_recebido")),AND($B$516="indireto",$B$517="Marketing global",OR($B$519="rs",$B$519="pct_vgv",$B$519="pct_recebido")),AND($B$516="indireto",$B$517="Stand de vendas",OR($B$519="rs",$B$519="pct_vgv")),AND($B$516="indireto",$B$517="Gestão",OR($B$519="rs",$B$519="pct_vgv",$B$519="pct_recebido")),AND($B$516="indireto",$B$517="Outro",OR($B$519="rs",$B$519="pct_vgv",$B$519="pct_recebido")),AND($B$516="financeiro",$B$517="Juros de financiamento",OR($B$519="rs",$B$519="pct_vgv")),AND($B$516="financeiro",$B$517="Taxas bancárias",OR($B$519="rs",$B$519="pct_vgv")),AND($B$516="financeiro",$B$517="Estruturação de dívida",OR($B$519="rs",$B$519="pct_vgv")),AND($B$516="financeiro",$B$517="Investidores",OR($B$519="rs",$B$519="pct_vgv")),AND($B$516="financeiro",$B$517="Outro",OR($B$519="rs",$B$519="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$520&lt;&gt;"",$B$521&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$519,3)="pct",$B$521="",$B$520=""),"⚠ falta o valor na linha certa","OK")))))</f>
+        <v/>
+      </c>
+      <c r="C864" s="20" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="D864" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" s="18" t="inlineStr">
+        <is>
+          <t>Custo 22 — conferência</t>
+        </is>
+      </c>
+      <c r="B865" s="23">
+        <f>IF(AND($B$527="",$B$528=""),"",IF(OR($B$527="",$B$528="",$B$530=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$527="terreno",$B$528="Preço",OR($B$530="rs",$B$530="rs_m2_terreno")),AND($B$527="terreno",$B$528="Registro",OR($B$530="rs",$B$530="rs_m2_priv")),AND($B$527="terreno",$B$528="Outro",OR($B$530="rs",$B$530="pct_vgv")),AND($B$527="obra",$B$528="Construção",OR($B$530="rs",$B$530="rs_m2_priv")),AND($B$527="obra",$B$528="Outorga",OR($B$530="rs",$B$530="pct_vgv")),AND($B$527="obra",$B$528="Decoração",OR($B$530="rs",$B$530="rs_m2_priv")),AND($B$527="obra",$B$528="Gestão da obra",OR($B$530="rs",$B$530="pct_obra")),AND($B$527="obra",$B$528="Contingência",OR($B$530="rs",$B$530="pct_vgv")),AND($B$527="obra",$B$528="Outro",OR($B$530="rs",$B$530="pct_vgv")),AND($B$527="diretos",$B$528="Marketing &amp; Publicidade",OR($B$530="rs",$B$530="pct_vgv",$B$530="pct_recebido")),AND($B$527="diretos",$B$528="Corretagem de vendas",OR($B$530="pct_vgv")),AND($B$527="diretos",$B$528="Projetos",OR($B$530="rs",$B$530="rs_m2_priv",$B$530="pct_constr")),AND($B$527="diretos",$B$528="Licenças e Aprovações",OR($B$530="rs",$B$530="rs_m2_priv")),AND($B$527="diretos",$B$528="Manutenção pós-obra",OR($B$530="rs",$B$530="pct_vgv",$B$530="pct_recebido")),AND($B$527="diretos",$B$528="Outro",OR($B$530="rs",$B$530="pct_vgv",$B$530="pct_recebido")),AND($B$527="indireto",$B$528="Marketing global",OR($B$530="rs",$B$530="pct_vgv",$B$530="pct_recebido")),AND($B$527="indireto",$B$528="Stand de vendas",OR($B$530="rs",$B$530="pct_vgv")),AND($B$527="indireto",$B$528="Gestão",OR($B$530="rs",$B$530="pct_vgv",$B$530="pct_recebido")),AND($B$527="indireto",$B$528="Outro",OR($B$530="rs",$B$530="pct_vgv",$B$530="pct_recebido")),AND($B$527="financeiro",$B$528="Juros de financiamento",OR($B$530="rs",$B$530="pct_vgv")),AND($B$527="financeiro",$B$528="Taxas bancárias",OR($B$530="rs",$B$530="pct_vgv")),AND($B$527="financeiro",$B$528="Estruturação de dívida",OR($B$530="rs",$B$530="pct_vgv")),AND($B$527="financeiro",$B$528="Investidores",OR($B$530="rs",$B$530="pct_vgv")),AND($B$527="financeiro",$B$528="Outro",OR($B$530="rs",$B$530="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$531&lt;&gt;"",$B$532&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$530,3)="pct",$B$532="",$B$531=""),"⚠ falta o valor na linha certa","OK")))))</f>
+        <v/>
+      </c>
+      <c r="C865" s="20" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="D865" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" s="18" t="inlineStr">
+        <is>
+          <t>Custo 23 — conferência</t>
+        </is>
+      </c>
+      <c r="B866" s="23">
+        <f>IF(AND($B$538="",$B$539=""),"",IF(OR($B$538="",$B$539="",$B$541=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$538="terreno",$B$539="Preço",OR($B$541="rs",$B$541="rs_m2_terreno")),AND($B$538="terreno",$B$539="Registro",OR($B$541="rs",$B$541="rs_m2_priv")),AND($B$538="terreno",$B$539="Outro",OR($B$541="rs",$B$541="pct_vgv")),AND($B$538="obra",$B$539="Construção",OR($B$541="rs",$B$541="rs_m2_priv")),AND($B$538="obra",$B$539="Outorga",OR($B$541="rs",$B$541="pct_vgv")),AND($B$538="obra",$B$539="Decoração",OR($B$541="rs",$B$541="rs_m2_priv")),AND($B$538="obra",$B$539="Gestão da obra",OR($B$541="rs",$B$541="pct_obra")),AND($B$538="obra",$B$539="Contingência",OR($B$541="rs",$B$541="pct_vgv")),AND($B$538="obra",$B$539="Outro",OR($B$541="rs",$B$541="pct_vgv")),AND($B$538="diretos",$B$539="Marketing &amp; Publicidade",OR($B$541="rs",$B$541="pct_vgv",$B$541="pct_recebido")),AND($B$538="diretos",$B$539="Corretagem de vendas",OR($B$541="pct_vgv")),AND($B$538="diretos",$B$539="Projetos",OR($B$541="rs",$B$541="rs_m2_priv",$B$541="pct_constr")),AND($B$538="diretos",$B$539="Licenças e Aprovações",OR($B$541="rs",$B$541="rs_m2_priv")),AND($B$538="diretos",$B$539="Manutenção pós-obra",OR($B$541="rs",$B$541="pct_vgv",$B$541="pct_recebido")),AND($B$538="diretos",$B$539="Outro",OR($B$541="rs",$B$541="pct_vgv",$B$541="pct_recebido")),AND($B$538="indireto",$B$539="Marketing global",OR($B$541="rs",$B$541="pct_vgv",$B$541="pct_recebido")),AND($B$538="indireto",$B$539="Stand de vendas",OR($B$541="rs",$B$541="pct_vgv")),AND($B$538="indireto",$B$539="Gestão",OR($B$541="rs",$B$541="pct_vgv",$B$541="pct_recebido")),AND($B$538="indireto",$B$539="Outro",OR($B$541="rs",$B$541="pct_vgv",$B$541="pct_recebido")),AND($B$538="financeiro",$B$539="Juros de financiamento",OR($B$541="rs",$B$541="pct_vgv")),AND($B$538="financeiro",$B$539="Taxas bancárias",OR($B$541="rs",$B$541="pct_vgv")),AND($B$538="financeiro",$B$539="Estruturação de dívida",OR($B$541="rs",$B$541="pct_vgv")),AND($B$538="financeiro",$B$539="Investidores",OR($B$541="rs",$B$541="pct_vgv")),AND($B$538="financeiro",$B$539="Outro",OR($B$541="rs",$B$541="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$542&lt;&gt;"",$B$543&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$541,3)="pct",$B$543="",$B$542=""),"⚠ falta o valor na linha certa","OK")))))</f>
+        <v/>
+      </c>
+      <c r="C866" s="20" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="D866" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" s="18" t="inlineStr">
+        <is>
+          <t>Custo 24 — conferência</t>
+        </is>
+      </c>
+      <c r="B867" s="23">
+        <f>IF(AND($B$549="",$B$550=""),"",IF(OR($B$549="",$B$550="",$B$552=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$549="terreno",$B$550="Preço",OR($B$552="rs",$B$552="rs_m2_terreno")),AND($B$549="terreno",$B$550="Registro",OR($B$552="rs",$B$552="rs_m2_priv")),AND($B$549="terreno",$B$550="Outro",OR($B$552="rs",$B$552="pct_vgv")),AND($B$549="obra",$B$550="Construção",OR($B$552="rs",$B$552="rs_m2_priv")),AND($B$549="obra",$B$550="Outorga",OR($B$552="rs",$B$552="pct_vgv")),AND($B$549="obra",$B$550="Decoração",OR($B$552="rs",$B$552="rs_m2_priv")),AND($B$549="obra",$B$550="Gestão da obra",OR($B$552="rs",$B$552="pct_obra")),AND($B$549="obra",$B$550="Contingência",OR($B$552="rs",$B$552="pct_vgv")),AND($B$549="obra",$B$550="Outro",OR($B$552="rs",$B$552="pct_vgv")),AND($B$549="diretos",$B$550="Marketing &amp; Publicidade",OR($B$552="rs",$B$552="pct_vgv",$B$552="pct_recebido")),AND($B$549="diretos",$B$550="Corretagem de vendas",OR($B$552="pct_vgv")),AND($B$549="diretos",$B$550="Projetos",OR($B$552="rs",$B$552="rs_m2_priv",$B$552="pct_constr")),AND($B$549="diretos",$B$550="Licenças e Aprovações",OR($B$552="rs",$B$552="rs_m2_priv")),AND($B$549="diretos",$B$550="Manutenção pós-obra",OR($B$552="rs",$B$552="pct_vgv",$B$552="pct_recebido")),AND($B$549="diretos",$B$550="Outro",OR($B$552="rs",$B$552="pct_vgv",$B$552="pct_recebido")),AND($B$549="indireto",$B$550="Marketing global",OR($B$552="rs",$B$552="pct_vgv",$B$552="pct_recebido")),AND($B$549="indireto",$B$550="Stand de vendas",OR($B$552="rs",$B$552="pct_vgv")),AND($B$549="indireto",$B$550="Gestão",OR($B$552="rs",$B$552="pct_vgv",$B$552="pct_recebido")),AND($B$549="indireto",$B$550="Outro",OR($B$552="rs",$B$552="pct_vgv",$B$552="pct_recebido")),AND($B$549="financeiro",$B$550="Juros de financiamento",OR($B$552="rs",$B$552="pct_vgv")),AND($B$549="financeiro",$B$550="Taxas bancárias",OR($B$552="rs",$B$552="pct_vgv")),AND($B$549="financeiro",$B$550="Estruturação de dívida",OR($B$552="rs",$B$552="pct_vgv")),AND($B$549="financeiro",$B$550="Investidores",OR($B$552="rs",$B$552="pct_vgv")),AND($B$549="financeiro",$B$550="Outro",OR($B$552="rs",$B$552="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$553&lt;&gt;"",$B$554&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$552,3)="pct",$B$554="",$B$553=""),"⚠ falta o valor na linha certa","OK")))))</f>
+        <v/>
+      </c>
+      <c r="C867" s="20" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="D867" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" s="18" t="inlineStr">
+        <is>
+          <t>Custo 25 — conferência</t>
+        </is>
+      </c>
+      <c r="B868" s="23">
+        <f>IF(AND($B$560="",$B$561=""),"",IF(OR($B$560="",$B$561="",$B$563=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$560="terreno",$B$561="Preço",OR($B$563="rs",$B$563="rs_m2_terreno")),AND($B$560="terreno",$B$561="Registro",OR($B$563="rs",$B$563="rs_m2_priv")),AND($B$560="terreno",$B$561="Outro",OR($B$563="rs",$B$563="pct_vgv")),AND($B$560="obra",$B$561="Construção",OR($B$563="rs",$B$563="rs_m2_priv")),AND($B$560="obra",$B$561="Outorga",OR($B$563="rs",$B$563="pct_vgv")),AND($B$560="obra",$B$561="Decoração",OR($B$563="rs",$B$563="rs_m2_priv")),AND($B$560="obra",$B$561="Gestão da obra",OR($B$563="rs",$B$563="pct_obra")),AND($B$560="obra",$B$561="Contingência",OR($B$563="rs",$B$563="pct_vgv")),AND($B$560="obra",$B$561="Outro",OR($B$563="rs",$B$563="pct_vgv")),AND($B$560="diretos",$B$561="Marketing &amp; Publicidade",OR($B$563="rs",$B$563="pct_vgv",$B$563="pct_recebido")),AND($B$560="diretos",$B$561="Corretagem de vendas",OR($B$563="pct_vgv")),AND($B$560="diretos",$B$561="Projetos",OR($B$563="rs",$B$563="rs_m2_priv",$B$563="pct_constr")),AND($B$560="diretos",$B$561="Licenças e Aprovações",OR($B$563="rs",$B$563="rs_m2_priv")),AND($B$560="diretos",$B$561="Manutenção pós-obra",OR($B$563="rs",$B$563="pct_vgv",$B$563="pct_recebido")),AND($B$560="diretos",$B$561="Outro",OR($B$563="rs",$B$563="pct_vgv",$B$563="pct_recebido")),AND($B$560="indireto",$B$561="Marketing global",OR($B$563="rs",$B$563="pct_vgv",$B$563="pct_recebido")),AND($B$560="indireto",$B$561="Stand de vendas",OR($B$563="rs",$B$563="pct_vgv")),AND($B$560="indireto",$B$561="Gestão",OR($B$563="rs",$B$563="pct_vgv",$B$563="pct_recebido")),AND($B$560="indireto",$B$561="Outro",OR($B$563="rs",$B$563="pct_vgv",$B$563="pct_recebido")),AND($B$560="financeiro",$B$561="Juros de financiamento",OR($B$563="rs",$B$563="pct_vgv")),AND($B$560="financeiro",$B$561="Taxas bancárias",OR($B$563="rs",$B$563="pct_vgv")),AND($B$560="financeiro",$B$561="Estruturação de dívida",OR($B$563="rs",$B$563="pct_vgv")),AND($B$560="financeiro",$B$561="Investidores",OR($B$563="rs",$B$563="pct_vgv")),AND($B$560="financeiro",$B$561="Outro",OR($B$563="rs",$B$563="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$564&lt;&gt;"",$B$565&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$563,3)="pct",$B$565="",$B$564=""),"⚠ falta o valor na linha certa","OK")))))</f>
+        <v/>
+      </c>
+      <c r="C868" s="20" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="D868" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" s="18" t="inlineStr">
+        <is>
+          <t>Custo 26 — conferência</t>
+        </is>
+      </c>
+      <c r="B869" s="23">
+        <f>IF(AND($B$571="",$B$572=""),"",IF(OR($B$571="",$B$572="",$B$574=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$571="terreno",$B$572="Preço",OR($B$574="rs",$B$574="rs_m2_terreno")),AND($B$571="terreno",$B$572="Registro",OR($B$574="rs",$B$574="rs_m2_priv")),AND($B$571="terreno",$B$572="Outro",OR($B$574="rs",$B$574="pct_vgv")),AND($B$571="obra",$B$572="Construção",OR($B$574="rs",$B$574="rs_m2_priv")),AND($B$571="obra",$B$572="Outorga",OR($B$574="rs",$B$574="pct_vgv")),AND($B$571="obra",$B$572="Decoração",OR($B$574="rs",$B$574="rs_m2_priv")),AND($B$571="obra",$B$572="Gestão da obra",OR($B$574="rs",$B$574="pct_obra")),AND($B$571="obra",$B$572="Contingência",OR($B$574="rs",$B$574="pct_vgv")),AND($B$571="obra",$B$572="Outro",OR($B$574="rs",$B$574="pct_vgv")),AND($B$571="diretos",$B$572="Marketing &amp; Publicidade",OR($B$574="rs",$B$574="pct_vgv",$B$574="pct_recebido")),AND($B$571="diretos",$B$572="Corretagem de vendas",OR($B$574="pct_vgv")),AND($B$571="diretos",$B$572="Projetos",OR($B$574="rs",$B$574="rs_m2_priv",$B$574="pct_constr")),AND($B$571="diretos",$B$572="Licenças e Aprovações",OR($B$574="rs",$B$574="rs_m2_priv")),AND($B$571="diretos",$B$572="Manutenção pós-obra",OR($B$574="rs",$B$574="pct_vgv",$B$574="pct_recebido")),AND($B$571="diretos",$B$572="Outro",OR($B$574="rs",$B$574="pct_vgv",$B$574="pct_recebido")),AND($B$571="indireto",$B$572="Marketing global",OR($B$574="rs",$B$574="pct_vgv",$B$574="pct_recebido")),AND($B$571="indireto",$B$572="Stand de vendas",OR($B$574="rs",$B$574="pct_vgv")),AND($B$571="indireto",$B$572="Gestão",OR($B$574="rs",$B$574="pct_vgv",$B$574="pct_recebido")),AND($B$571="indireto",$B$572="Outro",OR($B$574="rs",$B$574="pct_vgv",$B$574="pct_recebido")),AND($B$571="financeiro",$B$572="Juros de financiamento",OR($B$574="rs",$B$574="pct_vgv")),AND($B$571="financeiro",$B$572="Taxas bancárias",OR($B$574="rs",$B$574="pct_vgv")),AND($B$571="financeiro",$B$572="Estruturação de dívida",OR($B$574="rs",$B$574="pct_vgv")),AND($B$571="financeiro",$B$572="Investidores",OR($B$574="rs",$B$574="pct_vgv")),AND($B$571="financeiro",$B$572="Outro",OR($B$574="rs",$B$574="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$575&lt;&gt;"",$B$576&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$574,3)="pct",$B$576="",$B$575=""),"⚠ falta o valor na linha certa","OK")))))</f>
+        <v/>
+      </c>
+      <c r="C869" s="20" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="D869" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" s="18" t="inlineStr">
+        <is>
+          <t>Custo 27 — conferência</t>
+        </is>
+      </c>
+      <c r="B870" s="23">
+        <f>IF(AND($B$582="",$B$583=""),"",IF(OR($B$582="",$B$583="",$B$585=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$582="terreno",$B$583="Preço",OR($B$585="rs",$B$585="rs_m2_terreno")),AND($B$582="terreno",$B$583="Registro",OR($B$585="rs",$B$585="rs_m2_priv")),AND($B$582="terreno",$B$583="Outro",OR($B$585="rs",$B$585="pct_vgv")),AND($B$582="obra",$B$583="Construção",OR($B$585="rs",$B$585="rs_m2_priv")),AND($B$582="obra",$B$583="Outorga",OR($B$585="rs",$B$585="pct_vgv")),AND($B$582="obra",$B$583="Decoração",OR($B$585="rs",$B$585="rs_m2_priv")),AND($B$582="obra",$B$583="Gestão da obra",OR($B$585="rs",$B$585="pct_obra")),AND($B$582="obra",$B$583="Contingência",OR($B$585="rs",$B$585="pct_vgv")),AND($B$582="obra",$B$583="Outro",OR($B$585="rs",$B$585="pct_vgv")),AND($B$582="diretos",$B$583="Marketing &amp; Publicidade",OR($B$585="rs",$B$585="pct_vgv",$B$585="pct_recebido")),AND($B$582="diretos",$B$583="Corretagem de vendas",OR($B$585="pct_vgv")),AND($B$582="diretos",$B$583="Projetos",OR($B$585="rs",$B$585="rs_m2_priv",$B$585="pct_constr")),AND($B$582="diretos",$B$583="Licenças e Aprovações",OR($B$585="rs",$B$585="rs_m2_priv")),AND($B$582="diretos",$B$583="Manutenção pós-obra",OR($B$585="rs",$B$585="pct_vgv",$B$585="pct_recebido")),AND($B$582="diretos",$B$583="Outro",OR($B$585="rs",$B$585="pct_vgv",$B$585="pct_recebido")),AND($B$582="indireto",$B$583="Marketing global",OR($B$585="rs",$B$585="pct_vgv",$B$585="pct_recebido")),AND($B$582="indireto",$B$583="Stand de vendas",OR($B$585="rs",$B$585="pct_vgv")),AND($B$582="indireto",$B$583="Gestão",OR($B$585="rs",$B$585="pct_vgv",$B$585="pct_recebido")),AND($B$582="indireto",$B$583="Outro",OR($B$585="rs",$B$585="pct_vgv",$B$585="pct_recebido")),AND($B$582="financeiro",$B$583="Juros de financiamento",OR($B$585="rs",$B$585="pct_vgv")),AND($B$582="financeiro",$B$583="Taxas bancárias",OR($B$585="rs",$B$585="pct_vgv")),AND($B$582="financeiro",$B$583="Estruturação de dívida",OR($B$585="rs",$B$585="pct_vgv")),AND($B$582="financeiro",$B$583="Investidores",OR($B$585="rs",$B$585="pct_vgv")),AND($B$582="financeiro",$B$583="Outro",OR($B$585="rs",$B$585="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$586&lt;&gt;"",$B$587&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$585,3)="pct",$B$587="",$B$586=""),"⚠ falta o valor na linha certa","OK")))))</f>
+        <v/>
+      </c>
+      <c r="C870" s="20" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="D870" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" s="18" t="inlineStr">
+        <is>
+          <t>Custo 28 — conferência</t>
+        </is>
+      </c>
+      <c r="B871" s="23">
+        <f>IF(AND($B$593="",$B$594=""),"",IF(OR($B$593="",$B$594="",$B$596=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$593="terreno",$B$594="Preço",OR($B$596="rs",$B$596="rs_m2_terreno")),AND($B$593="terreno",$B$594="Registro",OR($B$596="rs",$B$596="rs_m2_priv")),AND($B$593="terreno",$B$594="Outro",OR($B$596="rs",$B$596="pct_vgv")),AND($B$593="obra",$B$594="Construção",OR($B$596="rs",$B$596="rs_m2_priv")),AND($B$593="obra",$B$594="Outorga",OR($B$596="rs",$B$596="pct_vgv")),AND($B$593="obra",$B$594="Decoração",OR($B$596="rs",$B$596="rs_m2_priv")),AND($B$593="obra",$B$594="Gestão da obra",OR($B$596="rs",$B$596="pct_obra")),AND($B$593="obra",$B$594="Contingência",OR($B$596="rs",$B$596="pct_vgv")),AND($B$593="obra",$B$594="Outro",OR($B$596="rs",$B$596="pct_vgv")),AND($B$593="diretos",$B$594="Marketing &amp; Publicidade",OR($B$596="rs",$B$596="pct_vgv",$B$596="pct_recebido")),AND($B$593="diretos",$B$594="Corretagem de vendas",OR($B$596="pct_vgv")),AND($B$593="diretos",$B$594="Projetos",OR($B$596="rs",$B$596="rs_m2_priv",$B$596="pct_constr")),AND($B$593="diretos",$B$594="Licenças e Aprovações",OR($B$596="rs",$B$596="rs_m2_priv")),AND($B$593="diretos",$B$594="Manutenção pós-obra",OR($B$596="rs",$B$596="pct_vgv",$B$596="pct_recebido")),AND($B$593="diretos",$B$594="Outro",OR($B$596="rs",$B$596="pct_vgv",$B$596="pct_recebido")),AND($B$593="indireto",$B$594="Marketing global",OR($B$596="rs",$B$596="pct_vgv",$B$596="pct_recebido")),AND($B$593="indireto",$B$594="Stand de vendas",OR($B$596="rs",$B$596="pct_vgv")),AND($B$593="indireto",$B$594="Gestão",OR($B$596="rs",$B$596="pct_vgv",$B$596="pct_recebido")),AND($B$593="indireto",$B$594="Outro",OR($B$596="rs",$B$596="pct_vgv",$B$596="pct_recebido")),AND($B$593="financeiro",$B$594="Juros de financiamento",OR($B$596="rs",$B$596="pct_vgv")),AND($B$593="financeiro",$B$594="Taxas bancárias",OR($B$596="rs",$B$596="pct_vgv")),AND($B$593="financeiro",$B$594="Estruturação de dívida",OR($B$596="rs",$B$596="pct_vgv")),AND($B$593="financeiro",$B$594="Investidores",OR($B$596="rs",$B$596="pct_vgv")),AND($B$593="financeiro",$B$594="Outro",OR($B$596="rs",$B$596="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$597&lt;&gt;"",$B$598&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$596,3)="pct",$B$598="",$B$597=""),"⚠ falta o valor na linha certa","OK")))))</f>
+        <v/>
+      </c>
+      <c r="C871" s="20" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="D871" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" s="18" t="inlineStr">
+        <is>
+          <t>Cada 1% do VGV de tabela equivale a (para converter Projetos, que não aceita % do VGV)</t>
+        </is>
+      </c>
+      <c r="B872" s="24">
+        <f>$B$757*0.01</f>
+        <v/>
+      </c>
+      <c r="C872" s="20" t="inlineStr">
+        <is>
+          <t>R$</t>
+        </is>
+      </c>
+      <c r="D872" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" s="18" t="inlineStr">
+        <is>
+          <t>Σ custos conversíveis — terreno</t>
+        </is>
+      </c>
+      <c r="B873" s="24">
+        <f>IF($B$296="terreno",N($B$816),0)+IF($B$307="terreno",N($B$817),0)+IF($B$318="terreno",N($B$818),0)+IF($B$329="terreno",N($B$819),0)+IF($B$340="terreno",N($B$820),0)+IF($B$351="terreno",N($B$821),0)+IF($B$362="terreno",N($B$822),0)+IF($B$373="terreno",N($B$823),0)+IF($B$384="terreno",N($B$824),0)+IF($B$395="terreno",N($B$825),0)+IF($B$406="terreno",N($B$826),0)+IF($B$417="terreno",N($B$827),0)+IF($B$428="terreno",N($B$828),0)+IF($B$439="terreno",N($B$829),0)+IF($B$450="terreno",N($B$830),0)+IF($B$461="terreno",N($B$831),0)+IF($B$472="terreno",N($B$832),0)+IF($B$483="terreno",N($B$833),0)+IF($B$494="terreno",N($B$834),0)+IF($B$505="terreno",N($B$835),0)+IF($B$516="terreno",N($B$836),0)+IF($B$527="terreno",N($B$837),0)+IF($B$538="terreno",N($B$838),0)+IF($B$549="terreno",N($B$839),0)+IF($B$560="terreno",N($B$840),0)+IF($B$571="terreno",N($B$841),0)+IF($B$582="terreno",N($B$842),0)+IF($B$593="terreno",N($B$843),0)</f>
+        <v/>
+      </c>
+      <c r="C873" s="20" t="inlineStr">
+        <is>
+          <t>R$</t>
+        </is>
+      </c>
+      <c r="D873" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" s="18" t="inlineStr">
+        <is>
+          <t>Σ custos conversíveis — obra</t>
+        </is>
+      </c>
+      <c r="B874" s="24">
+        <f>IF($B$296="obra",N($B$816),0)+IF($B$307="obra",N($B$817),0)+IF($B$318="obra",N($B$818),0)+IF($B$329="obra",N($B$819),0)+IF($B$340="obra",N($B$820),0)+IF($B$351="obra",N($B$821),0)+IF($B$362="obra",N($B$822),0)+IF($B$373="obra",N($B$823),0)+IF($B$384="obra",N($B$824),0)+IF($B$395="obra",N($B$825),0)+IF($B$406="obra",N($B$826),0)+IF($B$417="obra",N($B$827),0)+IF($B$428="obra",N($B$828),0)+IF($B$439="obra",N($B$829),0)+IF($B$450="obra",N($B$830),0)+IF($B$461="obra",N($B$831),0)+IF($B$472="obra",N($B$832),0)+IF($B$483="obra",N($B$833),0)+IF($B$494="obra",N($B$834),0)+IF($B$505="obra",N($B$835),0)+IF($B$516="obra",N($B$836),0)+IF($B$527="obra",N($B$837),0)+IF($B$538="obra",N($B$838),0)+IF($B$549="obra",N($B$839),0)+IF($B$560="obra",N($B$840),0)+IF($B$571="obra",N($B$841),0)+IF($B$582="obra",N($B$842),0)+IF($B$593="obra",N($B$843),0)</f>
+        <v/>
+      </c>
+      <c r="C874" s="20" t="inlineStr">
+        <is>
+          <t>R$</t>
+        </is>
+      </c>
+      <c r="D874" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" s="18" t="inlineStr">
+        <is>
+          <t>Σ custos conversíveis — diretos</t>
+        </is>
+      </c>
+      <c r="B875" s="24">
+        <f>IF($B$296="diretos",N($B$816),0)+IF($B$307="diretos",N($B$817),0)+IF($B$318="diretos",N($B$818),0)+IF($B$329="diretos",N($B$819),0)+IF($B$340="diretos",N($B$820),0)+IF($B$351="diretos",N($B$821),0)+IF($B$362="diretos",N($B$822),0)+IF($B$373="diretos",N($B$823),0)+IF($B$384="diretos",N($B$824),0)+IF($B$395="diretos",N($B$825),0)+IF($B$406="diretos",N($B$826),0)+IF($B$417="diretos",N($B$827),0)+IF($B$428="diretos",N($B$828),0)+IF($B$439="diretos",N($B$829),0)+IF($B$450="diretos",N($B$830),0)+IF($B$461="diretos",N($B$831),0)+IF($B$472="diretos",N($B$832),0)+IF($B$483="diretos",N($B$833),0)+IF($B$494="diretos",N($B$834),0)+IF($B$505="diretos",N($B$835),0)+IF($B$516="diretos",N($B$836),0)+IF($B$527="diretos",N($B$837),0)+IF($B$538="diretos",N($B$838),0)+IF($B$549="diretos",N($B$839),0)+IF($B$560="diretos",N($B$840),0)+IF($B$571="diretos",N($B$841),0)+IF($B$582="diretos",N($B$842),0)+IF($B$593="diretos",N($B$843),0)</f>
+        <v/>
+      </c>
+      <c r="C875" s="20" t="inlineStr">
+        <is>
+          <t>R$</t>
+        </is>
+      </c>
+      <c r="D875" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" s="18" t="inlineStr">
+        <is>
+          <t>Σ custos conversíveis — indireto</t>
+        </is>
+      </c>
+      <c r="B876" s="24">
+        <f>IF($B$296="indireto",N($B$816),0)+IF($B$307="indireto",N($B$817),0)+IF($B$318="indireto",N($B$818),0)+IF($B$329="indireto",N($B$819),0)+IF($B$340="indireto",N($B$820),0)+IF($B$351="indireto",N($B$821),0)+IF($B$362="indireto",N($B$822),0)+IF($B$373="indireto",N($B$823),0)+IF($B$384="indireto",N($B$824),0)+IF($B$395="indireto",N($B$825),0)+IF($B$406="indireto",N($B$826),0)+IF($B$417="indireto",N($B$827),0)+IF($B$428="indireto",N($B$828),0)+IF($B$439="indireto",N($B$829),0)+IF($B$450="indireto",N($B$830),0)+IF($B$461="indireto",N($B$831),0)+IF($B$472="indireto",N($B$832),0)+IF($B$483="indireto",N($B$833),0)+IF($B$494="indireto",N($B$834),0)+IF($B$505="indireto",N($B$835),0)+IF($B$516="indireto",N($B$836),0)+IF($B$527="indireto",N($B$837),0)+IF($B$538="indireto",N($B$838),0)+IF($B$549="indireto",N($B$839),0)+IF($B$560="indireto",N($B$840),0)+IF($B$571="indireto",N($B$841),0)+IF($B$582="indireto",N($B$842),0)+IF($B$593="indireto",N($B$843),0)</f>
+        <v/>
+      </c>
+      <c r="C876" s="20" t="inlineStr">
+        <is>
+          <t>R$</t>
+        </is>
+      </c>
+      <c r="D876" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" s="18" t="inlineStr">
+        <is>
+          <t>Σ custos conversíveis — financeiro</t>
+        </is>
+      </c>
+      <c r="B877" s="24">
+        <f>IF($B$296="financeiro",N($B$816),0)+IF($B$307="financeiro",N($B$817),0)+IF($B$318="financeiro",N($B$818),0)+IF($B$329="financeiro",N($B$819),0)+IF($B$340="financeiro",N($B$820),0)+IF($B$351="financeiro",N($B$821),0)+IF($B$362="financeiro",N($B$822),0)+IF($B$373="financeiro",N($B$823),0)+IF($B$384="financeiro",N($B$824),0)+IF($B$395="financeiro",N($B$825),0)+IF($B$406="financeiro",N($B$826),0)+IF($B$417="financeiro",N($B$827),0)+IF($B$428="financeiro",N($B$828),0)+IF($B$439="financeiro",N($B$829),0)+IF($B$450="financeiro",N($B$830),0)+IF($B$461="financeiro",N($B$831),0)+IF($B$472="financeiro",N($B$832),0)+IF($B$483="financeiro",N($B$833),0)+IF($B$494="financeiro",N($B$834),0)+IF($B$505="financeiro",N($B$835),0)+IF($B$516="financeiro",N($B$836),0)+IF($B$527="financeiro",N($B$837),0)+IF($B$538="financeiro",N($B$838),0)+IF($B$549="financeiro",N($B$839),0)+IF($B$560="financeiro",N($B$840),0)+IF($B$571="financeiro",N($B$841),0)+IF($B$582="financeiro",N($B$842),0)+IF($B$593="financeiro",N($B$843),0)</f>
+        <v/>
+      </c>
+      <c r="C877" s="20" t="inlineStr">
+        <is>
+          <t>R$</t>
+        </is>
+      </c>
+      <c r="D877" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" s="18" t="inlineStr">
+        <is>
+          <t>Permuta física 1 — VGV entregue (unidades × área × preço sugerido)</t>
+        </is>
+      </c>
+      <c r="B878" s="24">
+        <f>IF($B$604="",0,N($B$605)*(($B$58=$B$604)*(N($B$59)+N($B$60))*N($B$62)+($B$64=$B$604)*(N($B$65)+N($B$66))*N($B$68)+($B$70=$B$604)*(N($B$71)+N($B$72))*N($B$74)+($B$76=$B$604)*(N($B$77)+N($B$78))*N($B$80)+($B$82=$B$604)*(N($B$83)+N($B$84))*N($B$86)+($B$88=$B$604)*(N($B$89)+N($B$90))*N($B$92)+($B$94=$B$604)*(N($B$95)+N($B$96))*N($B$98)+($B$100=$B$604)*(N($B$101)+N($B$102))*N($B$104)+($B$106=$B$604)*(N($B$107)+N($B$108))*N($B$110)+($B$112=$B$604)*(N($B$113)+N($B$114))*N($B$116)))</f>
+        <v/>
+      </c>
+      <c r="C878" s="20" t="inlineStr">
+        <is>
+          <t>R$</t>
+        </is>
+      </c>
+      <c r="D878" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" s="18" t="inlineStr">
+        <is>
+          <t>Permuta financeira 1 — equivalente em R$</t>
+        </is>
+      </c>
+      <c r="B879" s="24">
+        <f>IF($B$609="pct_vgv",N($B$611)*$B$757,IF($B$609="rs",N($B$610),0))</f>
+        <v/>
+      </c>
+      <c r="C879" s="20" t="inlineStr">
+        <is>
+          <t>R$</t>
+        </is>
+      </c>
+      <c r="D879" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" s="18" t="inlineStr">
+        <is>
+          <t>Permuta física 2 — VGV entregue (unidades × área × preço sugerido)</t>
+        </is>
+      </c>
+      <c r="B880" s="24">
+        <f>IF($B$606="",0,N($B$607)*(($B$58=$B$606)*(N($B$59)+N($B$60))*N($B$62)+($B$64=$B$606)*(N($B$65)+N($B$66))*N($B$68)+($B$70=$B$606)*(N($B$71)+N($B$72))*N($B$74)+($B$76=$B$606)*(N($B$77)+N($B$78))*N($B$80)+($B$82=$B$606)*(N($B$83)+N($B$84))*N($B$86)+($B$88=$B$606)*(N($B$89)+N($B$90))*N($B$92)+($B$94=$B$606)*(N($B$95)+N($B$96))*N($B$98)+($B$100=$B$606)*(N($B$101)+N($B$102))*N($B$104)+($B$106=$B$606)*(N($B$107)+N($B$108))*N($B$110)+($B$112=$B$606)*(N($B$113)+N($B$114))*N($B$116)))</f>
+        <v/>
+      </c>
+      <c r="C880" s="20" t="inlineStr">
+        <is>
+          <t>R$</t>
+        </is>
+      </c>
+      <c r="D880" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" s="18" t="inlineStr">
+        <is>
+          <t>Permuta financeira 2 — equivalente em R$</t>
+        </is>
+      </c>
+      <c r="B881" s="24">
+        <f>IF($B$614="pct_vgv",N($B$616)*$B$757,IF($B$614="rs",N($B$615),0))</f>
+        <v/>
+      </c>
+      <c r="C881" s="20" t="inlineStr">
+        <is>
+          <t>R$</t>
+        </is>
+      </c>
+      <c r="D881" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" s="18" t="inlineStr">
+        <is>
+          <t>Σ valor das dívidas</t>
+        </is>
+      </c>
+      <c r="B882" s="24">
+        <f>N($B$631)+N($B$644)+N($B$657)</f>
+        <v/>
+      </c>
+      <c r="C882" s="20" t="inlineStr">
+        <is>
+          <t>R$</t>
+        </is>
+      </c>
+      <c r="D882" s="21" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" s="18" t="inlineStr">
+        <is>
           <t>Σ valor dos equities</t>
         </is>
       </c>
-      <c r="B854" s="24">
+      <c r="B883" s="24">
         <f>N($B$670)+N($B$677)+N($B$684)</f>
         <v/>
       </c>
-      <c r="C854" s="20" t="inlineStr">
+      <c r="C883" s="20" t="inlineStr">
         <is>
           <t>R$</t>
         </is>
       </c>
-      <c r="D854" s="21" t="inlineStr">
+      <c r="D883" s="21" t="inlineStr">
         <is>
           <t>calculado</t>
         </is>
       </c>
     </row>
-    <row r="857">
-      <c r="F857" t="inlineStr">
+    <row r="886">
+      <c r="F886" t="inlineStr">
         <is>
           <t>Preço</t>
         </is>
       </c>
     </row>
-    <row r="858">
-      <c r="F858" t="inlineStr">
+    <row r="887">
+      <c r="F887" t="inlineStr">
         <is>
           <t>Registro</t>
         </is>
       </c>
     </row>
-    <row r="859">
-      <c r="F859" t="inlineStr">
+    <row r="888">
+      <c r="F888" t="inlineStr">
         <is>
           <t>Outro</t>
         </is>
       </c>
     </row>
-    <row r="860">
-      <c r="F860" t="inlineStr">
+    <row r="889">
+      <c r="F889" t="inlineStr">
         <is>
           <t>Construção</t>
         </is>
       </c>
     </row>
-    <row r="861">
-      <c r="F861" t="inlineStr">
+    <row r="890">
+      <c r="F890" t="inlineStr">
         <is>
           <t>Outorga</t>
         </is>
       </c>
     </row>
-    <row r="862">
-      <c r="F862" t="inlineStr">
+    <row r="891">
+      <c r="F891" t="inlineStr">
         <is>
           <t>Decoração</t>
         </is>
       </c>
     </row>
-    <row r="863">
-      <c r="F863" t="inlineStr">
+    <row r="892">
+      <c r="F892" t="inlineStr">
         <is>
           <t>Gestão da obra</t>
         </is>
       </c>
     </row>
-    <row r="864">
-      <c r="F864" t="inlineStr">
+    <row r="893">
+      <c r="F893" t="inlineStr">
         <is>
           <t>Contingência</t>
         </is>
       </c>
     </row>
-    <row r="865">
-      <c r="F865" t="inlineStr">
+    <row r="894">
+      <c r="F894" t="inlineStr">
         <is>
           <t>Marketing &amp; Publicidade</t>
         </is>
       </c>
     </row>
-    <row r="866">
-      <c r="F866" t="inlineStr">
+    <row r="895">
+      <c r="F895" t="inlineStr">
         <is>
           <t>Corretagem de vendas</t>
         </is>
       </c>
     </row>
-    <row r="867">
-      <c r="F867" t="inlineStr">
+    <row r="896">
+      <c r="F896" t="inlineStr">
         <is>
           <t>Projetos</t>
         </is>
       </c>
     </row>
-    <row r="868">
-      <c r="F868" t="inlineStr">
+    <row r="897">
+      <c r="F897" t="inlineStr">
         <is>
           <t>Licenças e Aprovações</t>
         </is>
       </c>
     </row>
-    <row r="869">
-      <c r="F869" t="inlineStr">
+    <row r="898">
+      <c r="F898" t="inlineStr">
         <is>
           <t>Manutenção pós-obra</t>
         </is>
       </c>
     </row>
-    <row r="870">
-      <c r="F870" t="inlineStr">
+    <row r="899">
+      <c r="F899" t="inlineStr">
         <is>
           <t>Marketing global</t>
         </is>
       </c>
     </row>
-    <row r="871">
-      <c r="F871" t="inlineStr">
+    <row r="900">
+      <c r="F900" t="inlineStr">
         <is>
           <t>Gestão</t>
         </is>
       </c>
     </row>
-    <row r="872">
-      <c r="F872" t="inlineStr">
+    <row r="901">
+      <c r="F901" t="inlineStr">
         <is>
           <t>Stand de vendas</t>
         </is>
       </c>
     </row>
-    <row r="873">
-      <c r="F873" t="inlineStr">
+    <row r="902">
+      <c r="F902" t="inlineStr">
         <is>
           <t>Juros de financiamento</t>
         </is>
       </c>
     </row>
-    <row r="874">
-      <c r="F874" t="inlineStr">
+    <row r="903">
+      <c r="F903" t="inlineStr">
         <is>
           <t>Taxas bancárias</t>
         </is>
       </c>
     </row>
-    <row r="875">
-      <c r="F875" t="inlineStr">
+    <row r="904">
+      <c r="F904" t="inlineStr">
         <is>
           <t>Estruturação de dívida</t>
         </is>
       </c>
     </row>
-    <row r="876">
-      <c r="F876" t="inlineStr">
+    <row r="905">
+      <c r="F905" t="inlineStr">
         <is>
           <t>Investidores</t>
         </is>
       </c>
     </row>
-    <row r="878">
-      <c r="F878" t="inlineStr">
+    <row r="907">
+      <c r="F907" t="inlineStr">
         <is>
           <t>planejamento</t>
         </is>
       </c>
     </row>
-    <row r="879">
-      <c r="F879" t="inlineStr">
+    <row r="908">
+      <c r="F908" t="inlineStr">
         <is>
           <t>pre_lancamento</t>
         </is>
       </c>
     </row>
-    <row r="880">
-      <c r="F880" t="inlineStr">
+    <row r="909">
+      <c r="F909" t="inlineStr">
         <is>
           <t>lancamento</t>
         </is>
       </c>
     </row>
-    <row r="881">
-      <c r="F881" t="inlineStr">
+    <row r="910">
+      <c r="F910" t="inlineStr">
         <is>
           <t>obra</t>
         </is>
       </c>
     </row>
-    <row r="882">
-      <c r="F882" t="inlineStr">
+    <row r="911">
+      <c r="F911" t="inlineStr">
         <is>
           <t>pos_obra</t>
         </is>
       </c>
     </row>
-    <row r="883">
-      <c r="F883" t="inlineStr">
+    <row r="912">
+      <c r="F912" t="inlineStr">
         <is>
           <t>customizado</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="F914" t="inlineStr">
+        <is>
+          <t>Linear</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="F915" t="inlineStr">
+        <is>
+          <t>Curva S</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="F916" t="inlineStr">
+        <is>
+          <t>unit_delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="F917" t="inlineStr">
+        <is>
+          <t>sales_revenue</t>
         </is>
       </c>
     </row>
@@ -16117,7 +16754,7 @@
     <mergeCell ref="A449:D449"/>
     <mergeCell ref="A160:D160"/>
   </mergeCells>
-  <dataValidations count="22">
+  <dataValidations count="23">
     <dataValidation sqref="B5 B14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="No máximo 200 caracteres." type="textLength" errorStyle="warning" operator="lessThanOrEqual">
       <formula1>200</formula1>
     </dataValidation>
@@ -16173,14 +16810,17 @@
       <formula1>0</formula1>
       <formula2>10</formula2>
     </dataValidation>
+    <dataValidation sqref="B302 B313 B324 B335 B346 B357 B368 B379 B390 B401 B412 B423 B434 B445 B456 B467 B478 B489 B500 B511 B522 B533 B544 B555 B566 B577 B588 B599" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Confira o valor" error="Valor fora da lista de referência — confirme." type="list" errorStyle="warning">
+      <formula1>$F$914:$F$917</formula1>
+    </dataValidation>
     <dataValidation sqref="B303 B314 B325 B336 B347 B358 B369 B380 B391 B402 B413 B424 B435 B446 B457 B468 B479 B490 B501 B512 B523 B534 B545 B556 B567 B578 B589 B600 B632 B645 B658 B671 B678 B685" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Confira o valor" error="Valor fora da lista de referência — confirme." type="list" errorStyle="warning">
-      <formula1>$F$878:$F$883</formula1>
+      <formula1>$F$907:$F$912</formula1>
     </dataValidation>
     <dataValidation sqref="B329 B340 B351 B362 B373 B384 B395 B406 B417 B428 B439 B450 B461 B472 B483 B494 B505 B516 B527 B538 B549 B560 B571 B582 B593" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor inválido" error="Escolha um valor da lista." type="list">
       <formula1>"terreno,obra,diretos,indireto,financeiro"</formula1>
     </dataValidation>
     <dataValidation sqref="B330 B341 B352 B363 B374 B385 B396 B407 B418 B429 B440 B451 B462 B473 B484 B495 B506 B517 B528 B539 B550 B561 B572 B583 B594" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Confira o valor" error="Valor fora da lista de referência — confirme." type="list" errorStyle="warning">
-      <formula1>$F$857:$F$876</formula1>
+      <formula1>$F$886:$F$905</formula1>
     </dataValidation>
     <dataValidation sqref="B609 B614" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor inválido" error="Escolha um valor da lista." type="list">
       <formula1>"rs,pct_vgv"</formula1>

--- a/referencia/formularios/exemplos/exemplo-loteamento-vale-do-sol-avancado.xlsx
+++ b/referencia/formularios/exemplos/exemplo-loteamento-vale-do-sol-avancado.xlsx
@@ -712,7 +712,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>lista: manual (inserir novo) | nucleo (buscar terreno)</t>
+          <t>lista: manual (inserir novo) | nucleo (buscar terreno — o importador só aceita manual)</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
@@ -5567,7 +5567,7 @@
     <row r="293" ht="117" customHeight="1">
       <c r="A293" s="12" t="inlineStr">
         <is>
-          <t>Categorias e unidades aceitas (rs = R$ · rs_m2_priv = R$/m² privativo · rs_m2_terreno · pct_vgv · pct_receita · pct_obra · pct_recebido · pct_constr). TERRENO: Preço (rs, rs_m2_terreno; permuta financeira: rs, pct_vgv) · Registro (rs, rs_m2_priv) · Outro (rs, pct_vgv). OBRA: Construção, Decoração (rs, rs_m2_priv) · Outorga, Contingência, Outro (rs, pct_vgv) · Gestão da obra (rs, pct_obra). DIRETOS: Marketing &amp; Publicidade, Manutenção pós-obra, Outro (rs, pct_vgv, pct_recebido) · Corretagem de vendas (pct_vgv) · Projetos (rs, rs_m2_priv, pct_constr) · Licenças e Aprovações (rs, rs_m2_priv). INDIRETO: Marketing global, Gestão, Outro (rs, pct_vgv, pct_recebido) · Stand de vendas (rs, pct_vgv). FINANCEIRO: Juros de financiamento, Taxas bancárias, Estruturação de dívida, Investidores, Outro (rs, pct_vgv). Cronograma padrão: terreno/Preço = customizado; terreno/demais, indireto = planejamento; obra/diretos/financeiro = obra; Manutenção pós-obra = pos_obra. Início e Duração só valem com cronograma = customizado; cronograma ancorado em fase customizada = escrever "fase: &lt;nome da fase&gt;". Corretagem sai no mês da venda e a permuta física na entrega das unidades (não escolhem distribuição). Obrigatórias: terreno/Preço, obra/Construção, diretos/Corretagem de vendas (% VGV).</t>
+          <t>Categorias e unidades aceitas (rs = R$ · rs_m2_priv = R$/m² privativo · rs_m2_terreno · pct_vgv · pct_obra · pct_recebido · pct_constr). TERRENO: Preço (rs, rs_m2_terreno; permuta financeira: rs, pct_vgv) · Registro (rs, rs_m2_priv) · Outro (rs, pct_vgv). OBRA: Construção, Decoração (rs, rs_m2_priv) · Outorga, Contingência, Outro (rs, pct_vgv) · Gestão da obra (rs, pct_obra). DIRETOS: Marketing &amp; Publicidade, Manutenção pós-obra, Outro (rs, pct_vgv, pct_recebido) · Corretagem de vendas (pct_vgv) · Projetos (rs, rs_m2_priv, pct_constr) · Licenças e Aprovações (rs, rs_m2_priv). INDIRETO: Marketing global, Gestão, Outro (rs, pct_vgv, pct_recebido) · Stand de vendas (rs, pct_vgv). FINANCEIRO: Juros de financiamento, Taxas bancárias, Estruturação de dívida, Investidores, Outro (rs, pct_vgv). Cronograma padrão: terreno/Preço = customizado; terreno/demais, indireto = planejamento; obra/diretos/financeiro = obra; Manutenção pós-obra = pos_obra. Início e Duração só valem com cronograma = customizado; cronograma ancorado em fase customizada = escrever "fase: &lt;nome da fase&gt;". Corretagem sai no mês da venda e a permuta física na entrega das unidades (não escolhem distribuição). Obrigatórias: terreno/Preço, obra/Construção, diretos/Corretagem de vendas (% VGV).</t>
         </is>
       </c>
     </row>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C299" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D299" s="8" t="inlineStr">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C310" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D310" s="8" t="inlineStr">
@@ -6082,7 +6082,7 @@
       </c>
       <c r="C321" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D321" s="8" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="C332" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D332" s="8" t="inlineStr">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="C343" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D343" s="8" t="inlineStr">
@@ -6699,7 +6699,7 @@
       </c>
       <c r="C354" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D354" s="8" t="inlineStr">
@@ -6906,7 +6906,7 @@
       </c>
       <c r="C365" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D365" s="8" t="inlineStr">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="C376" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D376" s="8" t="inlineStr">
@@ -7324,7 +7324,7 @@
       </c>
       <c r="C387" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D387" s="8" t="inlineStr">
@@ -7519,7 +7519,7 @@
       <c r="B398" s="6" t="n"/>
       <c r="C398" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D398" s="8" t="inlineStr">
@@ -7704,7 +7704,7 @@
       <c r="B409" s="6" t="n"/>
       <c r="C409" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D409" s="8" t="inlineStr">
@@ -7889,7 +7889,7 @@
       <c r="B420" s="6" t="n"/>
       <c r="C420" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D420" s="8" t="inlineStr">
@@ -8074,7 +8074,7 @@
       <c r="B431" s="6" t="n"/>
       <c r="C431" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D431" s="8" t="inlineStr">
@@ -8259,7 +8259,7 @@
       <c r="B442" s="6" t="n"/>
       <c r="C442" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D442" s="8" t="inlineStr">
@@ -8444,7 +8444,7 @@
       <c r="B453" s="6" t="n"/>
       <c r="C453" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D453" s="8" t="inlineStr">
@@ -8629,7 +8629,7 @@
       <c r="B464" s="6" t="n"/>
       <c r="C464" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D464" s="8" t="inlineStr">
@@ -8814,7 +8814,7 @@
       <c r="B475" s="6" t="n"/>
       <c r="C475" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D475" s="8" t="inlineStr">
@@ -8999,7 +8999,7 @@
       <c r="B486" s="6" t="n"/>
       <c r="C486" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D486" s="8" t="inlineStr">
@@ -9184,7 +9184,7 @@
       <c r="B497" s="6" t="n"/>
       <c r="C497" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D497" s="8" t="inlineStr">
@@ -9369,7 +9369,7 @@
       <c r="B508" s="6" t="n"/>
       <c r="C508" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D508" s="8" t="inlineStr">
@@ -9554,7 +9554,7 @@
       <c r="B519" s="6" t="n"/>
       <c r="C519" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D519" s="8" t="inlineStr">
@@ -9739,7 +9739,7 @@
       <c r="B530" s="6" t="n"/>
       <c r="C530" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D530" s="8" t="inlineStr">
@@ -9924,7 +9924,7 @@
       <c r="B541" s="6" t="n"/>
       <c r="C541" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D541" s="8" t="inlineStr">
@@ -10109,7 +10109,7 @@
       <c r="B552" s="6" t="n"/>
       <c r="C552" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D552" s="8" t="inlineStr">
@@ -10294,7 +10294,7 @@
       <c r="B563" s="6" t="n"/>
       <c r="C563" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D563" s="8" t="inlineStr">
@@ -10479,7 +10479,7 @@
       <c r="B574" s="6" t="n"/>
       <c r="C574" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D574" s="8" t="inlineStr">
@@ -10664,7 +10664,7 @@
       <c r="B585" s="6" t="n"/>
       <c r="C585" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D585" s="8" t="inlineStr">
@@ -10849,7 +10849,7 @@
       <c r="B596" s="6" t="n"/>
       <c r="C596" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D596" s="8" t="inlineStr">
@@ -16804,7 +16804,7 @@
       <formula1>"Entrada,Parcelamento"</formula1>
     </dataValidation>
     <dataValidation sqref="B299 B310 B332 B343 B354 B365 B376 B387 B398 B409 B420 B431 B442 B453 B464 B475 B486 B497 B508 B519 B530 B541 B552 B563 B574 B585 B596" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor inválido" error="Escolha um valor da lista." type="list">
-      <formula1>"rs,rs_m2_priv,rs_m2_terreno,pct_vgv,pct_receita,pct_obra,pct_recebido,pct_constr"</formula1>
+      <formula1>"rs,rs_m2_priv,rs_m2_terreno,pct_vgv,pct_obra,pct_recebido,pct_constr"</formula1>
     </dataValidation>
     <dataValidation sqref="B301 B312 B323 B334 B345 B356 B367 B378 B389 B400 B411 B422 B433 B444 B455 B466 B477 B488 B499 B510 B521 B532 B543 B554 B565 B576 B587 B598" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Confira o valor" error="Valor fora da faixa esperada (0 a 10)." type="decimal" errorStyle="warning" operator="between">
       <formula1>0</formula1>

--- a/referencia/formularios/exemplos/exemplo-loteamento-vale-do-sol-avancado.xlsx
+++ b/referencia/formularios/exemplos/exemplo-loteamento-vale-do-sol-avancado.xlsx
@@ -600,7 +600,7 @@
     <row r="2" ht="92" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Como preencher: só as células AMARELAS da coluna B. Cinza-claro com valor em negrito = fixo do tipo de estudo (não editar); cinza com itálico = calculado pelo Excel, só para conferir (não editar). * = obrigatório. PERCENTUAL: digite como porcentagem (4% ou 4 numa célula já formatada em %). O Excel guarda 0,04; a API do app espera pontos (4) e o importador converte pelo FORMATO da célula — por isso não troque o formato das células. Números sem separador de milhar e com ponto decimal quando digitados fora do Excel. CAMPO COM VÁRIAS UNIDADES: há uma linha por unidade — preencha UMA só e deixe as outras em branco; o Excel não converte uma na outra. Listas (produtos, custos…) têm vagas numeradas; vaga totalmente em branco = sem item. Meses: 0 = mês da data de início do projeto.</t>
+          <t>Como preencher: só as células AMARELAS da coluna B. Cinza-claro com valor em negrito = fixo do tipo de estudo (não editar); cinza com itálico = calculado pelo Excel, só para conferir (não editar). * = obrigatório. PERCENTUAL: digite com o símbolo % (4%), nunca só o número. O Excel guarda 0,04; a API do app espera pontos (4) e o importador converte pelo FORMATO da célula — por isso não troque o formato das células. Números sem separador de milhar e com ponto decimal quando digitados fora do Excel. CAMPO COM VÁRIAS UNIDADES: há uma linha por unidade — preencha UMA só e deixe as outras em branco; o Excel não converte uma na outra. Listas (produtos, custos…) têm vagas numeradas; vaga totalmente em branco = sem item. Meses: 0 = mês da data de início do projeto.</t>
         </is>
       </c>
     </row>

--- a/referencia/formularios/exemplos/exemplo-loteamento-vale-do-sol-avancado.xlsx
+++ b/referencia/formularios/exemplos/exemplo-loteamento-vale-do-sol-avancado.xlsx
@@ -2594,7 +2594,7 @@
     <row r="119" ht="39" customHeight="1">
       <c r="A119" s="12" t="inlineStr">
         <is>
-          <t>Saldo de chaves = o Repasse acima. "Repasse bancário" é a parte dele paga pelo banco no mês seguinte ao fim da obra (vazio = 100%, tudo no banco). O resto vira carteira própria: a empresa financia o comprador em N parcelas mensais Price com os Juros de tabela, a partir do mês seguinte ao fim da obra + a carência. Loteamento sem banco: 0%.</t>
+          <t>Saldo de chaves = o Repasse acima. "Repasse bancário" é a parte dele paga pelo banco no mês seguinte ao fim da obra (vazio = 100%, tudo no banco). O resto vira carteira própria: a empresa financia o comprador em N parcelas mensais Price com os Juros de tabela, a partir do mês seguinte ao fim da obra + a carência (nunca antes do mês seguinte à venda): também a venda feita depois da entrega tem essa parte financiada. Loteamento sem banco: 0%.</t>
         </is>
       </c>
     </row>
@@ -17619,7 +17619,7 @@
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="A175:D175"/>
   </mergeCells>
-  <dataValidations count="23">
+  <dataValidations count="24">
     <dataValidation sqref="B5 B14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="No máximo 200 caracteres." type="textLength" errorStyle="warning" operator="lessThanOrEqual">
       <formula1>200</formula1>
     </dataValidation>
@@ -17640,7 +17640,7 @@
       <formula1>0</formula1>
       <formula2>9.9999</formula2>
     </dataValidation>
-    <dataValidation sqref="B20 B23 B122 B123 B124 B128 B133 B134 B135 B139 B144 B145 B146 B150 B155 B156 B157 B161 B166 B167 B168 B172 B180 B182 B183 B188 B190 B191 B196 B198 B199 B204 B206 B207 B212 B214 B215 B220 B222 B223 B228 B230 B231 B236 B238 B239 B244 B246 B247 B252 B254 B255 B627 B632 B640 B641 B642 B652 B655 B665 B668 B678 B681 B690 B697 B704 B710 B711 B712 B719 B720 B721 B728 B729 B730" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Confira o valor" error="Valor fora da faixa esperada (0 a 1)." type="decimal" errorStyle="warning" operator="between">
+    <dataValidation sqref="B20 B23 B122 B123 B124 B128 B133 B134 B135 B139 B144 B145 B146 B150 B155 B156 B157 B161 B166 B167 B168 B172 B180 B182 B183 B188 B190 B191 B196 B198 B199 B204 B206 B207 B212 B214 B215 B220 B222 B223 B228 B230 B231 B236 B238 B239 B244 B246 B247 B252 B254 B255 B627 B632 B640 B641 B642 B652 B655 B665 B668 B678 B681 B690 B697 B704 B711 B712 B720 B721 B729 B730" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Confira o valor" error="Valor fora da faixa esperada (0 a 1)." type="decimal" errorStyle="warning" operator="between">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
@@ -17693,6 +17693,10 @@
     <dataValidation sqref="B689 B696 B703" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor inválido" error="Escolha um valor da lista." type="list">
       <formula1>"permuta_financeira,resultado_final"</formula1>
     </dataValidation>
+    <dataValidation sqref="B710 B719 B728" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Confira o valor" error="Valor fora da faixa esperada (0.0001 a 1)." type="decimal" errorStyle="warning" operator="between">
+      <formula1>0.0001</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
     <dataValidation sqref="B735 B736 B738 B739 B741 B742 B744 B745 B747 B748" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Confira o valor" error="Valor fora da faixa esperada (-1 a 10)." type="decimal" errorStyle="warning" operator="between">
       <formula1>-1</formula1>
       <formula2>10</formula2>
